--- a/xlsx/CPE.xlsx
+++ b/xlsx/CPE.xlsx
@@ -76,9 +76,9 @@
     <t>A major</t>
   </si>
   <si>
-    <t>1. Allegro (la majeur)
-2. Adagio (fa dièse mineur)
-3. Allegro (la majeur)</t>
+    <t>1. Allegro (A major)
+2. Adagio (F-sharp minor)
+3. Allegro (A major)</t>
   </si>
   <si>
     <t>Harpsichord, 2 Violins, Viola, Basso</t>
@@ -90,9 +90,9 @@
     <t>H. 411</t>
   </si>
   <si>
-    <t>1. Allegro (la majeur)
-2. Andante (la mineur)
-3. Allegro (la majeur)</t>
+    <t>1. Allegro (A major)
+2. Andante (A minor)
+3. Allegro (A major)</t>
   </si>
   <si>
     <t>Wq. 19</t>
@@ -101,9 +101,9 @@
     <t>H. 422</t>
   </si>
   <si>
-    <t>1. Allegro (la majeur)
-2. Andante (la mineur)
-3. Allegro assai (la majeur)</t>
+    <t>1. Allegro (A major)
+2. Andante (A minor)
+3. Allegro assai (A major)</t>
   </si>
   <si>
     <t>Attribué à Johann Friedrich Bach</t>
@@ -115,9 +115,9 @@
     <t>H. 437</t>
   </si>
   <si>
-    <t>1. Allegro (la majeur)
-2. Largo mesto (la mineur)
-3. Allegro (la majeur)</t>
+    <t>1. Allegro (A major)
+2. Largo mesto (A minor)
+3. Allegro (A major)</t>
   </si>
   <si>
     <t>Aussi version pour flûte traversière et cordes (Wq 168/H 438);
@@ -130,9 +130,9 @@
     <t>H. 438</t>
   </si>
   <si>
-    <t>1. Allegro (la majeur)
-2. Largo mesto (la mineur)
-3. Allegro (mi majeur)</t>
+    <t>1. Allegro (A major)
+2. Largo mesto (A minor)
+3. Allegro (E major)</t>
   </si>
   <si>
     <t>Transverse Flute, 2 Violins, Viola, Basso</t>
@@ -164,9 +164,9 @@
     <t>A minor</t>
   </si>
   <si>
-    <t>1. Allegretto (la mineur)
-2. Andante (fa majeur)
-3. Presto (la mineur)</t>
+    <t>1. Allegretto (A minor)
+2. Andante (F major)
+3. Presto (A minor)</t>
   </si>
   <si>
     <t>revised in 1744</t>
@@ -178,9 +178,9 @@
     <t>H. 424</t>
   </si>
   <si>
-    <t>1. Allegro (la mineur)
-2. Adagio (fa majeur)
-3. Allegro con spirito (la mineur)</t>
+    <t>1. Allegro (A minor)
+2. Adagio (F major)
+3. Allegro con spirito (A minor)</t>
   </si>
   <si>
     <t>Wq. 26</t>
@@ -189,9 +189,9 @@
     <t>H. 430</t>
   </si>
   <si>
-    <t>1. Allegro assai (la mineur)
-2. Andante (do majeur)
-3. Allegro assai (la mineur)</t>
+    <t>1. Allegro assai (A minor)
+2. Andante (C major)
+3. Allegro assai (A minor)</t>
   </si>
   <si>
     <t>Aussi version pour flûte traversière et cordes (Wq 166/H 431);
@@ -228,9 +228,9 @@
     <t>B minor</t>
   </si>
   <si>
-    <t>1. Allegro di molto (si mineur)
-2. Adagio (sol majeur)
-3. Allegro (si mineur)</t>
+    <t>1. Allegro di molto (B minor)
+2. Adagio (G major)
+3. Allegro (B minor)</t>
   </si>
   <si>
     <t>Wq. 10</t>
@@ -242,9 +242,9 @@
     <t>B-flat major</t>
   </si>
   <si>
-    <t>1. ... (si bémol majeur)
-2. Largo (fa majeur)
-3. Presto, ma non tanto (si bémol majeur)</t>
+    <t>1. ... (B-flat major)
+2. Largo (F major)
+3. Presto, ma non tanto (B-flat major)</t>
   </si>
   <si>
     <t>Wq. 25</t>
@@ -253,9 +253,9 @@
     <t>H. 429</t>
   </si>
   <si>
-    <t>1. Allegro di molto (si bémol majeur)
-2. Largo mesto (ré mineur)
-3. Prestissimo (si bémol majeur)</t>
+    <t>1. Allegro di molto (B-flat major)
+2. Largo mesto (D minor)
+3. Prestissimo (B-flat major)</t>
   </si>
   <si>
     <t>Aussi arrangé pour 2 clavecins</t>
@@ -267,9 +267,9 @@
     <t>H. 434</t>
   </si>
   <si>
-    <t>1. Allegretto (si bémol majeur)
-2. Adagio (sol mineur)
-3. Allegro assai (si bémol majeur)</t>
+    <t>1. Allegretto (B-flat major)
+2. Adagio (G minor)
+3. Allegro assai (B-flat major)</t>
   </si>
   <si>
     <t>Aussi version pour flûte traversière et cordes (Wq 167/H 435);
@@ -302,9 +302,9 @@
     <t>H. 447</t>
   </si>
   <si>
-    <t>1. Allegro (si bémol majeur)
-2. Poco Adagio (mi bémol majeur)
-3. Allegro assai (si bémol majeur)</t>
+    <t>1. Allegro (B-flat major)
+2. Poco Adagio (E-flat major)
+3. Allegro assai (B-flat major)</t>
   </si>
   <si>
     <t>Wq. 39</t>
@@ -313,9 +313,9 @@
     <t>H. 465</t>
   </si>
   <si>
-    <t>1. Allegretto (si bémol majeur)
-2. Largo e mesto (sol mineur)
-3. Allegro moderato (si bémol majeur)</t>
+    <t>1. Allegretto (B-flat major)
+2. Largo e mesto (G minor)
+3. Allegro moderato (B-flat major)</t>
   </si>
   <si>
     <t>2 Solo Violins, Viola, Basso</t>
@@ -345,9 +345,9 @@
     <t>C major</t>
   </si>
   <si>
-    <t>1. Allegretto (do majeur)
-2. Adagio ma non troppo (do mineur)
-3. Allegro assai (do majeur)</t>
+    <t>1. Allegretto (C major)
+2. Adagio ma non troppo (C minor)
+3. Allegro assai (C major)</t>
   </si>
   <si>
     <t>Wq. 112/1</t>
@@ -365,9 +365,9 @@
     <t>H. 476</t>
   </si>
   <si>
-    <t>1. Allegro di molto (do majeur)
-2. Larghetto (ré mineur)
-3. Allegro (do majeur)</t>
+    <t>1. Allegro di molto (C major)
+2. Larghetto (D minor)
+3. Allegro (C major)</t>
   </si>
   <si>
     <t>2 Flutes, 2 Horns, 2 Violins, Viola, Basso</t>
@@ -382,9 +382,9 @@
     <t>C minor</t>
   </si>
   <si>
-    <t>1. Moderato (do mineur)
-2. Adagio non molto (mi bémol majeur)
-3. Vivace (do mineur)</t>
+    <t>1. Moderato (C minor)
+2. Adagio non molto (E-flat major)
+3. Vivace (C minor)</t>
   </si>
   <si>
     <t>revised in 1762</t>
@@ -396,9 +396,9 @@
     <t>H. 441</t>
   </si>
   <si>
-    <t>1. Allegro di molto (do mineur)
-2. Adagio (la bémol majeur)
-3. Allegretto (do mineur)</t>
+    <t>1. Allegro di molto (C minor)
+2. Adagio (A-flat major)
+3. Allegretto (C minor)</t>
   </si>
   <si>
     <t>Wq. 37</t>
@@ -407,9 +407,9 @@
     <t>H. 448</t>
   </si>
   <si>
-    <t>1. Allegro assai (do mineur)
-2. Andante ed arioso (do majeur)
-3. Presto (do mineur)</t>
+    <t>1. Allegro assai (C minor)
+2. Andante ed arioso (C major)
+3. Presto (C minor)</t>
   </si>
   <si>
     <t>Harpsichord, 2 Horns, 2 Violins, Viola, Basso</t>
@@ -421,10 +421,10 @@
     <t>H. 474</t>
   </si>
   <si>
-    <t>1. Allegro assai (do mineur)
-2. Poco Adagio (sol mineur)
-3. Tempo di Minuetto (mi bémol majeur)
-4. Allegro assai (do mineur)</t>
+    <t>1. Allegro assai (C minor)
+2. Poco Adagio (G minor)
+3. Tempo di Minuetto (E-flat major)
+4. Allegro assai (C minor)</t>
   </si>
   <si>
     <t>Harpsichord, 2 Flutes adlib, 2 Violins, Viola, Basso</t>
@@ -442,9 +442,9 @@
     <t>D major</t>
   </si>
   <si>
-    <t>1. Allegro di molto (ré majeur)
-2. Adagio non molto (ré mineur)
-3. Allegro (ré majeur)</t>
+    <t>1. Allegro di molto (D major)
+2. Adagio non molto (D minor)
+3. Allegro (D major)</t>
   </si>
   <si>
     <t>Aussi version avec ajout de 2 trompettes et timbales ad lib</t>
@@ -456,9 +456,9 @@
     <t>H. 416</t>
   </si>
   <si>
-    <t>1. Allegro (ré majeur)
-2. Un poco Andante (si mineur)
-3. Allegro assai (ré majeur)</t>
+    <t>1. Allegro (D major)
+2. Un poco Andante (B minor)
+3. Allegro assai (D major)</t>
   </si>
   <si>
     <t>? Version pour flûte concertante</t>
@@ -470,9 +470,9 @@
     <t>H. 421</t>
   </si>
   <si>
-    <t>1. Allegro (ré majeur)
-2. Andante (sol majeur)
-3. Allegro di molto (ré majeur)</t>
+    <t>1. Allegro (D major)
+2. Andante (G major)
+3. Allegro di molto (D major)</t>
   </si>
   <si>
     <t>Wq. 27</t>
@@ -481,9 +481,9 @@
     <t>H. 433</t>
   </si>
   <si>
-    <t>1. Allegro (ré majeur)
-2. Siciliana (si mineur)
-3. Allegro (ré majeur)</t>
+    <t>1. Allegro (D major)
+2. Siciliana (B minor)
+3. Allegro (D major)</t>
   </si>
   <si>
     <t>1ère version: 2 hautbois, 2 trompettes/cors, 2 flûtes ad lib et timpani;
@@ -496,9 +496,9 @@
     <t>H. 472</t>
   </si>
   <si>
-    <t>1. Allegro di molto (ré majeur)
-2. Andante (sol majeur)
-3. Allegretto (ré majeur)</t>
+    <t>1. Allegro di molto (D major)
+2. Andante (G major)
+3. Allegretto (D major)</t>
   </si>
   <si>
     <t>Wq. 45</t>
@@ -507,9 +507,9 @@
     <t>H. 478</t>
   </si>
   <si>
-    <t>1. Allegretto (ré majeur)
-2. Andantino (ré mineur)
-3. Allegro (ré majeur)</t>
+    <t>1. Allegretto (D major)
+2. Andantino (D minor)
+3. Allegro (D major)</t>
   </si>
   <si>
     <t>Wq. 17</t>
@@ -521,9 +521,9 @@
     <t>D minor</t>
   </si>
   <si>
-    <t>1. Allegro (ré mineur)
-2. Un poco Adagio (si bémol majeur)
-3. Allegro (ré mineur)</t>
+    <t>1. Allegro (D minor)
+2. Un poco Adagio (B-flat major)
+3. Allegro (D minor)</t>
   </si>
   <si>
     <t>Wq. 22</t>
@@ -532,9 +532,9 @@
     <t>H. 425</t>
   </si>
   <si>
-    <t>1. Allegro (ré mineur)
-2. Un poco Andante (ré majeur)
-3. Allegro di molto (ré mineur)</t>
+    <t>1. Allegro (D minor)
+2. Un poco Andante (D major)
+3. Allegro di molto (D minor)</t>
   </si>
   <si>
     <t>Wq. 23</t>
@@ -543,9 +543,9 @@
     <t>H. 427</t>
   </si>
   <si>
-    <t>1. Allegro (ré mineur)
-2. Poco Andante (fa majeur)
-3. Allegro assai (ré mineur)</t>
+    <t>1. Allegro (D minor)
+2. Poco Andante (F major)
+3. Allegro assai (D minor)</t>
   </si>
   <si>
     <t>Wq. 14</t>
@@ -557,9 +557,9 @@
     <t>E major</t>
   </si>
   <si>
-    <t>1. Allegro (mi majeur)
-2. Poco Adagio (mi mineur)
-3. Allegro assai (mi majeur)</t>
+    <t>1. Allegro (E major)
+2. Poco Adagio (E minor)
+3. Allegro assai (E major)</t>
   </si>
   <si>
     <t>Wq. 15</t>
@@ -571,9 +571,9 @@
     <t>E minor</t>
   </si>
   <si>
-    <t>1. Allegro (mi mineur)
-2. Adagio (sol majeur)
-3. Vivace (mi mineur)</t>
+    <t>1. Allegro (E minor)
+2. Adagio (G major)
+3. Vivace (E minor)</t>
   </si>
   <si>
     <t>Wq. 24</t>
@@ -582,9 +582,9 @@
     <t>H. 428</t>
   </si>
   <si>
-    <t>1. Allegretto (mi mineur)
-2. Largo (do majeur)
-3. Allegretto (mi mineur)</t>
+    <t>1. Allegretto (E minor)
+2. Largo (C major)
+3. Allegretto (E minor)</t>
   </si>
   <si>
     <t>? Révision d'une version antérieure</t>
@@ -593,9 +593,9 @@
     <t>Wq. 481.5</t>
   </si>
   <si>
-    <t>1. Allegretto (mi mineur)
-2. Adagio (si mineur)
-3. Presto (mi mineur)</t>
+    <t>1. Allegretto (E minor)
+2. Adagio (B minor)
+3. Presto (E minor)</t>
   </si>
   <si>
     <t>Possiblement authentique</t>
@@ -610,9 +610,9 @@
     <t>E-flat major</t>
   </si>
   <si>
-    <t>1. Allegro non molto (mi bémol majeur)
-2. Largo (do mineur)
-3. Allegro assai (mi bémol majeur)</t>
+    <t>1. Allegro non molto (E-flat major)
+2. Largo (C minor)
+3. Allegro assai (E-flat major)</t>
   </si>
   <si>
     <t>revised in 1743</t>
@@ -624,9 +624,9 @@
     <t>H. 446</t>
   </si>
   <si>
-    <t>1. Allegro ma non troppo (mi bémol majeur)
-2. Adagio sostenuto (la bémol majeur)
-3. Allegro assai (mi bémol majeur)</t>
+    <t>1. Allegro ma non troppo (E-flat major)
+2. Adagio sostenuto (A-flat major)
+3. Allegro assai (E-flat major)</t>
   </si>
   <si>
     <t>Organ/Harpsicord, 2 Horns, 2 Violins, Viola, Basso</t>
@@ -641,9 +641,9 @@
     <t>H. 467</t>
   </si>
   <si>
-    <t>1. Allegro (mi bémol majeur)
-2. Adagio ma non troppo (do mineur)
-3. Allegro ma non troppo (mi bémol majeur)</t>
+    <t>1. Allegro (E-flat major)
+2. Adagio ma non troppo (C minor)
+3. Allegro ma non troppo (E-flat major)</t>
   </si>
   <si>
     <t>Aussi version pour hautbois et cordes (Wq 165/H 468)</t>
@@ -664,9 +664,9 @@
     <t>H. 469</t>
   </si>
   <si>
-    <t>1. Largo (mi bémol majeur) / Prestissimo
-2. Largo (do majeur)
-3. Ziemlich geschwinde (mi bémol majeur)</t>
+    <t>1. Largo (E-flat major) / Prestissimo
+2. Largo (C major)
+3. Ziemlich geschwinde (E-flat major)</t>
   </si>
   <si>
     <t>Harpsichord, 2 Flutes, 2 Horns, 2 Violins, Viola, Basso</t>
@@ -678,9 +678,9 @@
     <t>H. 473</t>
   </si>
   <si>
-    <t>1. Allegro (mi bémol majeur)
-2. Larghetto (do majeur)
-3. Presto (mi bémol majeur)</t>
+    <t>1. Allegro (E-flat major)
+2. Larghetto (C major)
+3. Presto (E-flat major)</t>
   </si>
   <si>
     <t>Wq. 47</t>
@@ -692,9 +692,9 @@
     <t>Concerto doppio</t>
   </si>
   <si>
-    <t>1. Allegro di molto (mi bémol majeur)
-2. Larghetto (do majeur)
-3. Presto (mi bémol majeur)</t>
+    <t>1. Allegro di molto (E-flat major)
+2. Larghetto (C major)
+3. Presto (E-flat major)</t>
   </si>
   <si>
     <t>Harpsichord, Pianoforte, 2 Flutes, 2 Horns, 2 Violins, Viola, Basso</t>
@@ -712,9 +712,9 @@
     <t>F major</t>
   </si>
   <si>
-    <t>1. Allegro (fa majeur)
-2. Largo (fa mineur)
-3. Allegro assai (fa majeur)</t>
+    <t>1. Allegro (F major)
+2. Largo (F minor)
+3. Allegro assai (F major)</t>
   </si>
   <si>
     <t>2 Harpsichords, 2 Horns, 2 Violins, Viola, Basso</t>
@@ -729,9 +729,9 @@
     <t>H. 415</t>
   </si>
   <si>
-    <t>1. Allegro (fa majeur)
-2. Largo e sostenuto (fa mineur)
-3. Allegro assai (fa majeur)</t>
+    <t>1. Allegro (F major)
+2. Largo e sostenuto (F minor)
+3. Allegro assai (F major)</t>
   </si>
   <si>
     <t>Wq. 33</t>
@@ -740,9 +740,9 @@
     <t>H. 443</t>
   </si>
   <si>
-    <t>1. Allegretto (fa majeur)
-2. Adagio (si bémol majeur)
-3. Allegro assai (fa majeur)</t>
+    <t>1. Allegretto (F major)
+2. Adagio (B-flat major)
+3. Allegro assai (F major)</t>
   </si>
   <si>
     <t>Wq. 38</t>
@@ -751,9 +751,9 @@
     <t>H. 454</t>
   </si>
   <si>
-    <t>1. Allegro di molto (fa majeur)
-2. Poco Adagio (ré mineur)
-3. Allegro (fa majeur)</t>
+    <t>1. Allegro di molto (F major)
+2. Poco Adagio (D minor)
+3. Allegro (F major)</t>
   </si>
   <si>
     <t>Wq. 42</t>
@@ -762,9 +762,9 @@
     <t>H. 470</t>
   </si>
   <si>
-    <t>1. Allegro assai (fa majeur)
-2. Larghetto (do mineur)
-3. Poco Presto (fa majeur)</t>
+    <t>1. Allegro assai (F major)
+2. Larghetto (C minor)
+3. Poco Presto (F major)</t>
   </si>
   <si>
     <t>Wq. 43/1</t>
@@ -773,9 +773,9 @@
     <t>H. 471</t>
   </si>
   <si>
-    <t>1. Allegro di molto (fa majeur)
-2. Andante (fa mineur)
-3. Prestissimo (fa majeur)</t>
+    <t>1. Allegro di molto (F major)
+2. Andante (F minor)
+3. Prestissimo (F major)</t>
   </si>
   <si>
     <t>Wq. 3</t>
@@ -787,9 +787,9 @@
     <t>G major</t>
   </si>
   <si>
-    <t>1. Allegro di molto (sol majeur)
-2. Adagio (sol mineur)
-3. Allegro (sol majeur)</t>
+    <t>1. Allegro di molto (G major)
+2. Adagio (G minor)
+3. Allegro (G major)</t>
   </si>
   <si>
     <t>revised in 1745</t>
@@ -801,9 +801,9 @@
     <t>H. 406</t>
   </si>
   <si>
-    <t>1. Allegro (sol majeur)
-2. Adagio (sol mineur)
-3. Allegro (sol majeur)</t>
+    <t>1. Allegro (G major)
+2. Adagio (G minor)
+3. Allegro (G major)</t>
   </si>
   <si>
     <t>Wq. 9</t>
@@ -812,9 +812,9 @@
     <t>H. 412</t>
   </si>
   <si>
-    <t>1. Allegro (sol majeur)
-2. Adagio (si mineur)
-3. Allegro assai (sol majeur)</t>
+    <t>1. Allegro (G major)
+2. Adagio (B minor)
+3. Allegro assai (G major)</t>
   </si>
   <si>
     <t>Aussi arrangé pour orgue et violon</t>
@@ -826,9 +826,9 @@
     <t>H. 419</t>
   </si>
   <si>
-    <t>1. Allegro (sol majeur)
-2. Adagio (do majeur)
-3. Allegretto (sol majeur)</t>
+    <t>1. Allegro (G major)
+2. Adagio (C major)
+3. Allegretto (G major)</t>
   </si>
   <si>
     <t>? Révision d'une version datant de 1738</t>
@@ -840,9 +840,9 @@
     <t>H. 444</t>
   </si>
   <si>
-    <t>1. Allegro di molto (sol majeur)
-2. Largo (mi mineur)
-3. Presto (sol majeur)</t>
+    <t>1. Allegro di molto (G major)
+2. Largo (E minor)
+3. Presto (G major)</t>
   </si>
   <si>
     <t>Aussi version pour flûte traversière et cordes (Wq 169/H 445)</t>
@@ -863,8 +863,8 @@
     <t>H. 475</t>
   </si>
   <si>
-    <t>1. Adagio (sol majeur) / Presto
-2. Allegro (do majeur)</t>
+    <t>1. Adagio (G major) / Presto
+2. Allegro (C major)</t>
   </si>
   <si>
     <t>Wq. 44</t>
@@ -873,9 +873,9 @@
     <t>H. 477</t>
   </si>
   <si>
-    <t>1. Allegretto (sol majeur)
-2. Andantino (si mineur)
-3. Allegro (sol majeur)</t>
+    <t>1. Allegretto (G major)
+2. Andantino (B minor)
+3. Allegro (G major)</t>
   </si>
   <si>
     <t>Wq. 6</t>
@@ -887,9 +887,9 @@
     <t>G minor</t>
   </si>
   <si>
-    <t>1. ... (sol mineur)
-2. Largo (mi bémol majeur)
-3. Allegro (sol mineur)</t>
+    <t>1. ... (G minor)
+2. Largo (E-flat major)
+3. Allegro (G minor)</t>
   </si>
   <si>
     <t>Wq. 32</t>
@@ -898,9 +898,9 @@
     <t>H. 442</t>
   </si>
   <si>
-    <t>1. Allegretto (sol mineur)
-2. Un poco Andante (sol majeur)
-3. Allegro (sol mineur)</t>
+    <t>1. Allegretto (G minor)
+2. Un poco Andante (G major)
+3. Allegro (G minor)</t>
   </si>
   <si>
     <t>Autre version avec 2 violons, alto et basse</t>
@@ -909,9 +909,9 @@
     <t>Wq. 481</t>
   </si>
   <si>
-    <t>1. Allegro (sol mineur)
-2. Largo (si bémol majeur)
-3. Presto di molto (sol mineur)</t>
+    <t>1. Allegro (G minor)
+2. Largo (B-flat major)
+3. Presto di molto (G minor)</t>
   </si>
   <si>
     <t>Wq. 43</t>
@@ -2000,7 +2000,7 @@
     <t>H. 102</t>
   </si>
   <si>
-    <t>Fugue à 4 avec Anmerkungen, en fa mineur, pour orgue</t>
+    <t>Fugue à 4 avec Anmerkungen, en F minor, pour orgue</t>
   </si>
   <si>
     <t>F minor</t>
@@ -2840,9 +2840,9 @@
     <t>H. 601</t>
   </si>
   <si>
-    <t>1. … (do majeur)
-2. … (do majeur)
-3. ... (do majeur)
+    <t>1. … (C major)
+2. … (C major)
+3. ... (C major)
 reprise du premier Menuet.</t>
   </si>
   <si>
@@ -2942,9 +2942,9 @@
     <t>H. 638</t>
   </si>
   <si>
-    <t>1. Erste Menuet (ré majeur)
-2. Zweyte Menuet (ré mineur)
-3. Erste Menuet (ré majeur)
+    <t>1. Erste Menuet (D major)
+2. Zweyte Menuet (D minor)
+3. Erste Menuet (D major)
 reprise du premier Menuet.</t>
   </si>
   <si>
@@ -3005,9 +3005,9 @@
     <t>H. 622</t>
   </si>
   <si>
-    <t>1. Menuet (sol majeur)
-2. Trio (sol mineur)
-3. Menuet (sol majeur)
+    <t>1. Menuet (G major)
+2. Trio (G minor)
+3. Menuet (G major)
 reprise du Menuet.</t>
   </si>
   <si>
@@ -3801,9 +3801,9 @@
     <t>H. 558</t>
   </si>
   <si>
-    <t>1. Andante (do majeur)
-2. Allegretto (do majeur)
-3. Arioso (do majeur)</t>
+    <t>1. Andante (C major)
+2. Allegretto (C major)
+3. Arioso (C major)</t>
   </si>
   <si>
     <t>Viola da Gamba, Basso</t>
@@ -3815,9 +3815,9 @@
     <t>H. 559</t>
   </si>
   <si>
-    <t>1. Adagio ma non tanto (ré majeur)
-2. Allegro di molto (ré majeur)
-3. Arioso (ré majeur)</t>
+    <t>1. Adagio ma non tanto (D major)
+2. Allegro di molto (D major)
+3. Arioso (D major)</t>
   </si>
   <si>
     <t>Wq. 131</t>
@@ -3832,9 +3832,9 @@
     <t>H. 563</t>
   </si>
   <si>
-    <t>1. Adagio un poco (sol majeur)
-2. Allegro (sol majeur)
-3. Allegro (sol majeur)</t>
+    <t>1. Adagio un poco (G major)
+2. Allegro (G major)
+3. Allegro (G major)</t>
   </si>
   <si>
     <t>Wq. 135</t>
@@ -3843,9 +3843,9 @@
     <t>H. 549</t>
   </si>
   <si>
-    <t>1. Adagio (sol mineur)
-2. Allegro (sol mineur)
-3. Vivace (sol mineur)</t>
+    <t>1. Adagio (G minor)
+2. Allegro (G minor)
+3. Vivace (G minor)</t>
   </si>
   <si>
     <t>Oboe, Basso</t>
@@ -3857,7 +3857,7 @@
     <t>H. 557</t>
   </si>
   <si>
-    <t>1. … (sol mineur)</t>
+    <t>1. … (G minor)</t>
   </si>
   <si>
     <t>Cello, Basso</t>
@@ -3989,9 +3989,9 @@
     <t>H. 562</t>
   </si>
   <si>
-    <t>1. Poco Adagio (la mineur)
-2. Allegro (la mineur)
-3. Allegro (la mineur)</t>
+    <t>1. Poco Adagio (A minor)
+2. Allegro (A minor)
+3. Allegro (A minor)</t>
   </si>
   <si>
     <t>Transverse Flute</t>
@@ -4099,10 +4099,10 @@
     <t>H. 565/2</t>
   </si>
   <si>
-    <t>1. Largo (si mineur)
-2. Allegro (ré majeur)
-3. Adagio (ré majeur)
-4. Presto (ré majeur)</t>
+    <t>1. Largo (B minor)
+2. Allegro (D major)
+3. Adagio (D major)
+4. Presto (D major)</t>
   </si>
   <si>
     <t>Wq. 53/4</t>
@@ -4267,11 +4267,11 @@
     <t>H. 564.5</t>
   </si>
   <si>
-    <t>1. Andante (do majeur)
-2. Allegro (do majeur)
-3. Menuetto I (do majeur)
-4. Adagio (la mineur)
-5. Menuetto II (do majeur)</t>
+    <t>1. Andante (C major)
+2. Allegro (C major)
+3. Menuetto I (C major)
+4. Adagio (A minor)
+5. Menuetto II (C major)</t>
   </si>
   <si>
     <t>[arrangement de la sonate pour flûte solo, BWV 1033, de J.S. Bach]
@@ -4593,11 +4593,11 @@
     <t>H. 569</t>
   </si>
   <si>
-    <t>1. Allegretto (ré mineur)
+    <t>1. Allegretto (D minor)
 [variante du 2e mouvement de BWV 1036]
-2. Largo (fa majeur)
+2. Largo (F major)
 [variante du 3e mouvement de BWV 1036]
-3. Allegro (ré mineur)</t>
+3. Allegro (D minor)</t>
   </si>
   <si>
     <t>Wq. 65/3</t>
@@ -5125,7 +5125,7 @@
     <t>H. 581</t>
   </si>
   <si>
-    <t>Trio, en sol majeur, pour flûte, violon et basse</t>
+    <t>Trio, en G major, pour flûte, violon et basse</t>
   </si>
   <si>
     <t>Wq. 157</t>
@@ -5167,9 +5167,9 @@
     <t>H. 565/1</t>
   </si>
   <si>
-    <t>1. Affetuoso (sol majeur)
-2. Allegro (sol majeur)
-3. Tempo di Menuet (sol majeur)</t>
+    <t>1. Affetuoso (G major)
+2. Allegro (G major)
+3. Tempo di Menuet (G major)</t>
   </si>
   <si>
     <t>Wq. 55/6</t>
@@ -5751,7 +5751,7 @@
     <t>H. 194</t>
   </si>
   <si>
-    <t>Arioso, en la mineur, pour clavier</t>
+    <t>Arioso, en A minor, pour clavier</t>
   </si>
   <si>
     <t>Wq. 82/6</t>
@@ -5766,7 +5766,7 @@
     <t>H. 635/7</t>
   </si>
   <si>
-    <t>Presto, en la mineur, pour harpe</t>
+    <t>Presto, en A minor, pour harpe</t>
   </si>
   <si>
     <t>Wq. 81/4</t>
@@ -5793,7 +5793,7 @@
     <t>H. 635/30</t>
   </si>
   <si>
-    <t>Presto, en si bémol majeur, pour horloge mécanique</t>
+    <t>Presto, en B-flat major, pour horloge mécanique</t>
   </si>
   <si>
     <t>Mechanical Clock</t>
@@ -6018,7 +6018,7 @@
     <t>H. 635/28</t>
   </si>
   <si>
-    <t>Adagio, en sol mineur, pour orgue positif</t>
+    <t>Adagio, en G minor, pour orgue positif</t>
   </si>
   <si>
     <t>Wq. 211</t>
@@ -6695,59 +6695,59 @@
     <t>30 Morceaux divers</t>
   </si>
   <si>
-    <t>1. Allegro, en do majeur
-2. Allegro, en ré majeur
+    <t>1. Allegro, en C major
+2. Allegro, en D major
 [Variante de Wq 116/25, H 251; Wq 92/6, H 521; et Wq 115/1, H 610]
-3. Allegro, en ré majeur
-4. Polacca, en mi bémol majeur
-5. Allegro di molto, en la majeur, pour harpe
+3. Allegro, en D major
+4. Polacca, en E-flat major
+5. Allegro di molto, en A major, pour harpe
 [Variante de Wq 116/36, H 310]
-6. Allegro, en mi majeur, pour harpe
+6. Allegro, en E major, pour harpe
 [Variante de Wq 116/37, H 311]
-7. Presto, en la mineur, pour harpe
+7. Presto, en A minor, pour harpe
 [Variante de Wq 116/39, H 313]
-8. Allegro, en si bémol majeur, pour harpe
+8. Allegro, en B-flat major, pour harpe
 [Variante de Wq 116/38, H 312]
-9. Minuetto I, en sol mineur, pour harpe
+9. Minuetto I, en G minor, pour harpe
 [Variante de Wq 116/31, H 305 et Wq 189/5, H 624]
 répété après le Menuetto II]
-10. Minuetto II, en sol mineur, pour harpe
-11. Minuetto III, en ré majeur
+10. Minuetto II, en G minor, pour harpe
+11. Minuetto III, en D major
 [Variante de Wq 116/40, H 314]
-12. Minuetto IV, en fa majeur
+12. Minuetto IV, en F major
 [Variante de H 258; Wq 116/32, H 306; et Wq 189/6, H 625]
-13. Polonoise I, en fa majeur
+13. Polonoise I, en F major
 [Variante de Wq 116/41, H 315]
-14. Polonoise II, en la majeur,
+14. Polonoise II, en A major,
 [Variante de Wq 116/42, H 316]
-15. Polonoise III, en si bémol majeur
+15. Polonoise III, en B-flat major
 [Variante de Wq 116/43, H 317]
-16. Polonoise IV, en mi bémol majeur
+16. Polonoise IV, en E-flat major
 [Variante Wq 116/44, H 318]
-17. Marche I, en sol majeur
+17. Marche I, en G major
 [Variante de Wq 116/45, H 319; Wq 187/1, H 637/1)
-18. Marche II, en ré majeur
+18. Marche II, en D major
 [Variante de Wq 116/46, H 320; Wq 187/2, H 637/2]
-19. Minuetto I, en do majeur, pour flûte et harpe
+19. Minuetto I, en C major, pour flûte et harpe
 [Variante de Wq 116/47, H 321]
-20. Minuetto II, en sol majeur, pour flûte et harpe
+20. Minuetto II, en G major, pour flûte et harpe
 [Variante de Wq 116/48, H 322]
-21. Polonoise, en ré majeur, pour flûte et harpe
+21. Polonoise, en D major, pour flûte et harpe
 [Variante de Wq 116/49, H 323]
-22. Minuetto, en do majeur, pour 2 flûtes
-23. Allegro, en ré majeur, pour 2 flûtes
-24. Allegretto, en ré majeur, pour 2 flûtes
+22. Minuetto, en C major, pour 2 flûtes
+23. Allegro, en D major, pour 2 flûtes
+24. Allegretto, en D major, pour 2 flûtes
 [Variante de H 257]
-25. Polonoise, en sol majeur, pour 2 flûtes
-26. Adagio e sostenuto, en do majeur, pour 2 clarinettes
+25. Polonoise, en G major, pour 2 flûtes
+26. Adagio e sostenuto, en C major, pour 2 clarinettes
 [Variante du 1er mouvement de Wq 142, H 636]
-27. Allegro, en do majeur, pour 2 clarinettes
+27. Allegro, en C major, pour 2 clarinettes
 [Variante de H 636/2]
-28. Adagio, en sol mineur, pour orgue positif
+28. Adagio, en G minor, pour orgue positif
 Variante de Wq 115/3, H 612; Wq 116/50, H 324; et Wq 186/1, H H 620/1]
-29. Allegro, en do majeur, pour orgue positif
+29. Allegro, en C major, pour orgue positif
 [Variante de Wq 116/51, H 325]
-30. Presto, en si bémol majeur, pour horloge mécanique
+30. Presto, en B-flat major, pour horloge mécanique
 [Variante du 3e mouvement de Wq 53/1, H 162]</t>
   </si>
   <si>
@@ -9683,7 +9683,7 @@
     <col min="4" max="4" width="25.018018018018" style="4" customWidth="1"/>
     <col min="5" max="5" width="13.5315315315315" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.6126126126126" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.3783783783784" style="5" customWidth="1"/>
+    <col min="7" max="7" width="63.4684684684685" style="5" customWidth="1"/>
     <col min="8" max="8" width="22.7657657657658" style="5" customWidth="1"/>
     <col min="9" max="9" width="30.4594594594595" style="5" customWidth="1"/>
     <col min="10" max="16384" width="8.61261261261261" style="2"/>
@@ -9774,7 +9774,6 @@
       <c r="C4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4"/>
       <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
@@ -9801,7 +9800,6 @@
       <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="4"/>
       <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
@@ -9828,7 +9826,6 @@
       <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="4"/>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
@@ -9855,7 +9852,6 @@
       <c r="C7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="4"/>
       <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
@@ -9882,7 +9878,6 @@
       <c r="C8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="4"/>
       <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
@@ -9984,7 +9979,6 @@
       <c r="C12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="4"/>
       <c r="E12" s="2" t="s">
         <v>11</v>
       </c>
@@ -10011,7 +10005,6 @@
       <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="4"/>
       <c r="E13" s="2" t="s">
         <v>11</v>
       </c>
@@ -10035,7 +10028,6 @@
       <c r="C14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="4"/>
       <c r="E14" s="2" t="s">
         <v>11</v>
       </c>
@@ -10085,7 +10077,6 @@
       <c r="C16" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="4"/>
       <c r="E16" s="2" t="s">
         <v>11</v>
       </c>
@@ -10112,7 +10103,6 @@
       <c r="C17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="4"/>
       <c r="E17" s="2" t="s">
         <v>11</v>
       </c>
@@ -10139,7 +10129,6 @@
       <c r="C18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="4"/>
       <c r="E18" s="2" t="s">
         <v>11</v>
       </c>
@@ -10166,7 +10155,6 @@
       <c r="C19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="4"/>
       <c r="E19" s="2" t="s">
         <v>11</v>
       </c>
@@ -10190,7 +10178,6 @@
       <c r="C20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="4"/>
       <c r="E20" s="2" t="s">
         <v>11</v>
       </c>
@@ -10243,7 +10230,6 @@
       <c r="C22" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="4"/>
       <c r="E22" s="2" t="s">
         <v>11</v>
       </c>
@@ -10287,7 +10273,6 @@
       <c r="C24" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="4"/>
       <c r="E24" s="2" t="s">
         <v>11</v>
       </c>
@@ -10311,7 +10296,6 @@
       <c r="C25" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="4"/>
       <c r="E25" s="2" t="s">
         <v>11</v>
       </c>
@@ -10338,7 +10322,6 @@
       <c r="C26" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="4"/>
       <c r="E26" s="2" t="s">
         <v>11</v>
       </c>
@@ -10362,7 +10345,6 @@
       <c r="C27" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="4"/>
       <c r="E27" s="2" t="s">
         <v>11</v>
       </c>
@@ -10386,7 +10368,6 @@
       <c r="C28" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="4"/>
       <c r="E28" s="2" t="s">
         <v>11</v>
       </c>
@@ -10413,7 +10394,6 @@
       <c r="C29" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D29" s="4"/>
       <c r="E29" s="2" t="s">
         <v>11</v>
       </c>
@@ -10440,7 +10420,6 @@
       <c r="C30" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="4"/>
       <c r="E30" s="2" t="s">
         <v>11</v>
       </c>
@@ -10467,7 +10446,6 @@
       <c r="C31" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="4"/>
       <c r="E31" s="2" t="s">
         <v>11</v>
       </c>
@@ -10494,7 +10472,6 @@
       <c r="C32" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="4"/>
       <c r="E32" s="2" t="s">
         <v>11</v>
       </c>
@@ -10521,7 +10498,6 @@
       <c r="C33" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="4"/>
       <c r="E33" s="2" t="s">
         <v>11</v>
       </c>
@@ -10594,7 +10570,6 @@
       <c r="C36" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="4"/>
       <c r="E36" s="2" t="s">
         <v>11</v>
       </c>
@@ -10618,7 +10593,6 @@
       <c r="C37" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D37" s="4"/>
       <c r="E37" s="2" t="s">
         <v>11</v>
       </c>
@@ -10668,7 +10642,6 @@
       <c r="C39" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D39" s="4"/>
       <c r="E39" s="2" t="s">
         <v>11</v>
       </c>
@@ -10692,7 +10665,6 @@
       <c r="C40" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D40" s="4"/>
       <c r="E40" s="2" t="s">
         <v>11</v>
       </c>
@@ -10713,8 +10685,6 @@
       <c r="B41" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="4"/>
       <c r="E41" s="2" t="s">
         <v>11</v>
       </c>
@@ -10739,7 +10709,6 @@
       <c r="C42" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="4"/>
       <c r="E42" s="2" t="s">
         <v>11</v>
       </c>
@@ -10766,7 +10735,6 @@
       <c r="C43" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D43" s="4"/>
       <c r="E43" s="2" t="s">
         <v>11</v>
       </c>
@@ -10868,7 +10836,6 @@
       <c r="C47" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D47" s="4"/>
       <c r="E47" s="2" t="s">
         <v>11</v>
       </c>
@@ -10999,7 +10966,6 @@
       <c r="C52" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D52" s="4"/>
       <c r="E52" s="2" t="s">
         <v>11</v>
       </c>
@@ -11046,7 +11012,6 @@
       <c r="C54" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D54" s="4"/>
       <c r="E54" s="2" t="s">
         <v>11</v>
       </c>
@@ -11070,7 +11035,6 @@
       <c r="C55" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D55" s="4"/>
       <c r="E55" s="2" t="s">
         <v>11</v>
       </c>
@@ -11097,7 +11061,6 @@
       <c r="C56" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D56" s="4"/>
       <c r="E56" s="2" t="s">
         <v>11</v>
       </c>
@@ -11121,7 +11084,6 @@
       <c r="C57" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D57" s="4"/>
       <c r="E57" s="2" t="s">
         <v>11</v>
       </c>
@@ -11148,7 +11110,6 @@
       <c r="C58" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D58" s="4"/>
       <c r="E58" s="2" t="s">
         <v>11</v>
       </c>
@@ -11175,7 +11136,6 @@
       <c r="C59" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D59" s="4"/>
       <c r="E59" s="2" t="s">
         <v>11</v>
       </c>
@@ -11202,7 +11162,6 @@
       <c r="C60" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D60" s="4"/>
       <c r="E60" s="2" t="s">
         <v>11</v>
       </c>
@@ -11229,7 +11188,6 @@
       <c r="C61" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D61" s="4"/>
       <c r="E61" s="2" t="s">
         <v>11</v>
       </c>
@@ -11256,7 +11214,6 @@
       <c r="C62" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D62" s="4"/>
       <c r="E62" s="2" t="s">
         <v>11</v>
       </c>
@@ -11280,7 +11237,6 @@
       <c r="C63" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D63" s="4"/>
       <c r="E63" s="2" t="s">
         <v>11</v>
       </c>
@@ -11304,7 +11260,6 @@
       <c r="C64" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D64" s="4"/>
       <c r="E64" s="2" t="s">
         <v>11</v>
       </c>
@@ -11325,8 +11280,6 @@
       <c r="B65" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="4"/>
       <c r="E65" s="2" t="s">
         <v>11</v>
       </c>
@@ -11348,15 +11301,12 @@
       <c r="B66" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C66" s="3"/>
       <c r="D66" s="4" t="s">
         <v>253</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F66" s="2"/>
-      <c r="G66" s="5"/>
       <c r="H66" s="5" t="s">
         <v>97</v>
       </c>
@@ -11365,14 +11315,12 @@
       <c r="B67" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C67" s="3"/>
       <c r="D67" s="4" t="s">
         <v>255</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F67" s="2"/>
       <c r="H67" s="2" t="s">
         <v>256</v>
       </c>
@@ -11439,7 +11387,6 @@
       <c r="F70" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G70" s="5"/>
       <c r="H70" s="5" t="s">
         <v>268</v>
       </c>
@@ -11486,7 +11433,6 @@
       <c r="F72" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G72" s="5"/>
       <c r="H72" s="5" t="s">
         <v>268</v>
       </c>
@@ -11556,7 +11502,6 @@
       <c r="F75" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G75" s="5"/>
       <c r="H75" s="5" t="s">
         <v>268</v>
       </c>
@@ -11623,7 +11568,6 @@
       <c r="F78" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G78" s="5"/>
       <c r="H78" s="5" t="s">
         <v>268</v>
       </c>
@@ -11647,7 +11591,6 @@
       <c r="F79" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G79" s="5"/>
       <c r="H79" s="5" t="s">
         <v>261</v>
       </c>
@@ -11671,7 +11614,6 @@
       <c r="F80" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G80" s="5"/>
       <c r="H80" s="5" t="s">
         <v>268</v>
       </c>
@@ -11695,7 +11637,6 @@
       <c r="F81" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G81" s="5"/>
       <c r="H81" s="5" t="s">
         <v>268</v>
       </c>
@@ -11765,7 +11706,6 @@
       <c r="F84" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G84" s="5"/>
       <c r="H84" s="5" t="s">
         <v>268</v>
       </c>
@@ -11789,7 +11729,6 @@
       <c r="F85" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G85" s="5"/>
       <c r="H85" s="5" t="s">
         <v>300</v>
       </c>
@@ -11813,7 +11752,6 @@
       <c r="F86" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G86" s="5"/>
       <c r="H86" s="5" t="s">
         <v>268</v>
       </c>
@@ -11860,7 +11798,6 @@
       <c r="F88" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G88" s="5"/>
       <c r="H88" s="5" t="s">
         <v>308</v>
       </c>
@@ -11884,7 +11821,6 @@
       <c r="F89" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G89" s="5"/>
       <c r="H89" s="5" t="s">
         <v>268</v>
       </c>
@@ -11925,7 +11861,6 @@
       <c r="F91" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G91" s="5"/>
       <c r="H91" s="5" t="s">
         <v>268</v>
       </c>
@@ -12035,7 +11970,6 @@
       <c r="F96" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G96" s="5"/>
       <c r="H96" s="5" t="s">
         <v>326</v>
       </c>
@@ -12079,7 +12013,6 @@
       <c r="F98" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G98" s="5"/>
       <c r="H98" s="5" t="s">
         <v>268</v>
       </c>
@@ -12103,7 +12036,6 @@
       <c r="F99" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G99" s="5"/>
       <c r="H99" s="5" t="s">
         <v>268</v>
       </c>
@@ -12127,7 +12059,6 @@
       <c r="F100" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G100" s="5"/>
       <c r="H100" s="5" t="s">
         <v>261</v>
       </c>
@@ -12151,7 +12082,6 @@
       <c r="F101" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G101" s="5"/>
       <c r="H101" s="5" t="s">
         <v>338</v>
       </c>
@@ -12221,7 +12151,6 @@
       <c r="F104" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G104" s="5"/>
       <c r="H104" s="5" t="s">
         <v>268</v>
       </c>
@@ -12233,14 +12162,12 @@
       <c r="B105" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="C105" s="3"/>
       <c r="D105" s="4" t="s">
         <v>345</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="F105" s="2"/>
       <c r="H105" s="5" t="s">
         <v>346</v>
       </c>
@@ -12261,7 +12188,6 @@
       <c r="F106" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G106" s="5"/>
       <c r="H106" s="5" t="s">
         <v>350</v>
       </c>
@@ -12276,14 +12202,12 @@
       <c r="C107" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="D107" s="4"/>
       <c r="E107" s="2" t="s">
         <v>349</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G107" s="5"/>
       <c r="H107" s="5" t="s">
         <v>350</v>
       </c>
@@ -12295,7 +12219,6 @@
       <c r="C108" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D108" s="4"/>
       <c r="E108" s="2" t="s">
         <v>349</v>
       </c>
@@ -12336,14 +12259,12 @@
       <c r="C110" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D110" s="4"/>
       <c r="E110" s="2" t="s">
         <v>349</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G110" s="5"/>
       <c r="H110" s="5" t="s">
         <v>361</v>
       </c>
@@ -12358,7 +12279,6 @@
       <c r="C111" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D111" s="4"/>
       <c r="E111" s="2" t="s">
         <v>349</v>
       </c>
@@ -12396,12 +12316,9 @@
       <c r="B113" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C113" s="3"/>
-      <c r="D113" s="4"/>
       <c r="E113" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F113" s="2"/>
       <c r="H113" s="5" t="s">
         <v>350</v>
       </c>
@@ -12422,7 +12339,6 @@
       <c r="F114" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G114" s="5"/>
       <c r="H114" s="5" t="s">
         <v>268</v>
       </c>
@@ -12443,7 +12359,6 @@
       <c r="F115" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G115" s="5"/>
       <c r="H115" s="5" t="s">
         <v>268</v>
       </c>
@@ -12518,7 +12433,6 @@
       <c r="C119" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="D119" s="4"/>
       <c r="E119" s="2" t="s">
         <v>369</v>
       </c>
@@ -12548,7 +12462,6 @@
       <c r="F120" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G120" s="5"/>
       <c r="H120" s="5" t="s">
         <v>268</v>
       </c>
@@ -12563,14 +12476,12 @@
       <c r="C121" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="D121" s="4"/>
       <c r="E121" s="2" t="s">
         <v>369</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G121" s="5"/>
       <c r="H121" s="5" t="s">
         <v>268</v>
       </c>
@@ -12625,7 +12536,6 @@
       <c r="C124" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="D124" s="4"/>
       <c r="E124" s="2" t="s">
         <v>369</v>
       </c>
@@ -12646,7 +12556,6 @@
       <c r="C125" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="D125" s="4"/>
       <c r="E125" s="2" t="s">
         <v>369</v>
       </c>
@@ -12667,7 +12576,6 @@
       <c r="C126" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D126" s="4"/>
       <c r="E126" s="2" t="s">
         <v>369</v>
       </c>
@@ -12688,7 +12596,6 @@
       <c r="C127" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D127" s="4"/>
       <c r="E127" s="2" t="s">
         <v>369</v>
       </c>
@@ -12709,14 +12616,12 @@
       <c r="C128" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D128" s="4"/>
       <c r="E128" s="2" t="s">
         <v>369</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G128" s="5"/>
       <c r="H128" s="5" t="s">
         <v>268</v>
       </c>
@@ -12731,7 +12636,6 @@
       <c r="C129" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="D129" s="4"/>
       <c r="E129" s="2" t="s">
         <v>369</v>
       </c>
@@ -12752,7 +12656,6 @@
       <c r="C130" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="D130" s="4"/>
       <c r="E130" s="2" t="s">
         <v>369</v>
       </c>
@@ -12773,7 +12676,6 @@
       <c r="C131" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="D131" s="4"/>
       <c r="E131" s="2" t="s">
         <v>369</v>
       </c>
@@ -12794,7 +12696,6 @@
       <c r="C132" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="D132" s="4"/>
       <c r="E132" s="2" t="s">
         <v>369</v>
       </c>
@@ -12815,7 +12716,6 @@
       <c r="C133" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="D133" s="4"/>
       <c r="E133" s="2" t="s">
         <v>369</v>
       </c>
@@ -12859,7 +12759,6 @@
       <c r="C135" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="D135" s="4"/>
       <c r="E135" s="2" t="s">
         <v>369</v>
       </c>
@@ -12880,7 +12779,6 @@
       <c r="C136" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="D136" s="4"/>
       <c r="E136" s="2" t="s">
         <v>369</v>
       </c>
@@ -12910,7 +12808,6 @@
       <c r="F137" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G137" s="5"/>
       <c r="H137" s="5" t="s">
         <v>268</v>
       </c>
@@ -12934,7 +12831,6 @@
       <c r="F138" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G138" s="5"/>
       <c r="H138" s="5" t="s">
         <v>268</v>
       </c>
@@ -12958,7 +12854,6 @@
       <c r="F139" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G139" s="5"/>
       <c r="H139" s="5" t="s">
         <v>268</v>
       </c>
@@ -12982,7 +12877,6 @@
       <c r="F140" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G140" s="5"/>
       <c r="H140" s="5" t="s">
         <v>268</v>
       </c>
@@ -13052,7 +12946,6 @@
       <c r="F143" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G143" s="5"/>
       <c r="H143" s="5" t="s">
         <v>268</v>
       </c>
@@ -13084,7 +12977,6 @@
       <c r="B145" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="C145" s="3"/>
       <c r="D145" s="4" t="s">
         <v>439</v>
       </c>
@@ -13111,7 +13003,6 @@
       <c r="F146" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G146" s="5"/>
       <c r="H146" s="5" t="s">
         <v>268</v>
       </c>
@@ -13204,7 +13095,6 @@
       <c r="F150" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G150" s="5"/>
       <c r="H150" s="5" t="s">
         <v>268</v>
       </c>
@@ -13251,7 +13141,6 @@
       <c r="F152" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G152" s="5"/>
       <c r="H152" s="5" t="s">
         <v>268</v>
       </c>
@@ -13275,7 +13164,6 @@
       <c r="F153" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G153" s="5"/>
       <c r="H153" s="5" t="s">
         <v>268</v>
       </c>
@@ -13299,7 +13187,6 @@
       <c r="F154" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G154" s="5"/>
       <c r="H154" s="5" t="s">
         <v>268</v>
       </c>
@@ -13323,7 +13210,6 @@
       <c r="F155" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G155" s="5"/>
       <c r="H155" s="5" t="s">
         <v>268</v>
       </c>
@@ -13347,7 +13233,6 @@
       <c r="F156" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G156" s="5"/>
       <c r="H156" s="5" t="s">
         <v>268</v>
       </c>
@@ -13371,7 +13256,6 @@
       <c r="F157" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G157" s="5"/>
       <c r="H157" s="5" t="s">
         <v>268</v>
       </c>
@@ -13533,7 +13417,6 @@
       <c r="F164" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G164" s="5"/>
       <c r="H164" s="5" t="s">
         <v>268</v>
       </c>
@@ -13948,7 +13831,6 @@
       <c r="F182" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G182" s="5"/>
       <c r="H182" s="5" t="s">
         <v>268</v>
       </c>
@@ -13972,7 +13854,6 @@
       <c r="F183" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G183" s="5"/>
       <c r="H183" s="5" t="s">
         <v>268</v>
       </c>
@@ -13996,7 +13877,6 @@
       <c r="F184" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="G184" s="5"/>
       <c r="H184" s="5" t="s">
         <v>268</v>
       </c>
@@ -14043,7 +13923,6 @@
       <c r="F186" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G186" s="5"/>
       <c r="H186" s="5" t="s">
         <v>268</v>
       </c>
@@ -14136,7 +14015,6 @@
       <c r="F190" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G190" s="5"/>
       <c r="H190" s="5" t="s">
         <v>268</v>
       </c>
@@ -14160,7 +14038,6 @@
       <c r="F191" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G191" s="5"/>
       <c r="H191" s="5" t="s">
         <v>268</v>
       </c>
@@ -14184,7 +14061,6 @@
       <c r="F192" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G192" s="5"/>
       <c r="H192" s="5" t="s">
         <v>268</v>
       </c>
@@ -14599,7 +14475,6 @@
       <c r="F210" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G210" s="5"/>
       <c r="H210" s="5" t="s">
         <v>268</v>
       </c>
@@ -14646,7 +14521,6 @@
       <c r="F212" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G212" s="5"/>
       <c r="H212" s="5" t="s">
         <v>268</v>
       </c>
@@ -14716,7 +14590,6 @@
       <c r="F215" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G215" s="5"/>
       <c r="H215" s="5" t="s">
         <v>268</v>
       </c>
@@ -14878,7 +14751,6 @@
       <c r="F222" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G222" s="5"/>
       <c r="H222" s="5" t="s">
         <v>268</v>
       </c>
@@ -14994,7 +14866,6 @@
       <c r="F227" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G227" s="5"/>
       <c r="H227" s="5" t="s">
         <v>268</v>
       </c>
@@ -15164,14 +15035,12 @@
       <c r="B235" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="C235" s="3"/>
       <c r="D235" s="4" t="s">
         <v>454</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="F235" s="2"/>
       <c r="H235" s="5" t="s">
         <v>650</v>
       </c>
@@ -15183,14 +15052,12 @@
       <c r="B236" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="C236" s="3"/>
       <c r="D236" s="4" t="s">
         <v>652</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F236" s="2"/>
       <c r="H236" s="5" t="s">
         <v>654</v>
       </c>
@@ -15202,15 +15069,12 @@
       <c r="B237" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="C237" s="3"/>
       <c r="D237" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F237" s="2"/>
-      <c r="G237" s="5"/>
       <c r="H237" s="5" t="s">
         <v>650</v>
       </c>
@@ -15222,15 +15086,12 @@
       <c r="B238" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="C238" s="3"/>
       <c r="D238" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F238" s="2"/>
-      <c r="G238" s="5"/>
       <c r="H238" s="5" t="s">
         <v>650</v>
       </c>
@@ -15242,14 +15103,12 @@
       <c r="B239" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="C239" s="3"/>
       <c r="D239" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F239" s="2"/>
       <c r="H239" s="5" t="s">
         <v>650</v>
       </c>
@@ -15261,15 +15120,12 @@
       <c r="B240" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="C240" s="3"/>
       <c r="D240" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F240" s="2"/>
-      <c r="G240" s="5"/>
       <c r="H240" s="5" t="s">
         <v>650</v>
       </c>
@@ -15281,15 +15137,12 @@
       <c r="B241" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="C241" s="3"/>
       <c r="D241" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F241" s="2"/>
-      <c r="G241" s="5"/>
       <c r="H241" s="5" t="s">
         <v>650</v>
       </c>
@@ -15301,14 +15154,12 @@
       <c r="B242" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="C242" s="3"/>
       <c r="D242" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F242" s="2"/>
       <c r="H242" s="5" t="s">
         <v>650</v>
       </c>
@@ -15317,7 +15168,6 @@
       <c r="B243" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="C243" s="3"/>
       <c r="D243" s="4" t="s">
         <v>667</v>
       </c>
@@ -15329,7 +15179,6 @@
       <c r="B244" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="C244" s="3"/>
       <c r="D244" s="4" t="s">
         <v>669</v>
       </c>
@@ -15341,7 +15190,6 @@
       <c r="B245" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="C245" s="3"/>
       <c r="D245" s="4" t="s">
         <v>671</v>
       </c>
@@ -16203,7 +16051,6 @@
       <c r="B296" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="C296" s="3"/>
       <c r="D296" s="4" t="s">
         <v>829</v>
       </c>
@@ -16261,7 +16108,6 @@
       <c r="F299" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G299" s="5"/>
       <c r="H299" s="5" t="s">
         <v>840</v>
       </c>
@@ -16285,7 +16131,6 @@
       <c r="F300" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G300" s="5"/>
       <c r="H300" s="5" t="s">
         <v>844</v>
       </c>
@@ -16300,14 +16145,12 @@
       <c r="C301" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="D301" s="4"/>
       <c r="E301" s="2" t="s">
         <v>839</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G301" s="5"/>
       <c r="H301" s="5" t="s">
         <v>840</v>
       </c>
@@ -16328,7 +16171,6 @@
       <c r="F302" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G302" s="5"/>
       <c r="H302" s="5" t="s">
         <v>840</v>
       </c>
@@ -16366,7 +16208,6 @@
       <c r="F304" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G304" s="5"/>
       <c r="H304" s="5" t="s">
         <v>268</v>
       </c>
@@ -16384,7 +16225,6 @@
       <c r="F305" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G305" s="5"/>
       <c r="H305" s="5" t="s">
         <v>855</v>
       </c>
@@ -16399,14 +16239,12 @@
       <c r="C306" s="3" t="s">
         <v>857</v>
       </c>
-      <c r="D306" s="4"/>
       <c r="E306" s="2" t="s">
         <v>839</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G306" s="5"/>
       <c r="H306" s="5" t="s">
         <v>840</v>
       </c>
@@ -16421,14 +16259,12 @@
       <c r="C307" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="D307" s="4"/>
       <c r="E307" s="2" t="s">
         <v>839</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G307" s="5"/>
       <c r="H307" s="5" t="s">
         <v>840</v>
       </c>
@@ -16443,7 +16279,6 @@
       <c r="C308" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="D308" s="4"/>
       <c r="E308" s="2" t="s">
         <v>839</v>
       </c>
@@ -16461,14 +16296,12 @@
       <c r="C309" s="3" t="s">
         <v>863</v>
       </c>
-      <c r="D309" s="4"/>
       <c r="E309" s="2" t="s">
         <v>839</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G309" s="5"/>
       <c r="H309" s="5" t="s">
         <v>855</v>
       </c>
@@ -16483,14 +16316,12 @@
       <c r="C310" s="3" t="s">
         <v>865</v>
       </c>
-      <c r="D310" s="4"/>
       <c r="E310" s="2" t="s">
         <v>839</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G310" s="5"/>
       <c r="H310" s="5" t="s">
         <v>840</v>
       </c>
@@ -16505,7 +16336,6 @@
       <c r="C311" s="3" t="s">
         <v>867</v>
       </c>
-      <c r="D311" s="4"/>
       <c r="E311" s="2" t="s">
         <v>839</v>
       </c>
@@ -16520,13 +16350,9 @@
       <c r="B312" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="C312" s="3"/>
-      <c r="D312" s="4"/>
       <c r="E312" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="F312" s="2"/>
-      <c r="G312" s="5"/>
       <c r="H312" s="5" t="s">
         <v>840</v>
       </c>
@@ -16538,12 +16364,9 @@
       <c r="C313" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="D313" s="4"/>
       <c r="E313" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="F313" s="2"/>
-      <c r="G313" s="5"/>
       <c r="H313" s="5" t="s">
         <v>855</v>
       </c>
@@ -16558,14 +16381,12 @@
       <c r="C314" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="D314" s="4"/>
       <c r="E314" s="2" t="s">
         <v>873</v>
       </c>
       <c r="F314" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G314" s="5"/>
       <c r="H314" s="5" t="s">
         <v>268</v>
       </c>
@@ -16580,14 +16401,12 @@
       <c r="C315" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="D315" s="4"/>
       <c r="E315" s="2" t="s">
         <v>873</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G315" s="5"/>
       <c r="H315" s="5" t="s">
         <v>268</v>
       </c>
@@ -16602,14 +16421,12 @@
       <c r="C316" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="D316" s="4"/>
       <c r="E316" s="2" t="s">
         <v>873</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G316" s="5"/>
       <c r="H316" s="5" t="s">
         <v>268</v>
       </c>
@@ -16633,7 +16450,6 @@
       <c r="F317" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G317" s="5"/>
       <c r="H317" s="5" t="s">
         <v>268</v>
       </c>
@@ -16648,14 +16464,12 @@
       <c r="C318" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="D318" s="4"/>
       <c r="E318" s="2" t="s">
         <v>873</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G318" s="5"/>
       <c r="H318" s="5" t="s">
         <v>268</v>
       </c>
@@ -16670,14 +16484,12 @@
       <c r="C319" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="D319" s="4"/>
       <c r="E319" s="2" t="s">
         <v>873</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G319" s="5"/>
       <c r="H319" s="5" t="s">
         <v>268</v>
       </c>
@@ -16701,7 +16513,6 @@
       <c r="F320" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G320" s="5"/>
       <c r="H320" s="5" t="s">
         <v>308</v>
       </c>
@@ -16725,7 +16536,6 @@
       <c r="F321" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G321" s="5"/>
       <c r="H321" s="5" t="s">
         <v>338</v>
       </c>
@@ -16746,7 +16556,6 @@
       <c r="F322" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G322" s="5"/>
       <c r="H322" s="5" t="s">
         <v>268</v>
       </c>
@@ -16758,7 +16567,6 @@
       <c r="C323" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="D323" s="4"/>
       <c r="E323" s="2" t="s">
         <v>873</v>
       </c>
@@ -16785,14 +16593,12 @@
       <c r="C324" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="D324" s="4"/>
       <c r="E324" s="2" t="s">
         <v>873</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G324" s="5"/>
       <c r="H324" s="5" t="s">
         <v>268</v>
       </c>
@@ -16813,7 +16619,6 @@
       <c r="F325" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G325" s="5"/>
       <c r="H325" s="5" t="s">
         <v>268</v>
       </c>
@@ -16828,14 +16633,12 @@
       <c r="C326" s="3" t="s">
         <v>901</v>
       </c>
-      <c r="D326" s="4"/>
       <c r="E326" s="2" t="s">
         <v>873</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G326" s="5"/>
       <c r="H326" s="5" t="s">
         <v>268</v>
       </c>
@@ -16850,14 +16653,12 @@
       <c r="C327" s="3" t="s">
         <v>901</v>
       </c>
-      <c r="D327" s="4"/>
       <c r="E327" s="2" t="s">
         <v>873</v>
       </c>
       <c r="F327" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G327" s="5"/>
       <c r="H327" s="5" t="s">
         <v>268</v>
       </c>
@@ -16872,14 +16673,12 @@
       <c r="C328" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="D328" s="4"/>
       <c r="E328" s="2" t="s">
         <v>873</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G328" s="5"/>
       <c r="H328" s="5" t="s">
         <v>905</v>
       </c>
@@ -16894,7 +16693,6 @@
       <c r="C329" s="3" t="s">
         <v>907</v>
       </c>
-      <c r="D329" s="4"/>
       <c r="E329" s="2" t="s">
         <v>873</v>
       </c>
@@ -16915,7 +16713,6 @@
       <c r="C330" s="3" t="s">
         <v>909</v>
       </c>
-      <c r="D330" s="4"/>
       <c r="E330" s="2" t="s">
         <v>873</v>
       </c>
@@ -16942,7 +16739,6 @@
       <c r="F331" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G331" s="5"/>
       <c r="H331" s="5" t="s">
         <v>912</v>
       </c>
@@ -16957,7 +16753,6 @@
       <c r="C332" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="D332" s="4"/>
       <c r="E332" s="2" t="s">
         <v>873</v>
       </c>
@@ -17024,7 +16819,6 @@
       <c r="F335" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G335" s="5"/>
       <c r="H335" s="5" t="s">
         <v>268</v>
       </c>
@@ -17045,7 +16839,6 @@
       <c r="F336" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G336" s="5"/>
       <c r="H336" s="5" t="s">
         <v>268</v>
       </c>
@@ -17083,7 +16876,6 @@
       <c r="C338" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="D338" s="4"/>
       <c r="E338" s="2" t="s">
         <v>873</v>
       </c>
@@ -17130,7 +16922,6 @@
       <c r="F340" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G340" s="5"/>
       <c r="H340" s="5" t="s">
         <v>268</v>
       </c>
@@ -17145,7 +16936,6 @@
       <c r="C341" s="3" t="s">
         <v>937</v>
       </c>
-      <c r="D341" s="4"/>
       <c r="E341" s="2" t="s">
         <v>873</v>
       </c>
@@ -17206,7 +16996,6 @@
       <c r="C344" s="3" t="s">
         <v>944</v>
       </c>
-      <c r="D344" s="4"/>
       <c r="E344" s="2" t="s">
         <v>873</v>
       </c>
@@ -17227,7 +17016,6 @@
       <c r="C345" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="D345" s="4"/>
       <c r="E345" s="2" t="s">
         <v>873</v>
       </c>
@@ -17260,7 +17048,6 @@
       <c r="F346" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G346" s="5"/>
       <c r="H346" s="5" t="s">
         <v>915</v>
       </c>
@@ -17281,7 +17068,6 @@
       <c r="F347" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G347" s="5"/>
       <c r="H347" s="5" t="s">
         <v>915</v>
       </c>
@@ -17305,7 +17091,6 @@
       <c r="F348" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G348" s="5"/>
       <c r="H348" s="5" t="s">
         <v>308</v>
       </c>
@@ -17329,7 +17114,6 @@
       <c r="F349" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G349" s="5"/>
       <c r="H349" s="5" t="s">
         <v>268</v>
       </c>
@@ -17350,7 +17134,6 @@
       <c r="F350" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G350" s="5"/>
       <c r="H350" s="5" t="s">
         <v>268</v>
       </c>
@@ -17371,7 +17154,6 @@
       <c r="F351" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G351" s="5"/>
       <c r="H351" s="5" t="s">
         <v>268</v>
       </c>
@@ -17392,7 +17174,6 @@
       <c r="F352" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G352" s="5"/>
       <c r="H352" s="5" t="s">
         <v>268</v>
       </c>
@@ -17413,7 +17194,6 @@
       <c r="F353" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G353" s="5"/>
       <c r="H353" s="5" t="s">
         <v>268</v>
       </c>
@@ -17454,7 +17234,6 @@
       <c r="F355" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G355" s="5"/>
       <c r="H355" s="5" t="s">
         <v>973</v>
       </c>
@@ -17478,7 +17257,6 @@
       <c r="F356" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G356" s="5"/>
       <c r="H356" s="5" t="s">
         <v>973</v>
       </c>
@@ -17507,15 +17285,12 @@
       <c r="B358" s="3" t="s">
         <v>978</v>
       </c>
-      <c r="C358" s="3"/>
       <c r="D358" s="4" t="s">
         <v>979</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="F358" s="2"/>
-      <c r="G358" s="5"/>
       <c r="H358" s="5" t="s">
         <v>346</v>
       </c>
@@ -17524,7 +17299,6 @@
       <c r="B359" s="3" t="s">
         <v>980</v>
       </c>
-      <c r="C359" s="3"/>
       <c r="D359" s="4" t="s">
         <v>981</v>
       </c>
@@ -17626,7 +17400,6 @@
       <c r="E364" s="9" t="s">
         <v>996</v>
       </c>
-      <c r="F364" s="2"/>
       <c r="G364" s="11" t="s">
         <v>1003</v>
       </c>
@@ -18477,7 +18250,6 @@
       <c r="C414" s="3" t="s">
         <v>1154</v>
       </c>
-      <c r="D414" s="4"/>
       <c r="E414" s="2" t="s">
         <v>1155</v>
       </c>
@@ -18498,14 +18270,12 @@
       <c r="C415" s="3" t="s">
         <v>1158</v>
       </c>
-      <c r="D415" s="4"/>
       <c r="E415" s="2" t="s">
         <v>1155</v>
       </c>
       <c r="F415" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G415" s="5"/>
       <c r="H415" s="5" t="s">
         <v>261</v>
       </c>
@@ -18520,7 +18290,6 @@
       <c r="C416" s="3" t="s">
         <v>1160</v>
       </c>
-      <c r="D416" s="4"/>
       <c r="E416" s="2" t="s">
         <v>1155</v>
       </c>
@@ -18541,14 +18310,12 @@
       <c r="C417" s="3" t="s">
         <v>1162</v>
       </c>
-      <c r="D417" s="4"/>
       <c r="E417" s="2" t="s">
         <v>1155</v>
       </c>
       <c r="F417" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G417" s="5"/>
       <c r="H417" s="5" t="s">
         <v>1156</v>
       </c>
@@ -18563,7 +18330,6 @@
       <c r="C418" s="3" t="s">
         <v>1164</v>
       </c>
-      <c r="D418" s="4"/>
       <c r="E418" s="2" t="s">
         <v>1155</v>
       </c>
@@ -18584,14 +18350,12 @@
       <c r="C419" s="3" t="s">
         <v>1166</v>
       </c>
-      <c r="D419" s="4"/>
       <c r="E419" s="2" t="s">
         <v>1155</v>
       </c>
       <c r="F419" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G419" s="5"/>
       <c r="H419" s="5" t="s">
         <v>1167</v>
       </c>
@@ -18606,14 +18370,12 @@
       <c r="C420" s="3" t="s">
         <v>1169</v>
       </c>
-      <c r="D420" s="4"/>
       <c r="E420" s="2" t="s">
         <v>1155</v>
       </c>
       <c r="F420" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G420" s="5"/>
       <c r="H420" s="5" t="s">
         <v>1156</v>
       </c>
@@ -18634,7 +18396,6 @@
       <c r="F421" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G421" s="5"/>
       <c r="H421" s="5" t="s">
         <v>1167</v>
       </c>
@@ -18689,7 +18450,6 @@
       <c r="C424" s="3" t="s">
         <v>1177</v>
       </c>
-      <c r="D424" s="4"/>
       <c r="E424" s="2" t="s">
         <v>1155</v>
       </c>
@@ -18716,7 +18476,6 @@
       <c r="F425" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G425" s="5"/>
       <c r="H425" s="5" t="s">
         <v>1167</v>
       </c>
@@ -18728,15 +18487,12 @@
       <c r="B426" s="3" t="s">
         <v>1180</v>
       </c>
-      <c r="C426" s="3"/>
       <c r="D426" s="4" t="s">
         <v>1181</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="F426" s="2"/>
-      <c r="G426" s="5"/>
       <c r="H426" s="5" t="s">
         <v>1156</v>
       </c>
@@ -18748,14 +18504,12 @@
       <c r="B427" s="3" t="s">
         <v>1182</v>
       </c>
-      <c r="C427" s="3"/>
       <c r="D427" s="4" t="s">
         <v>1181</v>
       </c>
       <c r="E427" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="F427" s="2"/>
       <c r="H427" s="5" t="s">
         <v>1183</v>
       </c>
@@ -18770,14 +18524,12 @@
       <c r="C428" s="3" t="s">
         <v>1185</v>
       </c>
-      <c r="D428" s="4"/>
       <c r="E428" s="2" t="s">
         <v>1186</v>
       </c>
       <c r="F428" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G428" s="5"/>
       <c r="H428" s="5" t="s">
         <v>1187</v>
       </c>
@@ -18792,7 +18544,6 @@
       <c r="C429" s="3" t="s">
         <v>1189</v>
       </c>
-      <c r="D429" s="4"/>
       <c r="E429" s="2" t="s">
         <v>1186</v>
       </c>
@@ -18816,7 +18567,6 @@
       <c r="C430" s="3" t="s">
         <v>1193</v>
       </c>
-      <c r="D430" s="4"/>
       <c r="E430" s="2" t="s">
         <v>1186</v>
       </c>
@@ -18840,7 +18590,6 @@
       <c r="C431" s="3" t="s">
         <v>1196</v>
       </c>
-      <c r="D431" s="4"/>
       <c r="E431" s="2" t="s">
         <v>1186</v>
       </c>
@@ -18861,7 +18610,6 @@
       <c r="C432" s="3" t="s">
         <v>1198</v>
       </c>
-      <c r="D432" s="4"/>
       <c r="E432" s="2" t="s">
         <v>1186</v>
       </c>
@@ -18885,7 +18633,6 @@
       <c r="C433" s="3" t="s">
         <v>1201</v>
       </c>
-      <c r="D433" s="4"/>
       <c r="E433" s="2" t="s">
         <v>1186</v>
       </c>
@@ -18909,7 +18656,6 @@
       <c r="C434" s="3" t="s">
         <v>1205</v>
       </c>
-      <c r="D434" s="4"/>
       <c r="E434" s="2" t="s">
         <v>1186</v>
       </c>
@@ -18936,7 +18682,6 @@
       <c r="C435" s="3" t="s">
         <v>1210</v>
       </c>
-      <c r="D435" s="4"/>
       <c r="E435" s="2" t="s">
         <v>1211</v>
       </c>
@@ -18983,7 +18728,6 @@
       <c r="C437" s="3" t="s">
         <v>1217</v>
       </c>
-      <c r="D437" s="4"/>
       <c r="E437" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19004,7 +18748,6 @@
       <c r="C438" s="3" t="s">
         <v>1219</v>
       </c>
-      <c r="D438" s="4"/>
       <c r="E438" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19065,7 +18808,6 @@
       <c r="C441" s="3" t="s">
         <v>1225</v>
       </c>
-      <c r="D441" s="4"/>
       <c r="E441" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19086,7 +18828,6 @@
       <c r="C442" s="3" t="s">
         <v>1227</v>
       </c>
-      <c r="D442" s="4"/>
       <c r="E442" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19107,7 +18848,6 @@
       <c r="C443" s="3" t="s">
         <v>1229</v>
       </c>
-      <c r="D443" s="4"/>
       <c r="E443" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19128,7 +18868,6 @@
       <c r="C444" s="3" t="s">
         <v>1231</v>
       </c>
-      <c r="D444" s="4"/>
       <c r="E444" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19149,7 +18888,6 @@
       <c r="C445" s="3" t="s">
         <v>1233</v>
       </c>
-      <c r="D445" s="4"/>
       <c r="E445" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19170,14 +18908,12 @@
       <c r="C446" s="3" t="s">
         <v>1236</v>
       </c>
-      <c r="D446" s="4"/>
       <c r="E446" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F446" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G446" s="5"/>
       <c r="H446" s="5" t="s">
         <v>1237</v>
       </c>
@@ -19192,7 +18928,6 @@
       <c r="C447" s="3" t="s">
         <v>1239</v>
       </c>
-      <c r="D447" s="4"/>
       <c r="E447" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19213,7 +18948,6 @@
       <c r="C448" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="D448" s="4"/>
       <c r="E448" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19237,7 +18971,6 @@
       <c r="C449" s="3" t="s">
         <v>1243</v>
       </c>
-      <c r="D449" s="4"/>
       <c r="E449" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19261,14 +18994,12 @@
       <c r="C450" s="3" t="s">
         <v>1245</v>
       </c>
-      <c r="D450" s="4"/>
       <c r="E450" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F450" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G450" s="5"/>
       <c r="H450" s="5" t="s">
         <v>1187</v>
       </c>
@@ -19283,7 +19014,6 @@
       <c r="C451" s="3" t="s">
         <v>1247</v>
       </c>
-      <c r="D451" s="4"/>
       <c r="E451" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19304,7 +19034,6 @@
       <c r="C452" s="3" t="s">
         <v>1249</v>
       </c>
-      <c r="D452" s="4"/>
       <c r="E452" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19328,7 +19057,6 @@
       <c r="C453" s="3" t="s">
         <v>1253</v>
       </c>
-      <c r="D453" s="4"/>
       <c r="E453" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19469,7 +19197,6 @@
       <c r="C460" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="D460" s="4"/>
       <c r="E460" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19490,14 +19217,12 @@
       <c r="C461" s="3" t="s">
         <v>1271</v>
       </c>
-      <c r="D461" s="4"/>
       <c r="E461" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F461" s="2" t="s">
         <v>1272</v>
       </c>
-      <c r="G461" s="5"/>
       <c r="H461" s="5" t="s">
         <v>268</v>
       </c>
@@ -19512,7 +19237,6 @@
       <c r="C462" s="3" t="s">
         <v>1274</v>
       </c>
-      <c r="D462" s="4"/>
       <c r="E462" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19536,7 +19260,6 @@
       <c r="C463" s="3" t="s">
         <v>1276</v>
       </c>
-      <c r="D463" s="4"/>
       <c r="E463" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19557,7 +19280,6 @@
       <c r="C464" s="3" t="s">
         <v>1278</v>
       </c>
-      <c r="D464" s="4"/>
       <c r="E464" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19578,7 +19300,6 @@
       <c r="C465" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="D465" s="4"/>
       <c r="E465" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19599,7 +19320,6 @@
       <c r="C466" s="3" t="s">
         <v>1282</v>
       </c>
-      <c r="D466" s="4"/>
       <c r="E466" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19620,14 +19340,12 @@
       <c r="C467" s="3" t="s">
         <v>1284</v>
       </c>
-      <c r="D467" s="4"/>
       <c r="E467" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F467" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G467" s="5"/>
       <c r="H467" s="5" t="s">
         <v>408</v>
       </c>
@@ -19636,11 +19354,9 @@
       <c r="A468" s="2">
         <v>1763</v>
       </c>
-      <c r="B468" s="3"/>
       <c r="C468" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="D468" s="4"/>
       <c r="E468" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19667,7 +19383,6 @@
       <c r="C469" s="3" t="s">
         <v>1288</v>
       </c>
-      <c r="D469" s="4"/>
       <c r="E469" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19688,7 +19403,6 @@
       <c r="C470" s="3" t="s">
         <v>1290</v>
       </c>
-      <c r="D470" s="4"/>
       <c r="E470" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19709,7 +19423,6 @@
       <c r="C471" s="3" t="s">
         <v>1292</v>
       </c>
-      <c r="D471" s="4"/>
       <c r="E471" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19733,7 +19446,6 @@
       <c r="C472" s="3" t="s">
         <v>1294</v>
       </c>
-      <c r="D472" s="4"/>
       <c r="E472" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19757,14 +19469,12 @@
       <c r="C473" s="3" t="s">
         <v>1296</v>
       </c>
-      <c r="D473" s="4"/>
       <c r="E473" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F473" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G473" s="5"/>
       <c r="H473" s="5" t="s">
         <v>1187</v>
       </c>
@@ -19779,14 +19489,12 @@
       <c r="C474" s="3" t="s">
         <v>1298</v>
       </c>
-      <c r="D474" s="4"/>
       <c r="E474" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F474" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G474" s="5"/>
       <c r="H474" s="5" t="s">
         <v>268</v>
       </c>
@@ -19801,14 +19509,12 @@
       <c r="C475" s="3" t="s">
         <v>1300</v>
       </c>
-      <c r="D475" s="4"/>
       <c r="E475" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F475" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G475" s="5"/>
       <c r="H475" s="5" t="s">
         <v>268</v>
       </c>
@@ -19846,7 +19552,6 @@
       <c r="C477" s="3" t="s">
         <v>1305</v>
       </c>
-      <c r="D477" s="4"/>
       <c r="E477" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19867,7 +19572,6 @@
       <c r="C478" s="3" t="s">
         <v>1307</v>
       </c>
-      <c r="D478" s="4"/>
       <c r="E478" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19888,7 +19592,6 @@
       <c r="C479" s="3" t="s">
         <v>1309</v>
       </c>
-      <c r="D479" s="4"/>
       <c r="E479" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19909,7 +19612,6 @@
       <c r="C480" s="3" t="s">
         <v>1312</v>
       </c>
-      <c r="D480" s="4"/>
       <c r="E480" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19930,7 +19632,6 @@
       <c r="C481" s="3" t="s">
         <v>1314</v>
       </c>
-      <c r="D481" s="4"/>
       <c r="E481" s="2" t="s">
         <v>1211</v>
       </c>
@@ -19951,14 +19652,12 @@
       <c r="C482" s="3" t="s">
         <v>1316</v>
       </c>
-      <c r="D482" s="4"/>
       <c r="E482" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F482" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G482" s="5"/>
       <c r="H482" s="5" t="s">
         <v>616</v>
       </c>
@@ -19973,7 +19672,6 @@
       <c r="C483" s="3" t="s">
         <v>1318</v>
       </c>
-      <c r="D483" s="4"/>
       <c r="E483" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20014,14 +19712,12 @@
       <c r="C485" s="3" t="s">
         <v>1322</v>
       </c>
-      <c r="D485" s="4"/>
       <c r="E485" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F485" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G485" s="5"/>
       <c r="H485" s="5" t="s">
         <v>268</v>
       </c>
@@ -20056,7 +19752,6 @@
       <c r="C487" s="3" t="s">
         <v>1326</v>
       </c>
-      <c r="D487" s="4"/>
       <c r="E487" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20077,7 +19772,6 @@
       <c r="C488" s="3" t="s">
         <v>1328</v>
       </c>
-      <c r="D488" s="4"/>
       <c r="E488" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20098,7 +19792,6 @@
       <c r="C489" s="3" t="s">
         <v>1330</v>
       </c>
-      <c r="D489" s="4"/>
       <c r="E489" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20119,7 +19812,6 @@
       <c r="C490" s="3" t="s">
         <v>1332</v>
       </c>
-      <c r="D490" s="4"/>
       <c r="E490" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20146,7 +19838,6 @@
       <c r="F491" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G491" s="5"/>
       <c r="H491" s="5" t="s">
         <v>1333</v>
       </c>
@@ -20161,14 +19852,12 @@
       <c r="C492" s="3" t="s">
         <v>1337</v>
       </c>
-      <c r="D492" s="4"/>
       <c r="E492" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F492" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G492" s="5"/>
       <c r="H492" s="5" t="s">
         <v>1237</v>
       </c>
@@ -20183,7 +19872,6 @@
       <c r="C493" s="3" t="s">
         <v>1339</v>
       </c>
-      <c r="D493" s="4"/>
       <c r="E493" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20198,11 +19886,9 @@
       <c r="A494" s="2">
         <v>1731</v>
       </c>
-      <c r="B494" s="3"/>
       <c r="C494" s="3" t="s">
         <v>1340</v>
       </c>
-      <c r="D494" s="4"/>
       <c r="E494" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20229,7 +19915,6 @@
       <c r="C495" s="3" t="s">
         <v>1344</v>
       </c>
-      <c r="D495" s="4"/>
       <c r="E495" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20253,14 +19938,12 @@
       <c r="C496" s="3" t="s">
         <v>1346</v>
       </c>
-      <c r="D496" s="4"/>
       <c r="E496" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F496" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G496" s="5"/>
       <c r="H496" s="5" t="s">
         <v>268</v>
       </c>
@@ -20278,7 +19961,6 @@
       <c r="C497" s="3" t="s">
         <v>1348</v>
       </c>
-      <c r="D497" s="4"/>
       <c r="E497" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20299,7 +19981,6 @@
       <c r="C498" s="3" t="s">
         <v>1350</v>
       </c>
-      <c r="D498" s="4"/>
       <c r="E498" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20320,7 +20001,6 @@
       <c r="C499" s="3" t="s">
         <v>1352</v>
       </c>
-      <c r="D499" s="4"/>
       <c r="E499" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20341,7 +20021,6 @@
       <c r="C500" s="3" t="s">
         <v>1354</v>
       </c>
-      <c r="D500" s="4"/>
       <c r="E500" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20362,7 +20041,6 @@
       <c r="C501" s="3" t="s">
         <v>1356</v>
       </c>
-      <c r="D501" s="4"/>
       <c r="E501" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20383,7 +20061,6 @@
       <c r="C502" s="3" t="s">
         <v>1358</v>
       </c>
-      <c r="D502" s="4"/>
       <c r="E502" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20404,7 +20081,6 @@
       <c r="C503" s="3" t="s">
         <v>1360</v>
       </c>
-      <c r="D503" s="4"/>
       <c r="E503" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20425,7 +20101,6 @@
       <c r="C504" s="3" t="s">
         <v>1362</v>
       </c>
-      <c r="D504" s="4"/>
       <c r="E504" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20446,7 +20121,6 @@
       <c r="C505" s="3" t="s">
         <v>1364</v>
       </c>
-      <c r="D505" s="4"/>
       <c r="E505" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20467,14 +20141,12 @@
       <c r="C506" s="3" t="s">
         <v>1366</v>
       </c>
-      <c r="D506" s="4"/>
       <c r="E506" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F506" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G506" s="5"/>
       <c r="H506" s="5" t="s">
         <v>268</v>
       </c>
@@ -20489,14 +20161,12 @@
       <c r="C507" s="3" t="s">
         <v>1368</v>
       </c>
-      <c r="D507" s="4"/>
       <c r="E507" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F507" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G507" s="5"/>
       <c r="H507" s="5" t="s">
         <v>268</v>
       </c>
@@ -20511,7 +20181,6 @@
       <c r="C508" s="3" t="s">
         <v>1370</v>
       </c>
-      <c r="D508" s="4"/>
       <c r="E508" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20532,7 +20201,6 @@
       <c r="C509" s="3" t="s">
         <v>1372</v>
       </c>
-      <c r="D509" s="4"/>
       <c r="E509" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20553,7 +20221,6 @@
       <c r="C510" s="3" t="s">
         <v>1374</v>
       </c>
-      <c r="D510" s="4"/>
       <c r="E510" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20574,14 +20241,12 @@
       <c r="C511" s="3" t="s">
         <v>1376</v>
       </c>
-      <c r="D511" s="4"/>
       <c r="E511" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F511" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G511" s="5"/>
       <c r="H511" s="5" t="s">
         <v>268</v>
       </c>
@@ -20596,14 +20261,12 @@
       <c r="C512" s="3" t="s">
         <v>1378</v>
       </c>
-      <c r="D512" s="4"/>
       <c r="E512" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F512" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G512" s="5"/>
       <c r="H512" s="5" t="s">
         <v>268</v>
       </c>
@@ -20618,14 +20281,12 @@
       <c r="C513" s="3" t="s">
         <v>1380</v>
       </c>
-      <c r="D513" s="4"/>
       <c r="E513" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F513" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G513" s="5"/>
       <c r="H513" s="5" t="s">
         <v>1381</v>
       </c>
@@ -20640,7 +20301,6 @@
       <c r="C514" s="3" t="s">
         <v>1383</v>
       </c>
-      <c r="D514" s="4"/>
       <c r="E514" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20661,14 +20321,12 @@
       <c r="C515" s="3" t="s">
         <v>1385</v>
       </c>
-      <c r="D515" s="4"/>
       <c r="E515" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F515" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G515" s="5"/>
       <c r="H515" s="5" t="s">
         <v>268</v>
       </c>
@@ -20683,14 +20341,12 @@
       <c r="C516" s="3" t="s">
         <v>1387</v>
       </c>
-      <c r="D516" s="4"/>
       <c r="E516" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F516" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G516" s="5"/>
       <c r="H516" s="5" t="s">
         <v>1266</v>
       </c>
@@ -20705,7 +20361,6 @@
       <c r="C517" s="3" t="s">
         <v>1389</v>
       </c>
-      <c r="D517" s="4"/>
       <c r="E517" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20726,7 +20381,6 @@
       <c r="C518" s="3" t="s">
         <v>1391</v>
       </c>
-      <c r="D518" s="4"/>
       <c r="E518" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20747,7 +20401,6 @@
       <c r="C519" s="3" t="s">
         <v>1393</v>
       </c>
-      <c r="D519" s="4"/>
       <c r="E519" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20768,7 +20421,6 @@
       <c r="C520" s="3" t="s">
         <v>1395</v>
       </c>
-      <c r="D520" s="4"/>
       <c r="E520" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20789,7 +20441,6 @@
       <c r="C521" s="3" t="s">
         <v>1397</v>
       </c>
-      <c r="D521" s="4"/>
       <c r="E521" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20810,14 +20461,12 @@
       <c r="C522" s="3" t="s">
         <v>1399</v>
       </c>
-      <c r="D522" s="4"/>
       <c r="E522" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F522" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G522" s="5"/>
       <c r="H522" s="5" t="s">
         <v>268</v>
       </c>
@@ -20832,14 +20481,12 @@
       <c r="C523" s="3" t="s">
         <v>1401</v>
       </c>
-      <c r="D523" s="4"/>
       <c r="E523" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F523" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G523" s="5"/>
       <c r="H523" s="5" t="s">
         <v>268</v>
       </c>
@@ -20854,14 +20501,12 @@
       <c r="C524" s="3" t="s">
         <v>1403</v>
       </c>
-      <c r="D524" s="4"/>
       <c r="E524" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F524" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G524" s="5"/>
       <c r="H524" s="5" t="s">
         <v>268</v>
       </c>
@@ -20876,14 +20521,12 @@
       <c r="C525" s="3" t="s">
         <v>1405</v>
       </c>
-      <c r="D525" s="4"/>
       <c r="E525" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F525" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G525" s="5"/>
       <c r="H525" s="5" t="s">
         <v>408</v>
       </c>
@@ -20898,14 +20541,12 @@
       <c r="C526" s="3" t="s">
         <v>1407</v>
       </c>
-      <c r="D526" s="4"/>
       <c r="E526" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F526" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G526" s="5"/>
       <c r="H526" s="5" t="s">
         <v>650</v>
       </c>
@@ -20920,14 +20561,12 @@
       <c r="C527" s="3" t="s">
         <v>1409</v>
       </c>
-      <c r="D527" s="4"/>
       <c r="E527" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F527" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G527" s="5"/>
       <c r="H527" s="5" t="s">
         <v>408</v>
       </c>
@@ -20945,7 +20584,6 @@
       <c r="C528" s="3" t="s">
         <v>1412</v>
       </c>
-      <c r="D528" s="4"/>
       <c r="E528" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20966,7 +20604,6 @@
       <c r="C529" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="D529" s="4"/>
       <c r="E529" s="2" t="s">
         <v>1211</v>
       </c>
@@ -20987,7 +20624,6 @@
       <c r="C530" s="3" t="s">
         <v>1416</v>
       </c>
-      <c r="D530" s="4"/>
       <c r="E530" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21008,7 +20644,6 @@
       <c r="C531" s="3" t="s">
         <v>1418</v>
       </c>
-      <c r="D531" s="4"/>
       <c r="E531" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21029,7 +20664,6 @@
       <c r="C532" s="3" t="s">
         <v>1420</v>
       </c>
-      <c r="D532" s="4"/>
       <c r="E532" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21050,7 +20684,6 @@
       <c r="C533" s="3" t="s">
         <v>1422</v>
       </c>
-      <c r="D533" s="4"/>
       <c r="E533" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21071,7 +20704,6 @@
       <c r="C534" s="3" t="s">
         <v>1424</v>
       </c>
-      <c r="D534" s="4"/>
       <c r="E534" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21115,7 +20747,6 @@
       <c r="C536" s="3" t="s">
         <v>1429</v>
       </c>
-      <c r="D536" s="4"/>
       <c r="E536" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21136,7 +20767,6 @@
       <c r="C537" s="3" t="s">
         <v>1431</v>
       </c>
-      <c r="D537" s="4"/>
       <c r="E537" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21157,7 +20787,6 @@
       <c r="C538" s="3" t="s">
         <v>1433</v>
       </c>
-      <c r="D538" s="4"/>
       <c r="E538" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21178,7 +20807,6 @@
       <c r="C539" s="3" t="s">
         <v>1435</v>
       </c>
-      <c r="D539" s="4"/>
       <c r="E539" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21199,14 +20827,12 @@
       <c r="C540" s="3" t="s">
         <v>1437</v>
       </c>
-      <c r="D540" s="4"/>
       <c r="E540" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F540" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G540" s="5"/>
       <c r="H540" s="5" t="s">
         <v>1237</v>
       </c>
@@ -21221,14 +20847,12 @@
       <c r="C541" s="3" t="s">
         <v>1439</v>
       </c>
-      <c r="D541" s="4"/>
       <c r="E541" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F541" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G541" s="5"/>
       <c r="H541" s="5" t="s">
         <v>1237</v>
       </c>
@@ -21243,7 +20867,6 @@
       <c r="C542" s="3" t="s">
         <v>1441</v>
       </c>
-      <c r="D542" s="4"/>
       <c r="E542" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21264,7 +20887,6 @@
       <c r="C543" s="3" t="s">
         <v>1443</v>
       </c>
-      <c r="D543" s="4"/>
       <c r="E543" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21285,7 +20907,6 @@
       <c r="C544" s="3" t="s">
         <v>1445</v>
       </c>
-      <c r="D544" s="4"/>
       <c r="E544" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21309,7 +20930,6 @@
       <c r="C545" s="3" t="s">
         <v>1447</v>
       </c>
-      <c r="D545" s="4"/>
       <c r="E545" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21336,7 +20956,6 @@
       <c r="C546" s="3" t="s">
         <v>1450</v>
       </c>
-      <c r="D546" s="4"/>
       <c r="E546" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21360,7 +20979,6 @@
       <c r="C547" s="3" t="s">
         <v>1452</v>
       </c>
-      <c r="D547" s="4"/>
       <c r="E547" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21381,7 +20999,6 @@
       <c r="C548" s="3" t="s">
         <v>1454</v>
       </c>
-      <c r="D548" s="4"/>
       <c r="E548" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21402,7 +21019,6 @@
       <c r="C549" s="3" t="s">
         <v>1456</v>
       </c>
-      <c r="D549" s="4"/>
       <c r="E549" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21423,7 +21039,6 @@
       <c r="C550" s="3" t="s">
         <v>1458</v>
       </c>
-      <c r="D550" s="4"/>
       <c r="E550" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21444,14 +21059,12 @@
       <c r="C551" s="3" t="s">
         <v>1460</v>
       </c>
-      <c r="D551" s="4"/>
       <c r="E551" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F551" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G551" s="5"/>
       <c r="H551" s="5" t="s">
         <v>268</v>
       </c>
@@ -21466,7 +21079,6 @@
       <c r="C552" s="3" t="s">
         <v>1462</v>
       </c>
-      <c r="D552" s="4"/>
       <c r="E552" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21487,7 +21099,6 @@
       <c r="C553" s="3" t="s">
         <v>1464</v>
       </c>
-      <c r="D553" s="4"/>
       <c r="E553" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21508,7 +21119,6 @@
       <c r="C554" s="3" t="s">
         <v>1466</v>
       </c>
-      <c r="D554" s="4"/>
       <c r="E554" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21529,14 +21139,12 @@
       <c r="C555" s="3" t="s">
         <v>1468</v>
       </c>
-      <c r="D555" s="4"/>
       <c r="E555" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F555" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G555" s="5"/>
       <c r="H555" s="5" t="s">
         <v>268</v>
       </c>
@@ -21551,14 +21159,12 @@
       <c r="C556" s="3" t="s">
         <v>1470</v>
       </c>
-      <c r="D556" s="4"/>
       <c r="E556" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F556" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G556" s="5"/>
       <c r="H556" s="5" t="s">
         <v>268</v>
       </c>
@@ -21573,14 +21179,12 @@
       <c r="C557" s="3" t="s">
         <v>1472</v>
       </c>
-      <c r="D557" s="4"/>
       <c r="E557" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F557" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G557" s="5"/>
       <c r="H557" s="5" t="s">
         <v>268</v>
       </c>
@@ -21595,7 +21199,6 @@
       <c r="C558" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="D558" s="4"/>
       <c r="E558" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21616,7 +21219,6 @@
       <c r="C559" s="3" t="s">
         <v>1476</v>
       </c>
-      <c r="D559" s="4"/>
       <c r="E559" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21637,7 +21239,6 @@
       <c r="C560" s="3" t="s">
         <v>1478</v>
       </c>
-      <c r="D560" s="4"/>
       <c r="E560" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21658,7 +21259,6 @@
       <c r="C561" s="3" t="s">
         <v>1480</v>
       </c>
-      <c r="D561" s="4"/>
       <c r="E561" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21679,7 +21279,6 @@
       <c r="C562" s="3" t="s">
         <v>1482</v>
       </c>
-      <c r="D562" s="4"/>
       <c r="E562" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21700,7 +21299,6 @@
       <c r="C563" s="3" t="s">
         <v>1485</v>
       </c>
-      <c r="D563" s="4"/>
       <c r="E563" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21721,7 +21319,6 @@
       <c r="C564" s="3" t="s">
         <v>1487</v>
       </c>
-      <c r="D564" s="4"/>
       <c r="E564" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21742,14 +21339,12 @@
       <c r="C565" s="3" t="s">
         <v>1489</v>
       </c>
-      <c r="D565" s="4"/>
       <c r="E565" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F565" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G565" s="5"/>
       <c r="H565" s="5" t="s">
         <v>268</v>
       </c>
@@ -21764,7 +21359,6 @@
       <c r="C566" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="D566" s="4"/>
       <c r="E566" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21785,7 +21379,6 @@
       <c r="C567" s="3" t="s">
         <v>1493</v>
       </c>
-      <c r="D567" s="4"/>
       <c r="E567" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21809,14 +21402,12 @@
       <c r="C568" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="D568" s="4"/>
       <c r="E568" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F568" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G568" s="5"/>
       <c r="H568" s="5" t="s">
         <v>268</v>
       </c>
@@ -21834,7 +21425,6 @@
       <c r="C569" s="3" t="s">
         <v>1497</v>
       </c>
-      <c r="D569" s="4"/>
       <c r="E569" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21858,7 +21448,6 @@
       <c r="C570" s="3" t="s">
         <v>1499</v>
       </c>
-      <c r="D570" s="4"/>
       <c r="E570" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21879,7 +21468,6 @@
       <c r="C571" s="3" t="s">
         <v>1501</v>
       </c>
-      <c r="D571" s="4"/>
       <c r="E571" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21900,7 +21488,6 @@
       <c r="C572" s="3" t="s">
         <v>1503</v>
       </c>
-      <c r="D572" s="4"/>
       <c r="E572" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21921,7 +21508,6 @@
       <c r="C573" s="3" t="s">
         <v>1505</v>
       </c>
-      <c r="D573" s="4"/>
       <c r="E573" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21942,7 +21528,6 @@
       <c r="C574" s="3" t="s">
         <v>1507</v>
       </c>
-      <c r="D574" s="4"/>
       <c r="E574" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21963,7 +21548,6 @@
       <c r="C575" s="3" t="s">
         <v>1509</v>
       </c>
-      <c r="D575" s="4"/>
       <c r="E575" s="2" t="s">
         <v>1211</v>
       </c>
@@ -21984,7 +21568,6 @@
       <c r="C576" s="3" t="s">
         <v>1511</v>
       </c>
-      <c r="D576" s="4"/>
       <c r="E576" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22045,7 +21628,6 @@
       <c r="C579" s="3" t="s">
         <v>1517</v>
       </c>
-      <c r="D579" s="4"/>
       <c r="E579" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22066,7 +21648,6 @@
       <c r="C580" s="3" t="s">
         <v>1519</v>
       </c>
-      <c r="D580" s="4"/>
       <c r="E580" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22087,7 +21668,6 @@
       <c r="C581" s="3" t="s">
         <v>1521</v>
       </c>
-      <c r="D581" s="4"/>
       <c r="E581" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22111,7 +21691,6 @@
       <c r="C582" s="3" t="s">
         <v>1523</v>
       </c>
-      <c r="D582" s="4"/>
       <c r="E582" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22132,14 +21711,12 @@
       <c r="C583" s="3" t="s">
         <v>1525</v>
       </c>
-      <c r="D583" s="4"/>
       <c r="E583" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F583" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G583" s="5"/>
       <c r="H583" s="5" t="s">
         <v>268</v>
       </c>
@@ -22154,7 +21731,6 @@
       <c r="C584" s="3" t="s">
         <v>1527</v>
       </c>
-      <c r="D584" s="4"/>
       <c r="E584" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22175,14 +21751,12 @@
       <c r="C585" s="3" t="s">
         <v>1529</v>
       </c>
-      <c r="D585" s="4"/>
       <c r="E585" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F585" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G585" s="5"/>
       <c r="H585" s="5" t="s">
         <v>268</v>
       </c>
@@ -22197,14 +21771,12 @@
       <c r="C586" s="3" t="s">
         <v>1531</v>
       </c>
-      <c r="D586" s="4"/>
       <c r="E586" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F586" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G586" s="5"/>
       <c r="H586" s="5" t="s">
         <v>268</v>
       </c>
@@ -22219,7 +21791,6 @@
       <c r="C587" s="3" t="s">
         <v>1533</v>
       </c>
-      <c r="D587" s="4"/>
       <c r="E587" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22240,7 +21811,6 @@
       <c r="C588" s="3" t="s">
         <v>1535</v>
       </c>
-      <c r="D588" s="4"/>
       <c r="E588" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22261,7 +21831,6 @@
       <c r="C589" s="3" t="s">
         <v>1537</v>
       </c>
-      <c r="D589" s="4"/>
       <c r="E589" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22282,14 +21851,12 @@
       <c r="C590" s="3" t="s">
         <v>1539</v>
       </c>
-      <c r="D590" s="4"/>
       <c r="E590" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F590" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G590" s="5"/>
       <c r="H590" s="5" t="s">
         <v>1333</v>
       </c>
@@ -22304,7 +21871,6 @@
       <c r="C591" s="3" t="s">
         <v>1541</v>
       </c>
-      <c r="D591" s="4"/>
       <c r="E591" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22325,7 +21891,6 @@
       <c r="C592" s="3" t="s">
         <v>1543</v>
       </c>
-      <c r="D592" s="4"/>
       <c r="E592" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22346,7 +21911,6 @@
       <c r="C593" s="3" t="s">
         <v>1545</v>
       </c>
-      <c r="D593" s="4"/>
       <c r="E593" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22367,7 +21931,6 @@
       <c r="C594" s="3" t="s">
         <v>1547</v>
       </c>
-      <c r="D594" s="4"/>
       <c r="E594" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22391,7 +21954,6 @@
       <c r="C595" s="3" t="s">
         <v>1549</v>
       </c>
-      <c r="D595" s="4"/>
       <c r="E595" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22412,7 +21974,6 @@
       <c r="C596" s="3" t="s">
         <v>1551</v>
       </c>
-      <c r="D596" s="4"/>
       <c r="E596" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22433,7 +21994,6 @@
       <c r="C597" s="3" t="s">
         <v>1553</v>
       </c>
-      <c r="D597" s="4"/>
       <c r="E597" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22454,7 +22014,6 @@
       <c r="C598" s="3" t="s">
         <v>1555</v>
       </c>
-      <c r="D598" s="4"/>
       <c r="E598" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22475,7 +22034,6 @@
       <c r="C599" s="3" t="s">
         <v>1557</v>
       </c>
-      <c r="D599" s="4"/>
       <c r="E599" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22496,7 +22054,6 @@
       <c r="C600" s="3" t="s">
         <v>1559</v>
       </c>
-      <c r="D600" s="4"/>
       <c r="E600" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22517,14 +22074,12 @@
       <c r="C601" s="3" t="s">
         <v>1561</v>
       </c>
-      <c r="D601" s="4"/>
       <c r="E601" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F601" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G601" s="5"/>
       <c r="H601" s="5" t="s">
         <v>268</v>
       </c>
@@ -22539,7 +22094,6 @@
       <c r="C602" s="3" t="s">
         <v>1563</v>
       </c>
-      <c r="D602" s="4"/>
       <c r="E602" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22560,7 +22114,6 @@
       <c r="C603" s="3" t="s">
         <v>1566</v>
       </c>
-      <c r="D603" s="4"/>
       <c r="E603" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22581,7 +22134,6 @@
       <c r="C604" s="3" t="s">
         <v>1568</v>
       </c>
-      <c r="D604" s="4"/>
       <c r="E604" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22602,7 +22154,6 @@
       <c r="C605" s="3" t="s">
         <v>1570</v>
       </c>
-      <c r="D605" s="4"/>
       <c r="E605" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22623,7 +22174,6 @@
       <c r="C606" s="3" t="s">
         <v>1572</v>
       </c>
-      <c r="D606" s="4"/>
       <c r="E606" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22644,7 +22194,6 @@
       <c r="C607" s="3" t="s">
         <v>1574</v>
       </c>
-      <c r="D607" s="4"/>
       <c r="E607" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22665,7 +22214,6 @@
       <c r="C608" s="3" t="s">
         <v>1576</v>
       </c>
-      <c r="D608" s="4"/>
       <c r="E608" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22686,7 +22234,6 @@
       <c r="C609" s="3" t="s">
         <v>1578</v>
       </c>
-      <c r="D609" s="4"/>
       <c r="E609" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22707,7 +22254,6 @@
       <c r="C610" s="3" t="s">
         <v>1580</v>
       </c>
-      <c r="D610" s="4"/>
       <c r="E610" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22728,14 +22274,12 @@
       <c r="C611" s="3" t="s">
         <v>1582</v>
       </c>
-      <c r="D611" s="4"/>
       <c r="E611" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F611" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G611" s="5"/>
       <c r="H611" s="5" t="s">
         <v>268</v>
       </c>
@@ -22750,7 +22294,6 @@
       <c r="C612" s="3" t="s">
         <v>1584</v>
       </c>
-      <c r="D612" s="4"/>
       <c r="E612" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22771,7 +22314,6 @@
       <c r="C613" s="3" t="s">
         <v>1586</v>
       </c>
-      <c r="D613" s="4"/>
       <c r="E613" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22792,7 +22334,6 @@
       <c r="C614" s="3" t="s">
         <v>1587</v>
       </c>
-      <c r="D614" s="4"/>
       <c r="E614" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22813,7 +22354,6 @@
       <c r="C615" s="3" t="s">
         <v>1589</v>
       </c>
-      <c r="D615" s="4"/>
       <c r="E615" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22834,7 +22374,6 @@
       <c r="C616" s="3" t="s">
         <v>1591</v>
       </c>
-      <c r="D616" s="4"/>
       <c r="E616" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22855,7 +22394,6 @@
       <c r="C617" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="D617" s="4"/>
       <c r="E617" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22876,7 +22414,6 @@
       <c r="C618" s="3" t="s">
         <v>1595</v>
       </c>
-      <c r="D618" s="4"/>
       <c r="E618" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22897,7 +22434,6 @@
       <c r="C619" s="3" t="s">
         <v>1597</v>
       </c>
-      <c r="D619" s="4"/>
       <c r="E619" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22918,7 +22454,6 @@
       <c r="C620" s="3" t="s">
         <v>1599</v>
       </c>
-      <c r="D620" s="4"/>
       <c r="E620" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22939,7 +22474,6 @@
       <c r="C621" s="3" t="s">
         <v>1601</v>
       </c>
-      <c r="D621" s="4"/>
       <c r="E621" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22960,7 +22494,6 @@
       <c r="C622" s="3" t="s">
         <v>1603</v>
       </c>
-      <c r="D622" s="4"/>
       <c r="E622" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22984,7 +22517,6 @@
       <c r="C623" s="3" t="s">
         <v>1605</v>
       </c>
-      <c r="D623" s="4"/>
       <c r="E623" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23005,7 +22537,6 @@
       <c r="C624" s="3" t="s">
         <v>1607</v>
       </c>
-      <c r="D624" s="4"/>
       <c r="E624" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23026,7 +22557,6 @@
       <c r="C625" s="3" t="s">
         <v>1609</v>
       </c>
-      <c r="D625" s="4"/>
       <c r="E625" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23047,7 +22577,6 @@
       <c r="C626" s="3" t="s">
         <v>1611</v>
       </c>
-      <c r="D626" s="4"/>
       <c r="E626" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23068,7 +22597,6 @@
       <c r="C627" s="3" t="s">
         <v>1613</v>
       </c>
-      <c r="D627" s="4"/>
       <c r="E627" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23089,7 +22617,6 @@
       <c r="C628" s="3" t="s">
         <v>1615</v>
       </c>
-      <c r="D628" s="4"/>
       <c r="E628" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23110,14 +22637,12 @@
       <c r="C629" s="3" t="s">
         <v>1617</v>
       </c>
-      <c r="D629" s="4"/>
       <c r="E629" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F629" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G629" s="5"/>
       <c r="H629" s="5" t="s">
         <v>268</v>
       </c>
@@ -23132,14 +22657,12 @@
       <c r="C630" s="3" t="s">
         <v>1619</v>
       </c>
-      <c r="D630" s="4"/>
       <c r="E630" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F630" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G630" s="5"/>
       <c r="H630" s="5" t="s">
         <v>268</v>
       </c>
@@ -23154,7 +22677,6 @@
       <c r="C631" s="3" t="s">
         <v>1621</v>
       </c>
-      <c r="D631" s="4"/>
       <c r="E631" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23198,7 +22720,6 @@
       <c r="C633" s="3" t="s">
         <v>1626</v>
       </c>
-      <c r="D633" s="4"/>
       <c r="E633" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23219,14 +22740,12 @@
       <c r="C634" s="3" t="s">
         <v>1628</v>
       </c>
-      <c r="D634" s="4"/>
       <c r="E634" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F634" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G634" s="5"/>
       <c r="H634" s="5" t="s">
         <v>268</v>
       </c>
@@ -23241,14 +22760,12 @@
       <c r="C635" s="3" t="s">
         <v>1630</v>
       </c>
-      <c r="D635" s="4"/>
       <c r="E635" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F635" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G635" s="5"/>
       <c r="H635" s="5" t="s">
         <v>1381</v>
       </c>
@@ -23263,7 +22780,6 @@
       <c r="C636" s="3" t="s">
         <v>1632</v>
       </c>
-      <c r="D636" s="4"/>
       <c r="E636" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23284,7 +22800,6 @@
       <c r="C637" s="3" t="s">
         <v>1634</v>
       </c>
-      <c r="D637" s="4"/>
       <c r="E637" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23305,14 +22820,12 @@
       <c r="C638" s="3" t="s">
         <v>1636</v>
       </c>
-      <c r="D638" s="4"/>
       <c r="E638" s="2" t="s">
         <v>1211</v>
       </c>
       <c r="F638" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G638" s="5"/>
       <c r="H638" s="5" t="s">
         <v>268</v>
       </c>
@@ -23321,11 +22834,9 @@
       <c r="A639" s="2">
         <v>1763</v>
       </c>
-      <c r="B639" s="3"/>
       <c r="C639" s="3" t="s">
         <v>1637</v>
       </c>
-      <c r="D639" s="4"/>
       <c r="E639" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23352,7 +22863,6 @@
       <c r="C640" s="3" t="s">
         <v>1640</v>
       </c>
-      <c r="D640" s="4"/>
       <c r="E640" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23373,7 +22883,6 @@
       <c r="C641" s="3" t="s">
         <v>1642</v>
       </c>
-      <c r="D641" s="4"/>
       <c r="E641" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23394,7 +22903,6 @@
       <c r="C642" s="3" t="s">
         <v>1644</v>
       </c>
-      <c r="D642" s="4"/>
       <c r="E642" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23415,7 +22923,6 @@
       <c r="C643" s="3" t="s">
         <v>1646</v>
       </c>
-      <c r="D643" s="4"/>
       <c r="E643" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23436,7 +22943,6 @@
       <c r="C644" s="3" t="s">
         <v>1647</v>
       </c>
-      <c r="D644" s="4"/>
       <c r="E644" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23457,7 +22963,6 @@
       <c r="C645" s="3" t="s">
         <v>1649</v>
       </c>
-      <c r="D645" s="4"/>
       <c r="E645" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23478,7 +22983,6 @@
       <c r="C646" s="3" t="s">
         <v>1651</v>
       </c>
-      <c r="D646" s="4"/>
       <c r="E646" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23499,7 +23003,6 @@
       <c r="C647" s="3" t="s">
         <v>1653</v>
       </c>
-      <c r="D647" s="4"/>
       <c r="E647" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23520,7 +23023,6 @@
       <c r="C648" s="3" t="s">
         <v>1655</v>
       </c>
-      <c r="D648" s="4"/>
       <c r="E648" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23541,7 +23043,6 @@
       <c r="C649" s="3" t="s">
         <v>1657</v>
       </c>
-      <c r="D649" s="4"/>
       <c r="E649" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23562,7 +23063,6 @@
       <c r="C650" s="3" t="s">
         <v>1659</v>
       </c>
-      <c r="D650" s="4"/>
       <c r="E650" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23583,7 +23083,6 @@
       <c r="C651" s="3" t="s">
         <v>1661</v>
       </c>
-      <c r="D651" s="4"/>
       <c r="E651" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23604,7 +23103,6 @@
       <c r="C652" s="3" t="s">
         <v>1663</v>
       </c>
-      <c r="D652" s="4"/>
       <c r="E652" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23625,7 +23123,6 @@
       <c r="C653" s="3" t="s">
         <v>1665</v>
       </c>
-      <c r="D653" s="4"/>
       <c r="E653" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23646,7 +23143,6 @@
       <c r="C654" s="3" t="s">
         <v>1667</v>
       </c>
-      <c r="D654" s="4"/>
       <c r="E654" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23667,7 +23163,6 @@
       <c r="C655" s="3" t="s">
         <v>1669</v>
       </c>
-      <c r="D655" s="4"/>
       <c r="E655" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23688,7 +23183,6 @@
       <c r="C656" s="3" t="s">
         <v>1671</v>
       </c>
-      <c r="D656" s="4"/>
       <c r="E656" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23709,7 +23203,6 @@
       <c r="C657" s="3" t="s">
         <v>1674</v>
       </c>
-      <c r="D657" s="4"/>
       <c r="E657" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23730,7 +23223,6 @@
       <c r="C658" s="3" t="s">
         <v>1676</v>
       </c>
-      <c r="D658" s="4"/>
       <c r="E658" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23751,7 +23243,6 @@
       <c r="C659" s="3" t="s">
         <v>1678</v>
       </c>
-      <c r="D659" s="4"/>
       <c r="E659" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23769,14 +23260,12 @@
       <c r="B660" s="3" t="s">
         <v>1679</v>
       </c>
-      <c r="C660" s="3"/>
       <c r="D660" s="4" t="s">
         <v>1680</v>
       </c>
       <c r="E660" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="F660" s="2"/>
       <c r="H660" s="5" t="s">
         <v>650</v>
       </c>
@@ -23788,7 +23277,6 @@
       <c r="B661" s="3" t="s">
         <v>1681</v>
       </c>
-      <c r="C661" s="3"/>
       <c r="D661" s="4" t="s">
         <v>1680</v>
       </c>
@@ -23806,7 +23294,6 @@
       <c r="B662" s="3" t="s">
         <v>1682</v>
       </c>
-      <c r="C662" s="3"/>
       <c r="D662" s="4" t="s">
         <v>1680</v>
       </c>
@@ -23827,7 +23314,6 @@
       <c r="C663" s="3" t="s">
         <v>1684</v>
       </c>
-      <c r="D663" s="4"/>
       <c r="E663" s="2" t="s">
         <v>1211</v>
       </c>
@@ -23839,7 +23325,6 @@
       <c r="B664" s="3" t="s">
         <v>1685</v>
       </c>
-      <c r="C664" s="3"/>
       <c r="D664" s="4" t="s">
         <v>1680</v>
       </c>
@@ -23857,7 +23342,6 @@
       <c r="B665" s="3" t="s">
         <v>1686</v>
       </c>
-      <c r="C665" s="3"/>
       <c r="D665" s="4" t="s">
         <v>1680</v>
       </c>
@@ -23875,7 +23359,6 @@
       <c r="B666" s="3" t="s">
         <v>1687</v>
       </c>
-      <c r="C666" s="3"/>
       <c r="D666" s="4" t="s">
         <v>1680</v>
       </c>
@@ -23893,7 +23376,6 @@
       <c r="B667" s="3" t="s">
         <v>1688</v>
       </c>
-      <c r="C667" s="3"/>
       <c r="D667" s="4" t="s">
         <v>1689</v>
       </c>
@@ -23911,7 +23393,6 @@
       <c r="B668" s="3" t="s">
         <v>1690</v>
       </c>
-      <c r="C668" s="3"/>
       <c r="D668" s="4" t="s">
         <v>1691</v>
       </c>
@@ -23929,7 +23410,6 @@
       <c r="B669" s="3" t="s">
         <v>1692</v>
       </c>
-      <c r="C669" s="3"/>
       <c r="D669" s="4" t="s">
         <v>1693</v>
       </c>
@@ -23947,7 +23427,6 @@
       <c r="B670" s="3" t="s">
         <v>1694</v>
       </c>
-      <c r="C670" s="3"/>
       <c r="D670" s="4" t="s">
         <v>1695</v>
       </c>
@@ -23965,7 +23444,6 @@
       <c r="B671" s="3" t="s">
         <v>1696</v>
       </c>
-      <c r="C671" s="3"/>
       <c r="D671" s="4" t="s">
         <v>1695</v>
       </c>
@@ -23983,7 +23461,6 @@
       <c r="B672" s="3" t="s">
         <v>1698</v>
       </c>
-      <c r="C672" s="3"/>
       <c r="D672" s="4" t="s">
         <v>1699</v>
       </c>
@@ -24001,7 +23478,6 @@
       <c r="B673" s="3" t="s">
         <v>1701</v>
       </c>
-      <c r="C673" s="3"/>
       <c r="D673" s="4" t="s">
         <v>1702</v>
       </c>
@@ -24019,7 +23495,6 @@
       <c r="B674" s="3" t="s">
         <v>1704</v>
       </c>
-      <c r="C674" s="3"/>
       <c r="D674" s="4" t="s">
         <v>1680</v>
       </c>
@@ -24037,7 +23512,6 @@
       <c r="B675" s="3" t="s">
         <v>1706</v>
       </c>
-      <c r="C675" s="3"/>
       <c r="D675" s="4" t="s">
         <v>1680</v>
       </c>
@@ -24055,7 +23529,6 @@
       <c r="B676" s="3" t="s">
         <v>1708</v>
       </c>
-      <c r="C676" s="3"/>
       <c r="D676" s="4" t="s">
         <v>1709</v>
       </c>
@@ -24073,7 +23546,6 @@
       <c r="B677" s="3" t="s">
         <v>1711</v>
       </c>
-      <c r="C677" s="3"/>
       <c r="D677" s="4" t="s">
         <v>1712</v>
       </c>
@@ -24091,7 +23563,6 @@
       <c r="B678" s="3" t="s">
         <v>1714</v>
       </c>
-      <c r="C678" s="3"/>
       <c r="D678" s="4" t="s">
         <v>1680</v>
       </c>
@@ -24109,14 +23580,12 @@
       <c r="B679" s="3" t="s">
         <v>1716</v>
       </c>
-      <c r="C679" s="3"/>
       <c r="D679" s="4" t="s">
         <v>1717</v>
       </c>
       <c r="E679" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="F679" s="2"/>
       <c r="H679" s="5" t="s">
         <v>650</v>
       </c>
@@ -24128,14 +23597,12 @@
       <c r="B680" s="3" t="s">
         <v>1719</v>
       </c>
-      <c r="C680" s="3"/>
       <c r="D680" s="4" t="s">
         <v>1695</v>
       </c>
       <c r="E680" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="F680" s="2"/>
       <c r="H680" s="5" t="s">
         <v>650</v>
       </c>
@@ -24147,14 +23614,12 @@
       <c r="B681" s="3" t="s">
         <v>1721</v>
       </c>
-      <c r="C681" s="3"/>
       <c r="D681" s="4" t="s">
         <v>1717</v>
       </c>
       <c r="E681" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="F681" s="2"/>
       <c r="H681" s="5" t="s">
         <v>650</v>
       </c>
@@ -24163,14 +23628,12 @@
       <c r="B682" s="3" t="s">
         <v>1722</v>
       </c>
-      <c r="C682" s="3"/>
       <c r="D682" s="4" t="s">
         <v>1689</v>
       </c>
       <c r="E682" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="F682" s="2"/>
       <c r="H682" s="5" t="s">
         <v>268</v>
       </c>
@@ -24179,14 +23642,12 @@
       <c r="B683" s="3" t="s">
         <v>1723</v>
       </c>
-      <c r="C683" s="3"/>
       <c r="D683" s="4" t="s">
         <v>1689</v>
       </c>
       <c r="E683" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="F683" s="2"/>
       <c r="H683" s="5" t="s">
         <v>1237</v>
       </c>
@@ -24201,7 +23662,6 @@
       <c r="C684" s="3" t="s">
         <v>1725</v>
       </c>
-      <c r="D684" s="4"/>
       <c r="E684" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24225,7 +23685,6 @@
       <c r="C685" s="3" t="s">
         <v>1728</v>
       </c>
-      <c r="D685" s="4"/>
       <c r="E685" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24246,7 +23705,6 @@
       <c r="C686" s="3" t="s">
         <v>1731</v>
       </c>
-      <c r="D686" s="4"/>
       <c r="E686" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24267,7 +23725,6 @@
       <c r="C687" s="3" t="s">
         <v>1733</v>
       </c>
-      <c r="D687" s="4"/>
       <c r="E687" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24288,7 +23745,6 @@
       <c r="C688" s="3" t="s">
         <v>1735</v>
       </c>
-      <c r="D688" s="4"/>
       <c r="E688" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24309,7 +23765,6 @@
       <c r="C689" s="3" t="s">
         <v>1738</v>
       </c>
-      <c r="D689" s="4"/>
       <c r="E689" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24330,7 +23785,6 @@
       <c r="C690" s="3" t="s">
         <v>1740</v>
       </c>
-      <c r="D690" s="4"/>
       <c r="E690" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24354,7 +23808,6 @@
       <c r="C691" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="D691" s="4"/>
       <c r="E691" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24375,7 +23828,6 @@
       <c r="C692" s="3" t="s">
         <v>1744</v>
       </c>
-      <c r="D692" s="4"/>
       <c r="E692" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24396,7 +23848,6 @@
       <c r="C693" s="3" t="s">
         <v>1746</v>
       </c>
-      <c r="D693" s="4"/>
       <c r="E693" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24417,14 +23868,12 @@
       <c r="C694" s="3" t="s">
         <v>1748</v>
       </c>
-      <c r="D694" s="4"/>
       <c r="E694" s="2" t="s">
         <v>1726</v>
       </c>
       <c r="F694" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G694" s="5"/>
       <c r="H694" s="5" t="s">
         <v>268</v>
       </c>
@@ -24439,7 +23888,6 @@
       <c r="C695" s="3" t="s">
         <v>1750</v>
       </c>
-      <c r="D695" s="4"/>
       <c r="E695" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24460,7 +23908,6 @@
       <c r="C696" s="3" t="s">
         <v>1753</v>
       </c>
-      <c r="D696" s="4"/>
       <c r="E696" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24481,7 +23928,6 @@
       <c r="C697" s="3" t="s">
         <v>1755</v>
       </c>
-      <c r="D697" s="4"/>
       <c r="E697" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24502,7 +23948,6 @@
       <c r="C698" s="3" t="s">
         <v>1757</v>
       </c>
-      <c r="D698" s="4"/>
       <c r="E698" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24523,7 +23968,6 @@
       <c r="C699" s="3" t="s">
         <v>1759</v>
       </c>
-      <c r="D699" s="4"/>
       <c r="E699" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24547,7 +23991,6 @@
       <c r="C700" s="3" t="s">
         <v>1761</v>
       </c>
-      <c r="D700" s="4"/>
       <c r="E700" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24571,7 +24014,6 @@
       <c r="C701" s="3" t="s">
         <v>1763</v>
       </c>
-      <c r="D701" s="4"/>
       <c r="E701" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24592,7 +24034,6 @@
       <c r="C702" s="3" t="s">
         <v>1765</v>
       </c>
-      <c r="D702" s="4"/>
       <c r="E702" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24613,7 +24054,6 @@
       <c r="C703" s="3" t="s">
         <v>1767</v>
       </c>
-      <c r="D703" s="4"/>
       <c r="E703" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24637,7 +24077,6 @@
       <c r="C704" s="3" t="s">
         <v>1769</v>
       </c>
-      <c r="D704" s="4"/>
       <c r="E704" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24658,7 +24097,6 @@
       <c r="C705" s="3" t="s">
         <v>1771</v>
       </c>
-      <c r="D705" s="4"/>
       <c r="E705" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24679,7 +24117,6 @@
       <c r="C706" s="3" t="s">
         <v>1773</v>
       </c>
-      <c r="D706" s="4"/>
       <c r="E706" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24700,7 +24137,6 @@
       <c r="C707" s="3" t="s">
         <v>1775</v>
       </c>
-      <c r="D707" s="4"/>
       <c r="E707" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24724,7 +24160,6 @@
       <c r="C708" s="3" t="s">
         <v>1777</v>
       </c>
-      <c r="D708" s="4"/>
       <c r="E708" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24745,7 +24180,6 @@
       <c r="C709" s="3" t="s">
         <v>1779</v>
       </c>
-      <c r="D709" s="4"/>
       <c r="E709" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24766,7 +24200,6 @@
       <c r="C710" s="3" t="s">
         <v>1781</v>
       </c>
-      <c r="D710" s="4"/>
       <c r="E710" s="2" t="s">
         <v>1726</v>
       </c>
@@ -24784,7 +24217,6 @@
       <c r="B711" s="3" t="s">
         <v>1782</v>
       </c>
-      <c r="C711" s="3"/>
       <c r="D711" s="4" t="s">
         <v>1783</v>
       </c>
@@ -24805,7 +24237,6 @@
       <c r="C712" s="3" t="s">
         <v>1785</v>
       </c>
-      <c r="D712" s="4"/>
       <c r="E712" s="2" t="s">
         <v>1786</v>
       </c>
@@ -24826,7 +24257,6 @@
       <c r="C713" s="3" t="s">
         <v>1788</v>
       </c>
-      <c r="D713" s="4"/>
       <c r="E713" s="2" t="s">
         <v>1786</v>
       </c>
@@ -24847,14 +24277,12 @@
       <c r="C714" s="3" t="s">
         <v>1790</v>
       </c>
-      <c r="D714" s="4"/>
       <c r="E714" s="2" t="s">
         <v>1786</v>
       </c>
       <c r="F714" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G714" s="5"/>
       <c r="H714" s="5" t="s">
         <v>268</v>
       </c>
@@ -24869,7 +24297,6 @@
       <c r="C715" s="3" t="s">
         <v>1792</v>
       </c>
-      <c r="D715" s="4"/>
       <c r="E715" s="2" t="s">
         <v>1786</v>
       </c>
@@ -24890,7 +24317,6 @@
       <c r="C716" s="3" t="s">
         <v>1794</v>
       </c>
-      <c r="D716" s="4"/>
       <c r="E716" s="2" t="s">
         <v>1786</v>
       </c>
@@ -24911,7 +24337,6 @@
       <c r="C717" s="3" t="s">
         <v>1797</v>
       </c>
-      <c r="D717" s="4"/>
       <c r="E717" s="2" t="s">
         <v>1786</v>
       </c>
@@ -24932,7 +24357,6 @@
       <c r="C718" s="3" t="s">
         <v>1800</v>
       </c>
-      <c r="D718" s="4"/>
       <c r="E718" s="2" t="s">
         <v>1786</v>
       </c>
@@ -24953,7 +24377,6 @@
       <c r="C719" s="3" t="s">
         <v>1802</v>
       </c>
-      <c r="D719" s="4"/>
       <c r="E719" s="2" t="s">
         <v>1786</v>
       </c>
@@ -24974,7 +24397,6 @@
       <c r="C720" s="3" t="s">
         <v>1805</v>
       </c>
-      <c r="D720" s="4"/>
       <c r="E720" s="2" t="s">
         <v>1786</v>
       </c>
@@ -24995,7 +24417,6 @@
       <c r="C721" s="3" t="s">
         <v>1807</v>
       </c>
-      <c r="D721" s="4"/>
       <c r="E721" s="2" t="s">
         <v>1786</v>
       </c>
@@ -25016,7 +24437,6 @@
       <c r="C722" s="3" t="s">
         <v>1809</v>
       </c>
-      <c r="D722" s="4"/>
       <c r="E722" s="2" t="s">
         <v>1786</v>
       </c>
@@ -25037,7 +24457,6 @@
       <c r="C723" s="3" t="s">
         <v>1811</v>
       </c>
-      <c r="D723" s="4"/>
       <c r="E723" s="2" t="s">
         <v>1786</v>
       </c>
@@ -25058,7 +24477,6 @@
       <c r="C724" s="3" t="s">
         <v>1813</v>
       </c>
-      <c r="D724" s="4"/>
       <c r="E724" s="2" t="s">
         <v>1786</v>
       </c>
@@ -25076,7 +24494,6 @@
       <c r="C725" s="3" t="s">
         <v>1175</v>
       </c>
-      <c r="D725" s="4"/>
       <c r="E725" s="2" t="s">
         <v>1786</v>
       </c>
@@ -25091,7 +24508,6 @@
       <c r="B726" s="3" t="s">
         <v>1815</v>
       </c>
-      <c r="C726" s="3"/>
       <c r="D726" s="4" t="s">
         <v>1816</v>
       </c>
@@ -25115,7 +24531,6 @@
       <c r="D727" s="4" t="s">
         <v>1820</v>
       </c>
-      <c r="E727" s="2"/>
       <c r="F727" s="2" t="s">
         <v>12</v>
       </c>
@@ -25136,7 +24551,6 @@
       <c r="D728" s="4" t="s">
         <v>1823</v>
       </c>
-      <c r="E728" s="2"/>
       <c r="F728" s="2" t="s">
         <v>12</v>
       </c>
@@ -25157,7 +24571,6 @@
       <c r="D729" s="4" t="s">
         <v>1826</v>
       </c>
-      <c r="E729" s="2"/>
       <c r="F729" s="2" t="s">
         <v>12</v>
       </c>
@@ -25178,7 +24591,6 @@
       <c r="D730" s="4" t="s">
         <v>1829</v>
       </c>
-      <c r="E730" s="2"/>
       <c r="F730" s="2" t="s">
         <v>37</v>
       </c>
@@ -25199,7 +24611,6 @@
       <c r="D731" s="4" t="s">
         <v>1832</v>
       </c>
-      <c r="E731" s="2"/>
       <c r="F731" s="2" t="s">
         <v>37</v>
       </c>
@@ -25220,7 +24631,6 @@
       <c r="D732" s="4" t="s">
         <v>1820</v>
       </c>
-      <c r="E732" s="2"/>
       <c r="F732" s="2" t="s">
         <v>37</v>
       </c>
@@ -25241,7 +24651,6 @@
       <c r="D733" s="4" t="s">
         <v>1837</v>
       </c>
-      <c r="E733" s="2"/>
       <c r="F733" s="2" t="s">
         <v>37</v>
       </c>
@@ -25259,7 +24668,6 @@
       <c r="D734" s="4" t="s">
         <v>1840</v>
       </c>
-      <c r="E734" s="2"/>
       <c r="F734" s="2" t="s">
         <v>37</v>
       </c>
@@ -25280,7 +24688,6 @@
       <c r="D735" s="4" t="s">
         <v>1843</v>
       </c>
-      <c r="E735" s="2"/>
       <c r="F735" s="2" t="s">
         <v>59</v>
       </c>
@@ -25301,7 +24708,6 @@
       <c r="D736" s="4" t="s">
         <v>1846</v>
       </c>
-      <c r="E736" s="2"/>
       <c r="F736" s="2" t="s">
         <v>59</v>
       </c>
@@ -25322,7 +24728,6 @@
       <c r="D737" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E737" s="2"/>
       <c r="F737" s="2" t="s">
         <v>59</v>
       </c>
@@ -25340,7 +24745,6 @@
       <c r="D738" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E738" s="2"/>
       <c r="F738" s="2" t="s">
         <v>59</v>
       </c>
@@ -25361,7 +24765,6 @@
       <c r="D739" s="4" t="s">
         <v>1855</v>
       </c>
-      <c r="E739" s="2"/>
       <c r="F739" s="2" t="s">
         <v>89</v>
       </c>
@@ -25382,7 +24785,6 @@
       <c r="D740" s="4" t="s">
         <v>1858</v>
       </c>
-      <c r="E740" s="2"/>
       <c r="F740" s="2" t="s">
         <v>89</v>
       </c>
@@ -25403,7 +24805,6 @@
       <c r="D741" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E741" s="2"/>
       <c r="F741" s="2" t="s">
         <v>89</v>
       </c>
@@ -25421,7 +24822,6 @@
       <c r="D742" s="4" t="s">
         <v>1863</v>
       </c>
-      <c r="E742" s="2"/>
       <c r="F742" s="2" t="s">
         <v>89</v>
       </c>
@@ -25442,7 +24842,6 @@
       <c r="D743" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E743" s="2"/>
       <c r="F743" s="2" t="s">
         <v>89</v>
       </c>
@@ -25463,7 +24862,6 @@
       <c r="D744" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E744" s="2"/>
       <c r="F744" s="2" t="s">
         <v>89</v>
       </c>
@@ -25481,7 +24879,6 @@
       <c r="D745" s="4" t="s">
         <v>1871</v>
       </c>
-      <c r="E745" s="2"/>
       <c r="F745" s="2" t="s">
         <v>89</v>
       </c>
@@ -25499,7 +24896,6 @@
       <c r="D746" s="4" t="s">
         <v>1874</v>
       </c>
-      <c r="E746" s="2"/>
       <c r="F746" s="2" t="s">
         <v>100</v>
       </c>
@@ -25520,7 +24916,6 @@
       <c r="D747" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E747" s="2"/>
       <c r="F747" s="2" t="s">
         <v>1878</v>
       </c>
@@ -25541,7 +24936,6 @@
       <c r="D748" s="4" t="s">
         <v>1881</v>
       </c>
-      <c r="E748" s="2"/>
       <c r="F748" s="2" t="s">
         <v>117</v>
       </c>
@@ -25562,7 +24956,6 @@
       <c r="D749" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E749" s="2"/>
       <c r="F749" s="2" t="s">
         <v>117</v>
       </c>
@@ -25580,7 +24973,6 @@
       <c r="D750" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E750" s="2"/>
       <c r="F750" s="2" t="s">
         <v>117</v>
       </c>
@@ -25601,7 +24993,6 @@
       <c r="D751" s="4" t="s">
         <v>1888</v>
       </c>
-      <c r="E751" s="2"/>
       <c r="F751" s="2" t="s">
         <v>117</v>
       </c>
@@ -25622,7 +25013,6 @@
       <c r="D752" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E752" s="2"/>
       <c r="F752" s="2" t="s">
         <v>117</v>
       </c>
@@ -25637,7 +25027,6 @@
       <c r="D753" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E753" s="2"/>
       <c r="F753" s="2" t="s">
         <v>117</v>
       </c>
@@ -25655,7 +25044,6 @@
       <c r="D754" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E754" s="2"/>
       <c r="F754" s="2" t="s">
         <v>117</v>
       </c>
@@ -25673,7 +25061,6 @@
       <c r="D755" s="4" t="s">
         <v>1840</v>
       </c>
-      <c r="E755" s="2"/>
       <c r="F755" s="2" t="s">
         <v>117</v>
       </c>
@@ -25691,7 +25078,6 @@
       <c r="D756" s="4" t="s">
         <v>1888</v>
       </c>
-      <c r="E756" s="2"/>
       <c r="F756" s="2" t="s">
         <v>117</v>
       </c>
@@ -25712,7 +25098,6 @@
       <c r="D757" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E757" s="2"/>
       <c r="F757" s="2" t="s">
         <v>149</v>
       </c>
@@ -25733,7 +25118,6 @@
       <c r="D758" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E758" s="2"/>
       <c r="F758" s="2" t="s">
         <v>153</v>
       </c>
@@ -25754,7 +25138,6 @@
       <c r="D759" s="4" t="s">
         <v>1858</v>
       </c>
-      <c r="E759" s="2"/>
       <c r="F759" s="2" t="s">
         <v>164</v>
       </c>
@@ -25775,7 +25158,6 @@
       <c r="D760" s="4" t="s">
         <v>1907</v>
       </c>
-      <c r="E760" s="2"/>
       <c r="F760" s="2" t="s">
         <v>194</v>
       </c>
@@ -25793,7 +25175,6 @@
       <c r="D761" s="4" t="s">
         <v>1910</v>
       </c>
-      <c r="E761" s="2"/>
       <c r="F761" s="2" t="s">
         <v>194</v>
       </c>
@@ -25811,7 +25192,6 @@
       <c r="D762" s="4" t="s">
         <v>1910</v>
       </c>
-      <c r="E762" s="2"/>
       <c r="F762" s="2" t="s">
         <v>194</v>
       </c>
@@ -25832,7 +25212,6 @@
       <c r="D763" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E763" s="2"/>
       <c r="F763" s="2" t="s">
         <v>215</v>
       </c>
@@ -25853,11 +25232,9 @@
       <c r="D764" s="4" t="s">
         <v>1843</v>
       </c>
-      <c r="E764" s="2"/>
       <c r="F764" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G764" s="5"/>
       <c r="H764" s="5" t="s">
         <v>305</v>
       </c>
@@ -25875,7 +25252,6 @@
       <c r="D765" s="4" t="s">
         <v>1850</v>
       </c>
-      <c r="E765" s="2"/>
       <c r="F765" s="2" t="s">
         <v>244</v>
       </c>
@@ -25896,7 +25272,6 @@
       <c r="D766" s="4" t="s">
         <v>1921</v>
       </c>
-      <c r="E766" s="2"/>
       <c r="F766" s="2" t="s">
         <v>244</v>
       </c>
@@ -25998,11 +25373,9 @@
       <c r="B773" s="3" t="s">
         <v>1941</v>
       </c>
-      <c r="C773" s="3"/>
       <c r="D773" s="4" t="s">
         <v>1942</v>
       </c>
-      <c r="E773" s="2"/>
       <c r="H773" s="5" t="s">
         <v>346</v>
       </c>
@@ -26342,7 +25715,6 @@
       <c r="D797" s="4" t="s">
         <v>2014</v>
       </c>
-      <c r="E797" s="2"/>
       <c r="H797" s="5" t="s">
         <v>2015</v>
       </c>
@@ -26598,8 +25970,6 @@
       <c r="D815" s="4" t="s">
         <v>2068</v>
       </c>
-      <c r="E815" s="2"/>
-      <c r="F815" s="2"/>
       <c r="H815" s="5" t="s">
         <v>2069</v>
       </c>
@@ -26715,8 +26085,6 @@
       <c r="D823" s="4" t="s">
         <v>2093</v>
       </c>
-      <c r="E823" s="2"/>
-      <c r="F823" s="2"/>
       <c r="G823" s="5" t="s">
         <v>2094</v>
       </c>
@@ -29838,7 +29206,6 @@
       <c r="B1030" s="3" t="s">
         <v>2706</v>
       </c>
-      <c r="C1030" s="3"/>
       <c r="D1030" s="4" t="s">
         <v>2707</v>
       </c>
@@ -29899,7 +29266,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I1030" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:I1030">
+    <sortState ref="A1:I1030">
       <sortCondition ref="E1"/>
     </sortState>
     <extLst/>
@@ -29910,7 +29277,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B1031:I1125 B1:I1" numberStoredAsText="1"/>
+    <ignoredError sqref="B1:I1 B1031:I1125" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/xlsx/CPE.xlsx
+++ b/xlsx/CPE.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Wq &amp; H" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wq &amp; H'!$A$1:$I$1030</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wq &amp; H'!$A$1:$I$1125</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -8474,13 +8474,20 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="OPPO Sans 4.0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -8966,16 +8973,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8984,160 +8988,172 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -9680,45 +9696,42 @@
     <col min="1" max="1" width="10.981981981982" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.2342342342342" style="3" customWidth="1"/>
     <col min="3" max="3" width="10.9189189189189" style="3" customWidth="1"/>
-    <col min="4" max="4" width="25.018018018018" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13.5315315315315" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.6126126126126" style="2" customWidth="1"/>
-    <col min="7" max="7" width="63.4684684684685" style="5" customWidth="1"/>
-    <col min="8" max="8" width="22.7657657657658" style="5" customWidth="1"/>
-    <col min="9" max="9" width="30.4594594594595" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="8.61261261261261" style="2"/>
+    <col min="4" max="4" width="23.7027027027027" style="4" customWidth="1"/>
+    <col min="5" max="6" width="11.6576576576577" style="2" customWidth="1"/>
+    <col min="7" max="9" width="23.7027027027027" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.61261261261261" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:9">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" ht="30" customHeight="1" spans="1:9">
       <c r="A2" s="2">
         <v>1740</v>
       </c>
@@ -9741,7 +9754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" ht="30" customHeight="1" spans="1:9">
       <c r="A3" s="2">
         <v>1741</v>
       </c>
@@ -9764,7 +9777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" ht="30" customHeight="1" spans="1:9">
       <c r="A4" s="2">
         <v>1746</v>
       </c>
@@ -9790,7 +9803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" ht="30" customHeight="1" spans="1:9">
       <c r="A5" s="2">
         <v>1753</v>
       </c>
@@ -9816,7 +9829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" ht="30" customHeight="1" spans="1:9">
       <c r="A6" s="2">
         <v>1753</v>
       </c>
@@ -9842,7 +9855,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" ht="30" customHeight="1" spans="1:9">
       <c r="A7" s="2">
         <v>1753</v>
       </c>
@@ -9868,8 +9881,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="6">
+    <row r="8" ht="30" customHeight="1" spans="1:9">
+      <c r="A8" s="9">
         <v>1733</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -9894,8 +9907,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="6">
+    <row r="9" ht="30" customHeight="1" spans="1:9">
+      <c r="A9" s="9">
         <v>1747</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -9917,7 +9930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="2">
         <v>1750</v>
       </c>
@@ -9943,7 +9956,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="2">
         <v>1750</v>
       </c>
@@ -9969,7 +9982,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="2">
         <v>1750</v>
       </c>
@@ -9995,7 +10008,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="2">
         <v>1753</v>
       </c>
@@ -10018,7 +10031,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="2">
         <v>1742</v>
       </c>
@@ -10041,7 +10054,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="2">
         <v>1749</v>
       </c>
@@ -10067,7 +10080,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="2">
         <v>1751</v>
       </c>
@@ -10093,7 +10106,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" ht="30" customHeight="1" spans="1:9">
       <c r="A17" s="2">
         <v>1751</v>
       </c>
@@ -10119,7 +10132,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" ht="30" customHeight="1" spans="1:9">
       <c r="A18" s="2">
         <v>1753</v>
       </c>
@@ -10141,11 +10154,11 @@
       <c r="H18" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" ht="30" customHeight="1" spans="1:9">
       <c r="A19" s="2">
         <v>1762</v>
       </c>
@@ -10168,7 +10181,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" ht="30" customHeight="1" spans="1:9">
       <c r="A20" s="2">
         <v>1765</v>
       </c>
@@ -10194,7 +10207,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" ht="30" customHeight="1" spans="1:9">
       <c r="A21" s="2">
         <v>1765</v>
       </c>
@@ -10220,7 +10233,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" ht="30" customHeight="1" spans="1:9">
       <c r="A22" s="2">
         <v>1746</v>
       </c>
@@ -10243,7 +10256,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" ht="30" customHeight="1" spans="1:9">
       <c r="A23" s="2">
         <v>1765</v>
       </c>
@@ -10263,7 +10276,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" ht="30" customHeight="1" spans="1:9">
       <c r="A24" s="2">
         <v>1771</v>
       </c>
@@ -10286,8 +10299,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="6">
+    <row r="25" ht="30" customHeight="1" spans="1:9">
+      <c r="A25" s="9">
         <v>1739</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -10312,7 +10325,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" ht="30" customHeight="1" spans="1:9">
       <c r="A26" s="2">
         <v>1753</v>
       </c>
@@ -10335,7 +10348,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" ht="30" customHeight="1" spans="1:9">
       <c r="A27" s="2">
         <v>1762</v>
       </c>
@@ -10358,7 +10371,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" ht="30" customHeight="1" spans="1:9">
       <c r="A28" s="2">
         <v>1771</v>
       </c>
@@ -10384,7 +10397,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" ht="30" customHeight="1" spans="1:9">
       <c r="A29" s="2">
         <v>1743</v>
       </c>
@@ -10410,7 +10423,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" ht="30" customHeight="1" spans="1:9">
       <c r="A30" s="2">
         <v>1744</v>
       </c>
@@ -10436,7 +10449,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" ht="30" customHeight="1" spans="1:9">
       <c r="A31" s="2">
         <v>1745</v>
       </c>
@@ -10462,7 +10475,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" ht="30" customHeight="1" spans="1:9">
       <c r="A32" s="2">
         <v>1750</v>
       </c>
@@ -10488,7 +10501,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" ht="30" customHeight="1" spans="1:9">
       <c r="A33" s="2">
         <v>1771</v>
       </c>
@@ -10510,11 +10523,11 @@
       <c r="H33" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I33" s="10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" ht="30" customHeight="1" spans="1:9">
       <c r="A34" s="2">
         <v>1778</v>
       </c>
@@ -10537,7 +10550,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" ht="30" customHeight="1" spans="1:9">
       <c r="A35" s="2">
         <v>1745</v>
       </c>
@@ -10560,7 +10573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" ht="30" customHeight="1" spans="1:9">
       <c r="A36" s="2">
         <v>1747</v>
       </c>
@@ -10583,7 +10596,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" ht="30" customHeight="1" spans="1:9">
       <c r="A37" s="2">
         <v>1748</v>
       </c>
@@ -10609,7 +10622,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" ht="30" customHeight="1" spans="1:9">
       <c r="A38" s="2">
         <v>1744</v>
       </c>
@@ -10632,7 +10645,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" ht="30" customHeight="1" spans="1:9">
       <c r="A39" s="2">
         <v>1745</v>
       </c>
@@ -10655,7 +10668,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" ht="30" customHeight="1" spans="1:9">
       <c r="A40" s="2">
         <v>1748</v>
       </c>
@@ -10681,7 +10694,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" ht="30" customHeight="1" spans="1:9">
       <c r="B41" s="3" t="s">
         <v>159</v>
       </c>
@@ -10699,8 +10712,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="6">
+    <row r="42" ht="30" customHeight="1" spans="1:9">
+      <c r="A42" s="9">
         <v>1734</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -10725,7 +10738,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" ht="30" customHeight="1" spans="1:9">
       <c r="A43" s="2">
         <v>1759</v>
       </c>
@@ -10751,7 +10764,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" ht="30" customHeight="1" spans="1:9">
       <c r="A44" s="2">
         <v>1765</v>
       </c>
@@ -10777,7 +10790,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" ht="30" customHeight="1" spans="1:9">
       <c r="A45" s="2">
         <v>1765</v>
       </c>
@@ -10803,7 +10816,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" ht="30" customHeight="1" spans="1:9">
       <c r="A46" s="2">
         <v>1769</v>
       </c>
@@ -10826,7 +10839,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" ht="30" customHeight="1" spans="1:9">
       <c r="A47" s="2">
         <v>1771</v>
       </c>
@@ -10848,11 +10861,11 @@
       <c r="H47" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I47" s="7" t="s">
+      <c r="I47" s="10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" ht="30" customHeight="1" spans="1:9">
       <c r="A48" s="2">
         <v>1788</v>
       </c>
@@ -10881,7 +10894,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" ht="30" customHeight="1" spans="1:9">
       <c r="A49" s="2">
         <v>1740</v>
       </c>
@@ -10910,7 +10923,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" ht="30" customHeight="1" spans="1:9">
       <c r="A50" s="2">
         <v>1744</v>
       </c>
@@ -10933,7 +10946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" ht="30" customHeight="1" spans="1:9">
       <c r="A51" s="2">
         <v>1755</v>
       </c>
@@ -10956,7 +10969,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" ht="30" customHeight="1" spans="1:9">
       <c r="A52" s="2">
         <v>1763</v>
       </c>
@@ -10979,7 +10992,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" ht="30" customHeight="1" spans="1:9">
       <c r="A53" s="2">
         <v>1770</v>
       </c>
@@ -11002,7 +11015,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" ht="30" customHeight="1" spans="1:9">
       <c r="A54" s="2">
         <v>1771</v>
       </c>
@@ -11025,8 +11038,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6">
+    <row r="55" ht="30" customHeight="1" spans="1:9">
+      <c r="A55" s="9">
         <v>1737</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -11051,7 +11064,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" ht="30" customHeight="1" spans="1:9">
       <c r="A56" s="2">
         <v>1738</v>
       </c>
@@ -11074,7 +11087,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" ht="30" customHeight="1" spans="1:9">
       <c r="A57" s="2">
         <v>1742</v>
       </c>
@@ -11100,7 +11113,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" ht="30" customHeight="1" spans="1:9">
       <c r="A58" s="2">
         <v>1745</v>
       </c>
@@ -11126,7 +11139,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" ht="30" customHeight="1" spans="1:9">
       <c r="A59" s="2">
         <v>1755</v>
       </c>
@@ -11152,7 +11165,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" ht="30" customHeight="1" spans="1:9">
       <c r="A60" s="2">
         <v>1755</v>
       </c>
@@ -11174,11 +11187,11 @@
       <c r="H60" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I60" s="7" t="s">
+      <c r="I60" s="10" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" ht="30" customHeight="1" spans="1:9">
       <c r="A61" s="2">
         <v>1771</v>
       </c>
@@ -11204,7 +11217,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" ht="30" customHeight="1" spans="1:9">
       <c r="A62" s="2">
         <v>1778</v>
       </c>
@@ -11227,7 +11240,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" ht="30" customHeight="1" spans="1:9">
       <c r="A63" s="2">
         <v>1740</v>
       </c>
@@ -11250,7 +11263,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" ht="30" customHeight="1" spans="1:9">
       <c r="A64" s="2">
         <v>1754</v>
       </c>
@@ -11276,7 +11289,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" ht="30" customHeight="1" spans="1:9">
       <c r="B65" s="3" t="s">
         <v>250</v>
       </c>
@@ -11294,7 +11307,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" ht="30" customHeight="1" spans="1:9">
       <c r="A66" s="2">
         <v>1771</v>
       </c>
@@ -11311,7 +11324,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" ht="30" customHeight="1" spans="1:9">
       <c r="B67" s="3" t="s">
         <v>254</v>
       </c>
@@ -11325,7 +11338,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" ht="30" customHeight="1" spans="1:9">
       <c r="A68" s="2">
         <v>1768</v>
       </c>
@@ -11348,7 +11361,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" ht="30" customHeight="1" spans="1:9">
       <c r="A69" s="2">
         <v>1775</v>
       </c>
@@ -11368,7 +11381,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" ht="30" customHeight="1" spans="1:9">
       <c r="A70" s="2" t="s">
         <v>265</v>
       </c>
@@ -11391,7 +11404,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" ht="30" customHeight="1" spans="1:9">
       <c r="A71" s="2" t="s">
         <v>265</v>
       </c>
@@ -11414,7 +11427,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" ht="30" customHeight="1" spans="1:9">
       <c r="A72" s="2">
         <v>1762.5</v>
       </c>
@@ -11437,7 +11450,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" ht="30" customHeight="1" spans="1:9">
       <c r="A73" s="2">
         <v>1762.5</v>
       </c>
@@ -11460,7 +11473,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" ht="30" customHeight="1" spans="1:9">
       <c r="A74" s="2">
         <v>1762.5</v>
       </c>
@@ -11483,7 +11496,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" ht="30" customHeight="1" spans="1:9">
       <c r="A75" s="2">
         <v>1765</v>
       </c>
@@ -11506,7 +11519,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" ht="30" customHeight="1" spans="1:9">
       <c r="A76" s="2">
         <v>1775</v>
       </c>
@@ -11526,7 +11539,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" ht="30" customHeight="1" spans="1:9">
       <c r="A77" s="2" t="s">
         <v>265</v>
       </c>
@@ -11549,7 +11562,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" ht="30" customHeight="1" spans="1:9">
       <c r="A78" s="2">
         <v>1766</v>
       </c>
@@ -11572,7 +11585,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" ht="30" customHeight="1" spans="1:9">
       <c r="A79" s="2">
         <v>1766</v>
       </c>
@@ -11595,7 +11608,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" ht="30" customHeight="1" spans="1:9">
       <c r="A80" s="2">
         <v>1762.5</v>
       </c>
@@ -11618,7 +11631,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" ht="30" customHeight="1" spans="1:8">
       <c r="A81" s="2">
         <v>1762.5</v>
       </c>
@@ -11641,7 +11654,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" ht="30" customHeight="1" spans="1:8">
       <c r="A82" s="2">
         <v>1762.5</v>
       </c>
@@ -11664,7 +11677,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" ht="30" customHeight="1" spans="1:8">
       <c r="A83" s="2">
         <v>1765</v>
       </c>
@@ -11687,7 +11700,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" ht="30" customHeight="1" spans="1:8">
       <c r="A84" s="2">
         <v>1766</v>
       </c>
@@ -11710,7 +11723,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" ht="30" customHeight="1" spans="1:8">
       <c r="A85" s="2">
         <v>1766</v>
       </c>
@@ -11733,7 +11746,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" ht="30" customHeight="1" spans="1:8">
       <c r="A86" s="2">
         <v>1767</v>
       </c>
@@ -11756,7 +11769,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" ht="30" customHeight="1" spans="1:8">
       <c r="A87" s="2">
         <v>1769</v>
       </c>
@@ -11779,7 +11792,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" ht="30" customHeight="1" spans="1:8">
       <c r="A88" s="2">
         <v>1775</v>
       </c>
@@ -11802,7 +11815,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" ht="30" customHeight="1" spans="1:8">
       <c r="A89" s="2" t="s">
         <v>265</v>
       </c>
@@ -11825,7 +11838,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" ht="30" customHeight="1" spans="1:8">
       <c r="B90" s="3" t="s">
         <v>311</v>
       </c>
@@ -11842,7 +11855,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" ht="30" customHeight="1" spans="1:8">
       <c r="A91" s="2">
         <v>1763</v>
       </c>
@@ -11865,7 +11878,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" ht="30" customHeight="1" spans="1:8">
       <c r="A92" s="2">
         <v>1767</v>
       </c>
@@ -11888,7 +11901,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" ht="30" customHeight="1" spans="1:8">
       <c r="A93" s="2">
         <v>1775</v>
       </c>
@@ -11908,7 +11921,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" ht="30" customHeight="1" spans="1:8">
       <c r="A94" s="2">
         <v>1775</v>
       </c>
@@ -11928,7 +11941,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" ht="30" customHeight="1" spans="1:8">
       <c r="A95" s="2" t="s">
         <v>265</v>
       </c>
@@ -11951,7 +11964,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" ht="30" customHeight="1" spans="1:8">
       <c r="A96" s="2">
         <v>1769</v>
       </c>
@@ -11974,7 +11987,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" ht="30" customHeight="1" spans="1:8">
       <c r="A97" s="2">
         <v>1775</v>
       </c>
@@ -11994,7 +12007,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" ht="30" customHeight="1" spans="1:8">
       <c r="A98" s="2" t="s">
         <v>265</v>
       </c>
@@ -12017,7 +12030,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" ht="30" customHeight="1" spans="1:8">
       <c r="A99" s="2">
         <v>1766</v>
       </c>
@@ -12040,7 +12053,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" ht="30" customHeight="1" spans="1:8">
       <c r="A100" s="2">
         <v>1766</v>
       </c>
@@ -12063,7 +12076,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" ht="30" customHeight="1" spans="1:8">
       <c r="A101" s="2">
         <v>1775</v>
       </c>
@@ -12086,7 +12099,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" ht="30" customHeight="1" spans="1:8">
       <c r="A102" s="2">
         <v>1760</v>
       </c>
@@ -12109,7 +12122,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" ht="30" customHeight="1" spans="1:8">
       <c r="A103" s="2">
         <v>1762.5</v>
       </c>
@@ -12132,7 +12145,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" ht="30" customHeight="1" spans="1:8">
       <c r="A104" s="2">
         <v>1762.5</v>
       </c>
@@ -12155,7 +12168,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" ht="30" customHeight="1" spans="1:8">
       <c r="A105" s="2">
         <v>1762.8</v>
       </c>
@@ -12172,7 +12185,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" ht="30" customHeight="1" spans="1:8">
       <c r="A106" s="2">
         <v>1767</v>
       </c>
@@ -12192,7 +12205,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" ht="30" customHeight="1" spans="1:8">
       <c r="A107" s="2">
         <v>1767</v>
       </c>
@@ -12212,7 +12225,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" ht="30" customHeight="1" spans="1:8">
       <c r="B108" s="3" t="s">
         <v>353</v>
       </c>
@@ -12229,7 +12242,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" ht="30" customHeight="1" spans="1:8">
       <c r="A109" s="2">
         <v>1752</v>
       </c>
@@ -12249,7 +12262,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" ht="30" customHeight="1" spans="1:8">
       <c r="A110" s="2">
         <v>1748</v>
       </c>
@@ -12269,7 +12282,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" ht="30" customHeight="1" spans="1:8">
       <c r="A111" s="2">
         <v>1767</v>
       </c>
@@ -12289,7 +12302,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" ht="30" customHeight="1" spans="1:8">
       <c r="A112" s="2">
         <v>1767</v>
       </c>
@@ -12309,7 +12322,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" ht="30" customHeight="1" spans="1:8">
       <c r="A113" s="2">
         <v>1767</v>
       </c>
@@ -12323,7 +12336,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" ht="30" customHeight="1" spans="1:8">
       <c r="A114" s="2">
         <v>1782</v>
       </c>
@@ -12343,7 +12356,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" ht="30" customHeight="1" spans="1:8">
       <c r="A115" s="2">
         <v>1759</v>
       </c>
@@ -12363,7 +12376,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" ht="30" customHeight="1" spans="1:8">
       <c r="A116" s="2">
         <v>1759</v>
       </c>
@@ -12383,7 +12396,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" ht="30" customHeight="1" spans="1:8">
       <c r="A117" s="2">
         <v>1786</v>
       </c>
@@ -12403,7 +12416,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" ht="30" customHeight="1" spans="1:8">
       <c r="A118" s="2">
         <v>1784</v>
       </c>
@@ -12423,7 +12436,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" ht="30" customHeight="1" spans="1:8">
       <c r="A119" s="2">
         <v>1786</v>
       </c>
@@ -12443,7 +12456,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" ht="30" customHeight="1" spans="1:8">
       <c r="A120" s="2">
         <v>1754</v>
       </c>
@@ -12466,7 +12479,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" ht="30" customHeight="1" spans="1:8">
       <c r="A121" s="2">
         <v>1759</v>
       </c>
@@ -12486,7 +12499,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" ht="30" customHeight="1" spans="1:8">
       <c r="A122" s="2">
         <v>1759</v>
       </c>
@@ -12506,7 +12519,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" ht="30" customHeight="1" spans="1:8">
       <c r="A123" s="2">
         <v>1762</v>
       </c>
@@ -12526,7 +12539,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" ht="30" customHeight="1" spans="1:8">
       <c r="A124" s="2">
         <v>1765</v>
       </c>
@@ -12546,7 +12559,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" ht="30" customHeight="1" spans="1:8">
       <c r="A125" s="2">
         <v>1765</v>
       </c>
@@ -12566,7 +12579,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" ht="30" customHeight="1" spans="1:8">
       <c r="A126" s="2">
         <v>1766</v>
       </c>
@@ -12586,7 +12599,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" ht="30" customHeight="1" spans="1:8">
       <c r="A127" s="2">
         <v>1767</v>
       </c>
@@ -12606,7 +12619,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" ht="30" customHeight="1" spans="1:8">
       <c r="A128" s="2">
         <v>1767</v>
       </c>
@@ -12626,7 +12639,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" ht="30" customHeight="1" spans="1:8">
       <c r="A129" s="2">
         <v>1782</v>
       </c>
@@ -12646,7 +12659,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" ht="30" customHeight="1" spans="1:8">
       <c r="A130" s="2">
         <v>1759</v>
       </c>
@@ -12666,7 +12679,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" ht="30" customHeight="1" spans="1:8">
       <c r="A131" s="2">
         <v>1759</v>
       </c>
@@ -12686,7 +12699,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" ht="30" customHeight="1" spans="1:8">
       <c r="A132" s="2">
         <v>1782</v>
       </c>
@@ -12706,7 +12719,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" ht="30" customHeight="1" spans="1:8">
       <c r="A133" s="2">
         <v>1787</v>
       </c>
@@ -12726,7 +12739,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" ht="30" customHeight="1" spans="1:8">
       <c r="A134" s="2">
         <v>1787</v>
       </c>
@@ -12749,7 +12762,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" ht="30" customHeight="1" spans="1:8">
       <c r="A135" s="2">
         <v>1766</v>
       </c>
@@ -12769,7 +12782,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" ht="30" customHeight="1" spans="1:8">
       <c r="A136" s="2">
         <v>1766</v>
       </c>
@@ -12789,7 +12802,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" ht="30" customHeight="1" spans="1:8">
       <c r="A137" s="2">
         <v>1760</v>
       </c>
@@ -12812,7 +12825,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" ht="30" customHeight="1" spans="1:8">
       <c r="A138" s="2">
         <v>1750</v>
       </c>
@@ -12835,7 +12848,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" ht="30" customHeight="1" spans="1:8">
       <c r="A139" s="2">
         <v>1777</v>
       </c>
@@ -12858,7 +12871,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" ht="30" customHeight="1" spans="1:8">
       <c r="A140" s="2">
         <v>1778</v>
       </c>
@@ -12881,7 +12894,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" ht="30" customHeight="1" spans="1:8">
       <c r="A141" s="2">
         <v>1747</v>
       </c>
@@ -12904,7 +12917,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" ht="30" customHeight="1" spans="1:8">
       <c r="A142" s="2">
         <v>1752</v>
       </c>
@@ -12927,7 +12940,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" ht="30" customHeight="1" spans="1:8">
       <c r="A143" s="2">
         <v>1781</v>
       </c>
@@ -12950,7 +12963,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" ht="30" customHeight="1" spans="1:8">
       <c r="A144" s="2">
         <v>1766</v>
       </c>
@@ -12973,7 +12986,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" ht="30" customHeight="1" spans="1:8">
       <c r="B145" s="3" t="s">
         <v>438</v>
       </c>
@@ -12984,7 +12997,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" ht="30" customHeight="1" spans="1:8">
       <c r="A146" s="2">
         <v>1755</v>
       </c>
@@ -13007,7 +13020,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" ht="30" customHeight="1" spans="1:8">
       <c r="A147" s="2">
         <v>1755</v>
       </c>
@@ -13030,7 +13043,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" ht="30" customHeight="1" spans="1:8">
       <c r="A148" s="2">
         <v>1755</v>
       </c>
@@ -13053,7 +13066,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" ht="30" customHeight="1" spans="1:8">
       <c r="A149" s="2">
         <v>1765</v>
       </c>
@@ -13076,7 +13089,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" ht="30" customHeight="1" spans="1:8">
       <c r="A150" s="2">
         <v>1766</v>
       </c>
@@ -13099,7 +13112,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" ht="30" customHeight="1" spans="1:8">
       <c r="A151" s="2">
         <v>1767</v>
       </c>
@@ -13122,7 +13135,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" ht="30" customHeight="1" spans="1:8">
       <c r="A152" s="2">
         <v>1770</v>
       </c>
@@ -13145,7 +13158,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" ht="30" customHeight="1" spans="1:8">
       <c r="A153" s="2">
         <v>1782</v>
       </c>
@@ -13168,7 +13181,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" ht="30" customHeight="1" spans="1:8">
       <c r="A154" s="2" t="s">
         <v>265</v>
       </c>
@@ -13191,7 +13204,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" ht="30" customHeight="1" spans="1:8">
       <c r="A155" s="2">
         <v>1755</v>
       </c>
@@ -13214,7 +13227,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" ht="30" customHeight="1" spans="1:8">
       <c r="A156" s="2">
         <v>1755</v>
       </c>
@@ -13237,7 +13250,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" ht="30" customHeight="1" spans="1:8">
       <c r="A157" s="2">
         <v>1778</v>
       </c>
@@ -13260,7 +13273,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" ht="30" customHeight="1" spans="1:8">
       <c r="A158" s="2" t="s">
         <v>265</v>
       </c>
@@ -13283,7 +13296,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" ht="30" customHeight="1" spans="1:8">
       <c r="A159" s="2" t="s">
         <v>265</v>
       </c>
@@ -13306,7 +13319,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" ht="30" customHeight="1" spans="1:8">
       <c r="A160" s="2">
         <v>1755</v>
       </c>
@@ -13329,7 +13342,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" ht="30" customHeight="1" spans="1:8">
       <c r="A161" s="2">
         <v>1756</v>
       </c>
@@ -13352,7 +13365,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" ht="30" customHeight="1" spans="1:8">
       <c r="A162" s="2">
         <v>1757</v>
       </c>
@@ -13375,7 +13388,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" ht="30" customHeight="1" spans="1:8">
       <c r="A163" s="2">
         <v>1765</v>
       </c>
@@ -13398,7 +13411,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" ht="30" customHeight="1" spans="1:8">
       <c r="A164" s="2">
         <v>1767</v>
       </c>
@@ -13421,7 +13434,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" ht="30" customHeight="1" spans="1:8">
       <c r="A165" s="2">
         <v>1775</v>
       </c>
@@ -13444,7 +13457,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" ht="30" customHeight="1" spans="1:8">
       <c r="A166" s="2">
         <v>1779</v>
       </c>
@@ -13467,7 +13480,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" ht="30" customHeight="1" spans="1:8">
       <c r="A167" s="2" t="s">
         <v>265</v>
       </c>
@@ -13490,7 +13503,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" ht="30" customHeight="1" spans="1:8">
       <c r="A168" s="2">
         <v>1754</v>
       </c>
@@ -13513,7 +13526,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" ht="30" customHeight="1" spans="1:8">
       <c r="A169" s="2">
         <v>1755</v>
       </c>
@@ -13536,7 +13549,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" ht="30" customHeight="1" spans="1:8">
       <c r="A170" s="2">
         <v>1755</v>
       </c>
@@ -13559,7 +13572,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" ht="30" customHeight="1" spans="1:8">
       <c r="A171" s="2">
         <v>1759</v>
       </c>
@@ -13582,7 +13595,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" ht="30" customHeight="1" spans="1:8">
       <c r="A172" s="2">
         <v>1759</v>
       </c>
@@ -13605,7 +13618,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" ht="30" customHeight="1" spans="1:8">
       <c r="A173" s="2">
         <v>1767</v>
       </c>
@@ -13628,7 +13641,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" ht="30" customHeight="1" spans="1:8">
       <c r="A174" s="2">
         <v>1775</v>
       </c>
@@ -13651,7 +13664,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" ht="30" customHeight="1" spans="1:8">
       <c r="A175" s="2">
         <v>1778</v>
       </c>
@@ -13674,7 +13687,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" ht="30" customHeight="1" spans="1:8">
       <c r="A176" s="2" t="s">
         <v>265</v>
       </c>
@@ -13697,7 +13710,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" ht="30" customHeight="1" spans="1:8">
       <c r="A177" s="2" t="s">
         <v>265</v>
       </c>
@@ -13720,7 +13733,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" ht="30" customHeight="1" spans="1:8">
       <c r="A178" s="2" t="s">
         <v>265</v>
       </c>
@@ -13743,7 +13756,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" ht="30" customHeight="1" spans="1:8">
       <c r="A179" s="2">
         <v>1756</v>
       </c>
@@ -13766,7 +13779,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" ht="30" customHeight="1" spans="1:8">
       <c r="A180" s="2">
         <v>1756</v>
       </c>
@@ -13789,7 +13802,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" ht="30" customHeight="1" spans="1:8">
       <c r="A181" s="2">
         <v>1766</v>
       </c>
@@ -13812,7 +13825,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" ht="30" customHeight="1" spans="1:8">
       <c r="A182" s="2">
         <v>1767</v>
       </c>
@@ -13835,7 +13848,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" ht="30" customHeight="1" spans="1:8">
       <c r="A183" s="2">
         <v>1784</v>
       </c>
@@ -13858,7 +13871,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" ht="30" customHeight="1" spans="1:8">
       <c r="A184" s="2">
         <v>1757</v>
       </c>
@@ -13881,7 +13894,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" ht="30" customHeight="1" spans="1:8">
       <c r="A185" s="2">
         <v>1754</v>
       </c>
@@ -13904,7 +13917,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" ht="30" customHeight="1" spans="1:8">
       <c r="A186" s="2">
         <v>1756</v>
       </c>
@@ -13927,7 +13940,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" ht="30" customHeight="1" spans="1:8">
       <c r="A187" s="2">
         <v>1757</v>
       </c>
@@ -13950,7 +13963,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" ht="30" customHeight="1" spans="1:8">
       <c r="A188" s="2">
         <v>1765</v>
       </c>
@@ -13973,7 +13986,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" ht="30" customHeight="1" spans="1:8">
       <c r="A189" s="2">
         <v>1775</v>
       </c>
@@ -13996,7 +14009,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" ht="30" customHeight="1" spans="1:8">
       <c r="A190" s="2">
         <v>1775</v>
       </c>
@@ -14019,7 +14032,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" ht="30" customHeight="1" spans="1:8">
       <c r="A191" s="2">
         <v>1778</v>
       </c>
@@ -14042,7 +14055,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" ht="30" customHeight="1" spans="1:8">
       <c r="A192" s="2" t="s">
         <v>265</v>
       </c>
@@ -14065,7 +14078,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" ht="30" customHeight="1" spans="1:8">
       <c r="A193" s="2" t="s">
         <v>265</v>
       </c>
@@ -14088,7 +14101,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" ht="30" customHeight="1" spans="1:8">
       <c r="A194" s="2">
         <v>1755</v>
       </c>
@@ -14111,7 +14124,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" ht="30" customHeight="1" spans="1:8">
       <c r="A195" s="2">
         <v>1755</v>
       </c>
@@ -14134,7 +14147,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" ht="30" customHeight="1" spans="1:8">
       <c r="A196" s="2">
         <v>1755</v>
       </c>
@@ -14157,7 +14170,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" ht="30" customHeight="1" spans="1:8">
       <c r="A197" s="2">
         <v>1765</v>
       </c>
@@ -14180,7 +14193,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" ht="30" customHeight="1" spans="1:8">
       <c r="A198" s="2">
         <v>1767</v>
       </c>
@@ -14203,7 +14216,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" ht="30" customHeight="1" spans="1:8">
       <c r="A199" s="2">
         <v>1785</v>
       </c>
@@ -14226,7 +14239,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" ht="30" customHeight="1" spans="1:8">
       <c r="A200" s="2">
         <v>1767</v>
       </c>
@@ -14249,7 +14262,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" ht="30" customHeight="1" spans="1:8">
       <c r="A201" s="2">
         <v>1779</v>
       </c>
@@ -14272,7 +14285,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" ht="30" customHeight="1" spans="1:8">
       <c r="A202" s="2">
         <v>1781</v>
       </c>
@@ -14295,7 +14308,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" ht="30" customHeight="1" spans="1:8">
       <c r="A203" s="2" t="s">
         <v>265</v>
       </c>
@@ -14318,7 +14331,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" ht="30" customHeight="1" spans="1:8">
       <c r="A204" s="2">
         <v>1756</v>
       </c>
@@ -14341,7 +14354,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" ht="30" customHeight="1" spans="1:8">
       <c r="A205" s="2">
         <v>1767</v>
       </c>
@@ -14364,7 +14377,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" ht="30" customHeight="1" spans="1:8">
       <c r="A206" s="2">
         <v>1781</v>
       </c>
@@ -14387,7 +14400,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" ht="30" customHeight="1" spans="1:8">
       <c r="A207" s="2">
         <v>1766</v>
       </c>
@@ -14410,7 +14423,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" ht="30" customHeight="1" spans="1:8">
       <c r="A208" s="2">
         <v>1786</v>
       </c>
@@ -14433,7 +14446,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" ht="30" customHeight="1" spans="1:8">
       <c r="A209" s="2" t="s">
         <v>265</v>
       </c>
@@ -14456,7 +14469,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" ht="30" customHeight="1" spans="1:8">
       <c r="A210" s="2" t="s">
         <v>265</v>
       </c>
@@ -14479,7 +14492,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" ht="30" customHeight="1" spans="1:8">
       <c r="A211" s="2">
         <v>1754</v>
       </c>
@@ -14502,7 +14515,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" ht="30" customHeight="1" spans="1:8">
       <c r="A212" s="2">
         <v>1755</v>
       </c>
@@ -14525,7 +14538,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" ht="30" customHeight="1" spans="1:8">
       <c r="A213" s="2">
         <v>1755</v>
       </c>
@@ -14548,7 +14561,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" ht="30" customHeight="1" spans="1:8">
       <c r="A214" s="2">
         <v>1756</v>
       </c>
@@ -14571,7 +14584,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" ht="30" customHeight="1" spans="1:8">
       <c r="A215" s="2">
         <v>1775</v>
       </c>
@@ -14594,7 +14607,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" ht="30" customHeight="1" spans="1:8">
       <c r="A216" s="2">
         <v>1779</v>
       </c>
@@ -14617,7 +14630,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" ht="30" customHeight="1" spans="1:8">
       <c r="A217" s="2" t="s">
         <v>265</v>
       </c>
@@ -14640,7 +14653,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" ht="30" customHeight="1" spans="1:8">
       <c r="A218" s="2">
         <v>1755</v>
       </c>
@@ -14663,7 +14676,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" ht="30" customHeight="1" spans="1:8">
       <c r="A219" s="2">
         <v>1754</v>
       </c>
@@ -14686,7 +14699,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" ht="30" customHeight="1" spans="1:8">
       <c r="A220" s="2">
         <v>1755</v>
       </c>
@@ -14709,7 +14722,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" ht="30" customHeight="1" spans="1:8">
       <c r="A221" s="2">
         <v>1756</v>
       </c>
@@ -14732,7 +14745,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" ht="30" customHeight="1" spans="1:8">
       <c r="A222" s="2">
         <v>1759</v>
       </c>
@@ -14755,7 +14768,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" ht="30" customHeight="1" spans="1:8">
       <c r="A223" s="2">
         <v>1759</v>
       </c>
@@ -14778,7 +14791,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" ht="30" customHeight="1" spans="1:8">
       <c r="A224" s="2">
         <v>1759</v>
       </c>
@@ -14801,7 +14814,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" ht="30" customHeight="1" spans="1:8">
       <c r="A225" s="2">
         <v>1759</v>
       </c>
@@ -14824,7 +14837,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" ht="30" customHeight="1" spans="1:8">
       <c r="A226" s="2">
         <v>1765</v>
       </c>
@@ -14847,7 +14860,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" ht="30" customHeight="1" spans="1:8">
       <c r="A227" s="2">
         <v>1775</v>
       </c>
@@ -14870,7 +14883,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" ht="30" customHeight="1" spans="1:8">
       <c r="A228" s="2">
         <v>1779</v>
       </c>
@@ -14893,7 +14906,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" ht="30" customHeight="1" spans="1:8">
       <c r="A229" s="2">
         <v>1780</v>
       </c>
@@ -14916,7 +14929,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" ht="30" customHeight="1" spans="1:8">
       <c r="A230" s="2" t="s">
         <v>265</v>
       </c>
@@ -14939,7 +14952,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" ht="30" customHeight="1" spans="1:8">
       <c r="A231" s="2">
         <v>1755</v>
       </c>
@@ -14962,7 +14975,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" ht="30" customHeight="1" spans="1:8">
       <c r="A232" s="2">
         <v>1755</v>
       </c>
@@ -14985,7 +14998,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" ht="30" customHeight="1" spans="1:8">
       <c r="A233" s="2">
         <v>1755</v>
       </c>
@@ -15008,7 +15021,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" ht="30" customHeight="1" spans="1:8">
       <c r="A234" s="2">
         <v>1765</v>
       </c>
@@ -15031,7 +15044,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" ht="30" customHeight="1" spans="1:8">
       <c r="B235" s="3" t="s">
         <v>649</v>
       </c>
@@ -15045,7 +15058,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" ht="30" customHeight="1" spans="1:8">
       <c r="A236" s="2">
         <v>1754.5</v>
       </c>
@@ -15062,7 +15075,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" ht="30" customHeight="1" spans="1:8">
       <c r="A237" s="2">
         <v>1765</v>
       </c>
@@ -15079,7 +15092,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" ht="30" customHeight="1" spans="1:8">
       <c r="A238" s="2">
         <v>1767</v>
       </c>
@@ -15096,7 +15109,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" ht="30" customHeight="1" spans="1:8">
       <c r="A239" s="2" t="s">
         <v>658</v>
       </c>
@@ -15113,7 +15126,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" ht="30" customHeight="1" spans="1:8">
       <c r="A240" s="2" t="s">
         <v>660</v>
       </c>
@@ -15130,7 +15143,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" ht="30" customHeight="1" spans="1:8">
       <c r="A241" s="2" t="s">
         <v>662</v>
       </c>
@@ -15147,7 +15160,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" ht="30" customHeight="1" spans="1:8">
       <c r="A242" s="2" t="s">
         <v>664</v>
       </c>
@@ -15164,7 +15177,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" ht="30" customHeight="1" spans="1:8">
       <c r="B243" s="3" t="s">
         <v>666</v>
       </c>
@@ -15175,7 +15188,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" ht="30" customHeight="1" spans="1:8">
       <c r="B244" s="3" t="s">
         <v>668</v>
       </c>
@@ -15186,7 +15199,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" ht="30" customHeight="1" spans="1:8">
       <c r="B245" s="3" t="s">
         <v>670</v>
       </c>
@@ -15197,7 +15210,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" ht="30" customHeight="1" spans="1:8">
       <c r="A246" s="2">
         <v>1741</v>
       </c>
@@ -15214,7 +15227,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" ht="30" customHeight="1" spans="1:8">
       <c r="A247" s="2">
         <v>1756</v>
       </c>
@@ -15231,7 +15244,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" ht="30" customHeight="1" spans="1:8">
       <c r="A248" s="2">
         <v>1764</v>
       </c>
@@ -15248,7 +15261,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" ht="30" customHeight="1" spans="1:8">
       <c r="A249" s="2">
         <v>1764</v>
       </c>
@@ -15265,7 +15278,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" ht="30" customHeight="1" spans="1:8">
       <c r="A250" s="2">
         <v>1767</v>
       </c>
@@ -15282,7 +15295,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" ht="30" customHeight="1" spans="1:8">
       <c r="A251" s="2">
         <v>1770</v>
       </c>
@@ -15299,7 +15312,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" ht="30" customHeight="1" spans="1:8">
       <c r="A252" s="2">
         <v>1770</v>
       </c>
@@ -15316,7 +15329,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" ht="30" customHeight="1" spans="1:8">
       <c r="A253" s="2">
         <v>1770</v>
       </c>
@@ -15333,7 +15346,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" ht="30" customHeight="1" spans="1:8">
       <c r="A254" s="2">
         <v>1773</v>
       </c>
@@ -15346,11 +15359,11 @@
       <c r="D254" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="E254" s="8" t="s">
+      <c r="E254" s="11" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" ht="30" customHeight="1" spans="1:8">
       <c r="A255" s="2">
         <v>1775</v>
       </c>
@@ -15367,7 +15380,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" ht="30" customHeight="1" spans="1:8">
       <c r="A256" s="2">
         <v>1780</v>
       </c>
@@ -15384,7 +15397,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" ht="30" customHeight="1" spans="1:5">
       <c r="A257" s="2">
         <v>1780</v>
       </c>
@@ -15401,7 +15414,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" ht="30" customHeight="1" spans="1:5">
       <c r="A258" s="2">
         <v>1780</v>
       </c>
@@ -15418,7 +15431,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" ht="30" customHeight="1" spans="1:5">
       <c r="A259" s="2">
         <v>1780</v>
       </c>
@@ -15431,11 +15444,11 @@
       <c r="D259" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="E259" s="8" t="s">
+      <c r="E259" s="11" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" ht="30" customHeight="1" spans="1:5">
       <c r="A260" s="2">
         <v>1780</v>
       </c>
@@ -15452,7 +15465,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" ht="30" customHeight="1" spans="1:5">
       <c r="A261" s="2">
         <v>1780</v>
       </c>
@@ -15469,7 +15482,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" ht="30" customHeight="1" spans="1:5">
       <c r="A262" s="2">
         <v>1780</v>
       </c>
@@ -15486,7 +15499,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" ht="30" customHeight="1" spans="1:5">
       <c r="A263" s="2">
         <v>1780</v>
       </c>
@@ -15503,7 +15516,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" ht="30" customHeight="1" spans="1:5">
       <c r="A264" s="2">
         <v>1780</v>
       </c>
@@ -15520,7 +15533,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" ht="30" customHeight="1" spans="1:5">
       <c r="A265" s="2">
         <v>1780</v>
       </c>
@@ -15537,7 +15550,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" ht="30" customHeight="1" spans="1:5">
       <c r="A266" s="2">
         <v>1780</v>
       </c>
@@ -15554,7 +15567,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" ht="30" customHeight="1" spans="1:5">
       <c r="A267" s="2">
         <v>1780</v>
       </c>
@@ -15571,7 +15584,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" ht="30" customHeight="1" spans="1:5">
       <c r="A268" s="2">
         <v>1781</v>
       </c>
@@ -15588,7 +15601,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" ht="30" customHeight="1" spans="1:5">
       <c r="A269" s="2">
         <v>1781</v>
       </c>
@@ -15605,7 +15618,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" ht="30" customHeight="1" spans="1:5">
       <c r="A270" s="2">
         <v>1781</v>
       </c>
@@ -15622,7 +15635,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" ht="30" customHeight="1" spans="1:5">
       <c r="A271" s="2">
         <v>1781</v>
       </c>
@@ -15639,7 +15652,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" ht="30" customHeight="1" spans="1:5">
       <c r="A272" s="2">
         <v>1781</v>
       </c>
@@ -15656,7 +15669,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" ht="30" customHeight="1" spans="1:5">
       <c r="A273" s="2">
         <v>1781</v>
       </c>
@@ -15673,7 +15686,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" ht="30" customHeight="1" spans="1:5">
       <c r="A274" s="2">
         <v>1782</v>
       </c>
@@ -15690,7 +15703,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" ht="30" customHeight="1" spans="1:5">
       <c r="A275" s="2">
         <v>1782</v>
       </c>
@@ -15707,7 +15720,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" ht="30" customHeight="1" spans="1:5">
       <c r="A276" s="2">
         <v>1783</v>
       </c>
@@ -15724,7 +15737,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" ht="30" customHeight="1" spans="1:5">
       <c r="A277" s="2">
         <v>1785</v>
       </c>
@@ -15741,7 +15754,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" ht="30" customHeight="1" spans="1:5">
       <c r="A278" s="2">
         <v>1788</v>
       </c>
@@ -15758,7 +15771,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" ht="30" customHeight="1" spans="1:5">
       <c r="A279" s="2">
         <v>1788</v>
       </c>
@@ -15775,7 +15788,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" ht="30" customHeight="1" spans="1:5">
       <c r="A280" s="2">
         <v>1788</v>
       </c>
@@ -15792,7 +15805,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" ht="30" customHeight="1" spans="1:5">
       <c r="A281" s="2">
         <v>1788</v>
       </c>
@@ -15809,7 +15822,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" ht="30" customHeight="1" spans="1:5">
       <c r="A282" s="2">
         <v>1788</v>
       </c>
@@ -15826,7 +15839,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" ht="30" customHeight="1" spans="1:5">
       <c r="A283" s="2" t="s">
         <v>784</v>
       </c>
@@ -15843,7 +15856,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" ht="30" customHeight="1" spans="1:5">
       <c r="A284" s="2" t="s">
         <v>788</v>
       </c>
@@ -15860,7 +15873,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" ht="30" customHeight="1" spans="1:5">
       <c r="A285" s="2" t="s">
         <v>788</v>
       </c>
@@ -15877,7 +15890,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" ht="30" customHeight="1" spans="1:5">
       <c r="A286" s="2" t="s">
         <v>788</v>
       </c>
@@ -15894,7 +15907,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" ht="30" customHeight="1" spans="1:5">
       <c r="A287" s="2" t="s">
         <v>788</v>
       </c>
@@ -15911,7 +15924,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" ht="30" customHeight="1" spans="1:5">
       <c r="A288" s="2" t="s">
         <v>788</v>
       </c>
@@ -15928,7 +15941,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="289" spans="1:8">
+    <row r="289" ht="30" customHeight="1" spans="1:8">
       <c r="A289" s="2" t="s">
         <v>788</v>
       </c>
@@ -15945,7 +15958,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="290" spans="1:8">
+    <row r="290" ht="30" customHeight="1" spans="1:8">
       <c r="A290" s="2" t="s">
         <v>788</v>
       </c>
@@ -15962,7 +15975,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="291" spans="1:8">
+    <row r="291" ht="30" customHeight="1" spans="1:8">
       <c r="A291" s="2" t="s">
         <v>788</v>
       </c>
@@ -15979,7 +15992,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="292" spans="1:8">
+    <row r="292" ht="30" customHeight="1" spans="1:8">
       <c r="A292" s="2" t="s">
         <v>788</v>
       </c>
@@ -15996,7 +16009,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="293" spans="1:8">
+    <row r="293" ht="30" customHeight="1" spans="1:8">
       <c r="A293" s="2" t="s">
         <v>816</v>
       </c>
@@ -16013,7 +16026,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="294" spans="1:8">
+    <row r="294" ht="30" customHeight="1" spans="1:8">
       <c r="A294" s="2" t="s">
         <v>820</v>
       </c>
@@ -16030,7 +16043,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="295" spans="1:8">
+    <row r="295" ht="30" customHeight="1" spans="1:8">
       <c r="A295" s="2" t="s">
         <v>824</v>
       </c>
@@ -16047,7 +16060,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="296" spans="1:8">
+    <row r="296" ht="30" customHeight="1" spans="1:8">
       <c r="B296" s="3" t="s">
         <v>828</v>
       </c>
@@ -16058,7 +16071,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="297" spans="1:8">
+    <row r="297" ht="30" customHeight="1" spans="1:8">
       <c r="A297" s="2">
         <v>1785</v>
       </c>
@@ -16075,7 +16088,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" ht="30" customHeight="1" spans="1:8">
       <c r="A298" s="2">
         <v>1749</v>
       </c>
@@ -16092,7 +16105,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="299" spans="1:8">
+    <row r="299" ht="30" customHeight="1" spans="1:8">
       <c r="A299" s="2">
         <v>1767</v>
       </c>
@@ -16112,7 +16125,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="300" spans="1:8">
+    <row r="300" ht="30" customHeight="1" spans="1:8">
       <c r="A300" s="2">
         <v>1767</v>
       </c>
@@ -16135,7 +16148,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="301" spans="1:8">
+    <row r="301" ht="30" customHeight="1" spans="1:8">
       <c r="A301" s="2">
         <v>1767</v>
       </c>
@@ -16155,7 +16168,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="302" spans="1:8">
+    <row r="302" ht="30" customHeight="1" spans="1:8">
       <c r="A302" s="2">
         <v>1767</v>
       </c>
@@ -16175,7 +16188,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="303" spans="1:8">
+    <row r="303" ht="30" customHeight="1" spans="1:8">
       <c r="A303" s="2">
         <v>1775</v>
       </c>
@@ -16192,7 +16205,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" ht="30" customHeight="1" spans="1:8">
       <c r="A304" s="2" t="s">
         <v>265</v>
       </c>
@@ -16212,7 +16225,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" ht="30" customHeight="1" spans="1:8">
       <c r="B305" s="3" t="s">
         <v>853</v>
       </c>
@@ -16229,7 +16242,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" ht="30" customHeight="1" spans="1:8">
       <c r="A306" s="2">
         <v>1767</v>
       </c>
@@ -16249,7 +16262,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" ht="30" customHeight="1" spans="1:8">
       <c r="A307" s="2">
         <v>1767</v>
       </c>
@@ -16269,7 +16282,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" ht="30" customHeight="1" spans="1:8">
       <c r="A308" s="2" t="s">
         <v>265</v>
       </c>
@@ -16289,7 +16302,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" ht="30" customHeight="1" spans="1:8">
       <c r="B309" s="3" t="s">
         <v>862</v>
       </c>
@@ -16306,7 +16319,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" ht="30" customHeight="1" spans="1:8">
       <c r="A310" s="2">
         <v>1767</v>
       </c>
@@ -16326,7 +16339,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" ht="30" customHeight="1" spans="1:8">
       <c r="A311" s="2">
         <v>1775</v>
       </c>
@@ -16343,7 +16356,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" ht="30" customHeight="1" spans="1:8">
       <c r="A312" s="2">
         <v>1767</v>
       </c>
@@ -16357,7 +16370,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="313" spans="1:8">
+    <row r="313" ht="30" customHeight="1" spans="1:8">
       <c r="B313" s="3" t="s">
         <v>869</v>
       </c>
@@ -16371,7 +16384,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" ht="30" customHeight="1" spans="1:8">
       <c r="A314" s="2">
         <v>1762.5</v>
       </c>
@@ -16391,7 +16404,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" ht="30" customHeight="1" spans="1:8">
       <c r="A315" s="2">
         <v>1762.5</v>
       </c>
@@ -16411,7 +16424,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" ht="30" customHeight="1" spans="1:8">
       <c r="A316" s="2">
         <v>1731</v>
       </c>
@@ -16431,7 +16444,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" ht="30" customHeight="1" spans="1:8">
       <c r="A317" s="2">
         <v>1745</v>
       </c>
@@ -16454,7 +16467,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" ht="30" customHeight="1" spans="1:8">
       <c r="A318" s="2">
         <v>1762</v>
       </c>
@@ -16474,7 +16487,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="319" spans="1:8">
+    <row r="319" ht="30" customHeight="1" spans="1:8">
       <c r="A319" s="2">
         <v>1766</v>
       </c>
@@ -16494,7 +16507,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" ht="30" customHeight="1" spans="1:8">
       <c r="A320" s="2">
         <v>1775</v>
       </c>
@@ -16517,7 +16530,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="321" spans="1:9">
+    <row r="321" ht="30" customHeight="1" spans="1:9">
       <c r="A321" s="2">
         <v>1775</v>
       </c>
@@ -16540,7 +16553,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="322" spans="1:9">
+    <row r="322" ht="30" customHeight="1" spans="1:9">
       <c r="A322" s="2" t="s">
         <v>265</v>
       </c>
@@ -16560,7 +16573,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="323" spans="1:9">
+    <row r="323" ht="30" customHeight="1" spans="1:9">
       <c r="B323" s="3" t="s">
         <v>892</v>
       </c>
@@ -16583,7 +16596,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="324" spans="1:9">
+    <row r="324" ht="30" customHeight="1" spans="1:9">
       <c r="A324" s="2">
         <v>1762.5</v>
       </c>
@@ -16603,7 +16616,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="325" spans="1:9">
+    <row r="325" ht="30" customHeight="1" spans="1:9">
       <c r="A325" s="2">
         <v>1762.5</v>
       </c>
@@ -16623,7 +16636,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="326" spans="1:9">
+    <row r="326" ht="30" customHeight="1" spans="1:9">
       <c r="A326" s="2">
         <v>1762.5</v>
       </c>
@@ -16643,7 +16656,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="327" spans="1:9">
+    <row r="327" ht="30" customHeight="1" spans="1:9">
       <c r="A327" s="2">
         <v>1762.5</v>
       </c>
@@ -16663,7 +16676,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="328" spans="1:9">
+    <row r="328" ht="30" customHeight="1" spans="1:9">
       <c r="A328" s="2">
         <v>1762.5</v>
       </c>
@@ -16683,7 +16696,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="329" spans="1:9">
+    <row r="329" ht="30" customHeight="1" spans="1:9">
       <c r="A329" s="2">
         <v>1762.5</v>
       </c>
@@ -16703,7 +16716,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="330" spans="1:9">
+    <row r="330" ht="30" customHeight="1" spans="1:9">
       <c r="A330" s="2">
         <v>1766</v>
       </c>
@@ -16723,7 +16736,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="331" spans="1:9">
+    <row r="331" ht="30" customHeight="1" spans="1:9">
       <c r="A331" s="2">
         <v>1766</v>
       </c>
@@ -16743,7 +16756,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="332" spans="1:9">
+    <row r="332" ht="30" customHeight="1" spans="1:9">
       <c r="A332" s="2">
         <v>1768</v>
       </c>
@@ -16763,7 +16776,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="333" spans="1:9">
+    <row r="333" ht="30" customHeight="1" spans="1:9">
       <c r="A333" s="2">
         <v>1775</v>
       </c>
@@ -16783,7 +16796,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="334" spans="1:9">
+    <row r="334" ht="30" customHeight="1" spans="1:9">
       <c r="A334" s="2" t="s">
         <v>265</v>
       </c>
@@ -16803,7 +16816,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="335" spans="1:9">
+    <row r="335" ht="30" customHeight="1" spans="1:9">
       <c r="A335" s="2" t="s">
         <v>265</v>
       </c>
@@ -16823,7 +16836,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="336" spans="1:9">
+    <row r="336" ht="30" customHeight="1" spans="1:9">
       <c r="A336" s="2" t="s">
         <v>265</v>
       </c>
@@ -16843,7 +16856,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="337" spans="1:9">
+    <row r="337" ht="30" customHeight="1" spans="1:9">
       <c r="B337" s="3" t="s">
         <v>925</v>
       </c>
@@ -16866,7 +16879,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="338" spans="1:9">
+    <row r="338" ht="30" customHeight="1" spans="1:9">
       <c r="A338" s="2">
         <v>1763</v>
       </c>
@@ -16886,7 +16899,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="339" spans="1:9">
+    <row r="339" ht="30" customHeight="1" spans="1:9">
       <c r="A339" s="2">
         <v>1765</v>
       </c>
@@ -16906,7 +16919,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="340" spans="1:9">
+    <row r="340" ht="30" customHeight="1" spans="1:9">
       <c r="A340" s="2">
         <v>1766</v>
       </c>
@@ -16926,7 +16939,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="341" spans="1:9">
+    <row r="341" ht="30" customHeight="1" spans="1:9">
       <c r="A341" s="2">
         <v>1768</v>
       </c>
@@ -16946,7 +16959,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="342" spans="1:9">
+    <row r="342" ht="30" customHeight="1" spans="1:9">
       <c r="A342" s="2">
         <v>1775</v>
       </c>
@@ -16966,7 +16979,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="343" spans="1:9">
+    <row r="343" ht="30" customHeight="1" spans="1:9">
       <c r="A343" s="2" t="s">
         <v>265</v>
       </c>
@@ -16986,7 +16999,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="344" spans="1:9">
+    <row r="344" ht="30" customHeight="1" spans="1:9">
       <c r="A344" s="2">
         <v>1767</v>
       </c>
@@ -17006,7 +17019,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="345" spans="1:9">
+    <row r="345" ht="30" customHeight="1" spans="1:9">
       <c r="A345" s="2">
         <v>1768</v>
       </c>
@@ -17032,7 +17045,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="346" spans="1:9">
+    <row r="346" ht="30" customHeight="1" spans="1:9">
       <c r="A346" s="2">
         <v>1768</v>
       </c>
@@ -17052,7 +17065,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="347" spans="1:9">
+    <row r="347" ht="30" customHeight="1" spans="1:9">
       <c r="A347" s="2">
         <v>1768</v>
       </c>
@@ -17072,7 +17085,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="348" spans="1:9">
+    <row r="348" ht="30" customHeight="1" spans="1:9">
       <c r="A348" s="2">
         <v>1775</v>
       </c>
@@ -17095,7 +17108,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="349" spans="1:9">
+    <row r="349" ht="30" customHeight="1" spans="1:9">
       <c r="A349" s="2" t="s">
         <v>265</v>
       </c>
@@ -17118,7 +17131,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="350" spans="1:9">
+    <row r="350" ht="30" customHeight="1" spans="1:9">
       <c r="A350" s="2" t="s">
         <v>265</v>
       </c>
@@ -17138,7 +17151,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="351" spans="1:9">
+    <row r="351" ht="30" customHeight="1" spans="1:9">
       <c r="A351" s="2" t="s">
         <v>265</v>
       </c>
@@ -17158,7 +17171,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="352" spans="1:9">
+    <row r="352" ht="30" customHeight="1" spans="1:9">
       <c r="A352" s="2" t="s">
         <v>265</v>
       </c>
@@ -17178,7 +17191,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="353" spans="1:9">
+    <row r="353" ht="30" customHeight="1" spans="1:9">
       <c r="B353" s="3" t="s">
         <v>966</v>
       </c>
@@ -17198,7 +17211,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="354" spans="1:9">
+    <row r="354" ht="30" customHeight="1" spans="1:9">
       <c r="B354" s="3" t="s">
         <v>969</v>
       </c>
@@ -17215,7 +17228,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="355" spans="1:9">
+    <row r="355" ht="30" customHeight="1" spans="1:9">
       <c r="A355" s="2">
         <v>1775</v>
       </c>
@@ -17238,7 +17251,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="356" spans="1:9">
+    <row r="356" ht="30" customHeight="1" spans="1:9">
       <c r="A356" s="2">
         <v>1775</v>
       </c>
@@ -17261,7 +17274,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="357" spans="1:9">
+    <row r="357" ht="30" customHeight="1" spans="1:9">
       <c r="B357" s="3" t="s">
         <v>976</v>
       </c>
@@ -17278,7 +17291,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="358" spans="1:9">
+    <row r="358" ht="30" customHeight="1" spans="1:9">
       <c r="A358" s="2">
         <v>1762.8</v>
       </c>
@@ -17295,7 +17308,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="359" spans="1:9">
+    <row r="359" ht="30" customHeight="1" spans="1:9">
       <c r="B359" s="3" t="s">
         <v>980</v>
       </c>
@@ -17306,7 +17319,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="360" spans="1:9">
+    <row r="360" ht="30" customHeight="1" spans="1:9">
       <c r="A360" s="2" t="s">
         <v>982</v>
       </c>
@@ -17323,7 +17336,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="361" spans="1:9">
+    <row r="361" ht="30" customHeight="1" spans="1:9">
       <c r="A361" s="2">
         <v>1778</v>
       </c>
@@ -17340,7 +17353,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="362" spans="1:9">
+    <row r="362" ht="30" customHeight="1" spans="1:9">
       <c r="A362" s="2">
         <v>1780</v>
       </c>
@@ -17357,8 +17370,8 @@
         <v>990</v>
       </c>
     </row>
-    <row r="363" spans="1:9">
-      <c r="A363" s="9">
+    <row r="363" ht="30" customHeight="1" spans="1:9">
+      <c r="A363" s="12">
         <v>1786.7</v>
       </c>
       <c r="B363" s="3" t="s">
@@ -17367,25 +17380,25 @@
       <c r="C363" s="3" t="s">
         <v>994</v>
       </c>
-      <c r="D363" s="10" t="s">
+      <c r="D363" s="13" t="s">
         <v>995</v>
       </c>
-      <c r="E363" s="9" t="s">
+      <c r="E363" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="F363" s="9"/>
-      <c r="G363" s="11" t="s">
+      <c r="F363" s="12"/>
+      <c r="G363" s="14" t="s">
         <v>997</v>
       </c>
-      <c r="H363" s="11" t="s">
+      <c r="H363" s="14" t="s">
         <v>998</v>
       </c>
-      <c r="I363" s="12" t="s">
+      <c r="I363" s="15" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="364" spans="1:9">
-      <c r="A364" s="9">
+    <row r="364" ht="30" customHeight="1" spans="1:9">
+      <c r="A364" s="12">
         <v>1788.9</v>
       </c>
       <c r="B364" s="3" t="s">
@@ -17397,17 +17410,17 @@
       <c r="D364" s="4" t="s">
         <v>1002</v>
       </c>
-      <c r="E364" s="9" t="s">
+      <c r="E364" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="G364" s="11" t="s">
+      <c r="G364" s="14" t="s">
         <v>1003</v>
       </c>
       <c r="H364" s="5" t="s">
         <v>1004</v>
       </c>
     </row>
-    <row r="365" spans="1:9">
+    <row r="365" ht="30" customHeight="1" spans="1:9">
       <c r="A365" s="2">
         <v>1761</v>
       </c>
@@ -17424,7 +17437,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="366" spans="1:9">
+    <row r="366" ht="30" customHeight="1" spans="1:9">
       <c r="A366" s="2">
         <v>1761</v>
       </c>
@@ -17441,7 +17454,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="367" spans="1:9">
+    <row r="367" ht="30" customHeight="1" spans="1:9">
       <c r="A367" s="2">
         <v>1764</v>
       </c>
@@ -17458,7 +17471,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="368" spans="1:9">
+    <row r="368" ht="30" customHeight="1" spans="1:9">
       <c r="A368" s="2">
         <v>1764</v>
       </c>
@@ -17475,7 +17488,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" ht="30" customHeight="1" spans="1:5">
       <c r="A369" s="2">
         <v>1764</v>
       </c>
@@ -17492,7 +17505,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" ht="30" customHeight="1" spans="1:5">
       <c r="A370" s="2">
         <v>1774</v>
       </c>
@@ -17509,7 +17522,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" ht="30" customHeight="1" spans="1:5">
       <c r="A371" s="2" t="s">
         <v>816</v>
       </c>
@@ -17526,7 +17539,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" ht="30" customHeight="1" spans="1:5">
       <c r="A372" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17543,7 +17556,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" ht="30" customHeight="1" spans="1:5">
       <c r="A373" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17560,7 +17573,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" ht="30" customHeight="1" spans="1:5">
       <c r="A374" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17577,7 +17590,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" ht="30" customHeight="1" spans="1:5">
       <c r="A375" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17594,7 +17607,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" ht="30" customHeight="1" spans="1:5">
       <c r="A376" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17611,7 +17624,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" ht="30" customHeight="1" spans="1:5">
       <c r="A377" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17628,7 +17641,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" ht="30" customHeight="1" spans="1:5">
       <c r="A378" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17645,7 +17658,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" ht="30" customHeight="1" spans="1:5">
       <c r="A379" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17662,7 +17675,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" ht="30" customHeight="1" spans="1:5">
       <c r="A380" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17679,7 +17692,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" ht="30" customHeight="1" spans="1:5">
       <c r="A381" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17696,7 +17709,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" ht="30" customHeight="1" spans="1:5">
       <c r="A382" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17713,7 +17726,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" ht="30" customHeight="1" spans="1:5">
       <c r="A383" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17730,7 +17743,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" ht="30" customHeight="1" spans="1:5">
       <c r="A384" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17747,7 +17760,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" ht="30" customHeight="1" spans="1:5">
       <c r="A385" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17764,7 +17777,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" ht="30" customHeight="1" spans="1:5">
       <c r="A386" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17781,7 +17794,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" ht="30" customHeight="1" spans="1:5">
       <c r="A387" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17798,7 +17811,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" ht="30" customHeight="1" spans="1:5">
       <c r="A388" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17815,7 +17828,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" ht="30" customHeight="1" spans="1:5">
       <c r="A389" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17832,7 +17845,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" ht="30" customHeight="1" spans="1:5">
       <c r="A390" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17849,7 +17862,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" ht="30" customHeight="1" spans="1:5">
       <c r="A391" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17866,7 +17879,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" ht="30" customHeight="1" spans="1:5">
       <c r="A392" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17883,7 +17896,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" ht="30" customHeight="1" spans="1:5">
       <c r="A393" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17900,7 +17913,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" ht="30" customHeight="1" spans="1:5">
       <c r="A394" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17917,7 +17930,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" ht="30" customHeight="1" spans="1:5">
       <c r="A395" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17934,7 +17947,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" ht="30" customHeight="1" spans="1:5">
       <c r="A396" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17951,7 +17964,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" ht="30" customHeight="1" spans="1:5">
       <c r="A397" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17968,7 +17981,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" ht="30" customHeight="1" spans="1:5">
       <c r="A398" s="2" t="s">
         <v>1027</v>
       </c>
@@ -17985,7 +17998,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" ht="30" customHeight="1" spans="1:5">
       <c r="A399" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18002,7 +18015,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" ht="30" customHeight="1" spans="1:5">
       <c r="A400" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18019,7 +18032,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="401" spans="1:8">
+    <row r="401" ht="30" customHeight="1" spans="1:8">
       <c r="A401" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18036,7 +18049,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="402" spans="1:8">
+    <row r="402" ht="30" customHeight="1" spans="1:8">
       <c r="A402" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18053,7 +18066,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="403" spans="1:8">
+    <row r="403" ht="30" customHeight="1" spans="1:8">
       <c r="A403" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18070,7 +18083,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="404" spans="1:8">
+    <row r="404" ht="30" customHeight="1" spans="1:8">
       <c r="A404" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18087,7 +18100,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="405" spans="1:8">
+    <row r="405" ht="30" customHeight="1" spans="1:8">
       <c r="A405" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18104,7 +18117,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="406" spans="1:8">
+    <row r="406" ht="30" customHeight="1" spans="1:8">
       <c r="A406" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18121,7 +18134,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="407" spans="1:8">
+    <row r="407" ht="30" customHeight="1" spans="1:8">
       <c r="A407" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18138,7 +18151,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="408" spans="1:8">
+    <row r="408" ht="30" customHeight="1" spans="1:8">
       <c r="A408" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18155,7 +18168,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="409" spans="1:8">
+    <row r="409" ht="30" customHeight="1" spans="1:8">
       <c r="A409" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18172,7 +18185,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="410" spans="1:8">
+    <row r="410" ht="30" customHeight="1" spans="1:8">
       <c r="A410" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18189,7 +18202,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="411" spans="1:8">
+    <row r="411" ht="30" customHeight="1" spans="1:8">
       <c r="A411" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18206,7 +18219,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="412" spans="1:8">
+    <row r="412" ht="30" customHeight="1" spans="1:8">
       <c r="A412" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18223,7 +18236,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="413" spans="1:8">
+    <row r="413" ht="30" customHeight="1" spans="1:8">
       <c r="A413" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18240,7 +18253,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="414" spans="1:8">
+    <row r="414" ht="30" customHeight="1" spans="1:8">
       <c r="A414" s="2">
         <v>1773</v>
       </c>
@@ -18260,7 +18273,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="415" spans="1:8">
+    <row r="415" ht="30" customHeight="1" spans="1:8">
       <c r="A415" s="2">
         <v>1754</v>
       </c>
@@ -18280,7 +18293,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="416" spans="1:8">
+    <row r="416" ht="30" customHeight="1" spans="1:8">
       <c r="A416" s="2">
         <v>1773</v>
       </c>
@@ -18300,7 +18313,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="417" spans="1:8">
+    <row r="417" ht="30" customHeight="1" spans="1:8">
       <c r="A417" s="2">
         <v>1773</v>
       </c>
@@ -18320,7 +18333,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="418" spans="1:8">
+    <row r="418" ht="30" customHeight="1" spans="1:8">
       <c r="A418" s="2">
         <v>1773</v>
       </c>
@@ -18340,7 +18353,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="419" spans="1:8">
+    <row r="419" ht="30" customHeight="1" spans="1:8">
       <c r="A419" s="2">
         <v>1775.6</v>
       </c>
@@ -18360,7 +18373,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="420" spans="1:8">
+    <row r="420" ht="30" customHeight="1" spans="1:8">
       <c r="A420" s="2">
         <v>1773</v>
       </c>
@@ -18380,7 +18393,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="421" spans="1:8">
+    <row r="421" ht="30" customHeight="1" spans="1:8">
       <c r="A421" s="2">
         <v>1775.6</v>
       </c>
@@ -18400,7 +18413,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="422" spans="1:8">
+    <row r="422" ht="30" customHeight="1" spans="1:8">
       <c r="A422" s="2">
         <v>1775.6</v>
       </c>
@@ -18420,7 +18433,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="423" spans="1:8">
+    <row r="423" ht="30" customHeight="1" spans="1:8">
       <c r="A423" s="2">
         <v>1765</v>
       </c>
@@ -18440,7 +18453,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="424" spans="1:8">
+    <row r="424" ht="30" customHeight="1" spans="1:8">
       <c r="A424" s="2">
         <v>1773</v>
       </c>
@@ -18460,7 +18473,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="425" spans="1:8">
+    <row r="425" ht="30" customHeight="1" spans="1:8">
       <c r="A425" s="2">
         <v>1775.6</v>
       </c>
@@ -18480,7 +18493,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="426" spans="1:8">
+    <row r="426" ht="30" customHeight="1" spans="1:8">
       <c r="A426" s="2">
         <v>1773</v>
       </c>
@@ -18497,7 +18510,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="427" spans="1:8">
+    <row r="427" ht="30" customHeight="1" spans="1:8">
       <c r="A427" s="2">
         <v>1775.6</v>
       </c>
@@ -18514,7 +18527,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="428" spans="1:8">
+    <row r="428" ht="30" customHeight="1" spans="1:8">
       <c r="A428" s="2">
         <v>1746</v>
       </c>
@@ -18534,7 +18547,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="429" spans="1:8">
+    <row r="429" ht="30" customHeight="1" spans="1:8">
       <c r="A429" s="2">
         <v>1745</v>
       </c>
@@ -18557,7 +18570,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="430" spans="1:8">
+    <row r="430" ht="30" customHeight="1" spans="1:8">
       <c r="A430" s="2">
         <v>1746</v>
       </c>
@@ -18580,7 +18593,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="431" spans="1:8">
+    <row r="431" ht="30" customHeight="1" spans="1:8">
       <c r="A431" s="2">
         <v>1747</v>
       </c>
@@ -18600,7 +18613,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="432" spans="1:8">
+    <row r="432" ht="30" customHeight="1" spans="1:8">
       <c r="A432" s="2">
         <v>1762</v>
       </c>
@@ -18623,7 +18636,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="433" spans="1:9">
+    <row r="433" ht="30" customHeight="1" spans="1:9">
       <c r="A433" s="2">
         <v>1735</v>
       </c>
@@ -18646,7 +18659,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="434" spans="1:9">
+    <row r="434" ht="30" customHeight="1" spans="1:9">
       <c r="A434" s="2">
         <v>1740</v>
       </c>
@@ -18672,8 +18685,8 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="435" spans="1:9">
-      <c r="A435" s="6">
+    <row r="435" ht="30" customHeight="1" spans="1:9">
+      <c r="A435" s="9">
         <v>1731</v>
       </c>
       <c r="B435" s="3" t="s">
@@ -18695,8 +18708,8 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="436" spans="1:9">
-      <c r="A436" s="6">
+    <row r="436" ht="30" customHeight="1" spans="1:9">
+      <c r="A436" s="9">
         <v>1738</v>
       </c>
       <c r="B436" s="3" t="s">
@@ -18718,7 +18731,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="437" spans="1:9">
+    <row r="437" ht="30" customHeight="1" spans="1:9">
       <c r="A437" s="2">
         <v>1742</v>
       </c>
@@ -18738,7 +18751,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="438" spans="1:9">
+    <row r="438" ht="30" customHeight="1" spans="1:9">
       <c r="A438" s="2">
         <v>1753</v>
       </c>
@@ -18758,7 +18771,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="439" spans="1:9">
+    <row r="439" ht="30" customHeight="1" spans="1:9">
       <c r="A439" s="2">
         <v>1758</v>
       </c>
@@ -18778,7 +18791,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="440" spans="1:9">
+    <row r="440" ht="30" customHeight="1" spans="1:9">
       <c r="A440" s="2">
         <v>1758</v>
       </c>
@@ -18798,7 +18811,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="441" spans="1:9">
+    <row r="441" ht="30" customHeight="1" spans="1:9">
       <c r="A441" s="2">
         <v>1763</v>
       </c>
@@ -18818,7 +18831,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="442" spans="1:9">
+    <row r="442" ht="30" customHeight="1" spans="1:9">
       <c r="A442" s="2">
         <v>1765</v>
       </c>
@@ -18838,7 +18851,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="443" spans="1:9">
+    <row r="443" ht="30" customHeight="1" spans="1:9">
       <c r="A443" s="2">
         <v>1765.6</v>
       </c>
@@ -18858,7 +18871,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="444" spans="1:9">
+    <row r="444" ht="30" customHeight="1" spans="1:9">
       <c r="A444" s="2">
         <v>1766</v>
       </c>
@@ -18878,7 +18891,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="445" spans="1:9">
+    <row r="445" ht="30" customHeight="1" spans="1:9">
       <c r="A445" s="2">
         <v>1775</v>
       </c>
@@ -18898,7 +18911,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="446" spans="1:9">
+    <row r="446" ht="30" customHeight="1" spans="1:9">
       <c r="A446" s="2">
         <v>1775.6</v>
       </c>
@@ -18918,7 +18931,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="447" spans="1:9">
+    <row r="447" ht="30" customHeight="1" spans="1:9">
       <c r="A447" s="2">
         <v>1780</v>
       </c>
@@ -18938,8 +18951,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="448" spans="1:9">
-      <c r="A448" s="6">
+    <row r="448" ht="30" customHeight="1" spans="1:9">
+      <c r="A448" s="9">
         <v>1732</v>
       </c>
       <c r="B448" s="3" t="s">
@@ -18961,8 +18974,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="449" spans="1:9">
-      <c r="A449" s="6">
+    <row r="449" ht="30" customHeight="1" spans="1:9">
+      <c r="A449" s="9">
         <v>1735</v>
       </c>
       <c r="B449" s="3" t="s">
@@ -18984,7 +18997,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="450" spans="1:9">
+    <row r="450" ht="30" customHeight="1" spans="1:9">
       <c r="A450" s="2">
         <v>1740</v>
       </c>
@@ -19004,7 +19017,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="451" spans="1:9">
+    <row r="451" ht="30" customHeight="1" spans="1:9">
       <c r="A451" s="2">
         <v>1742</v>
       </c>
@@ -19024,7 +19037,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="452" spans="1:9">
+    <row r="452" ht="30" customHeight="1" spans="1:9">
       <c r="A452" s="2">
         <v>1747</v>
       </c>
@@ -19047,7 +19060,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="453" spans="1:9">
+    <row r="453" ht="30" customHeight="1" spans="1:9">
       <c r="A453" s="2">
         <v>1755</v>
       </c>
@@ -19067,7 +19080,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="454" spans="1:9">
+    <row r="454" ht="30" customHeight="1" spans="1:9">
       <c r="A454" s="2">
         <v>1758</v>
       </c>
@@ -19087,7 +19100,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="455" spans="1:9">
+    <row r="455" ht="30" customHeight="1" spans="1:9">
       <c r="A455" s="2">
         <v>1759</v>
       </c>
@@ -19107,7 +19120,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="456" spans="1:9">
+    <row r="456" ht="30" customHeight="1" spans="1:9">
       <c r="A456" s="2">
         <v>1759</v>
       </c>
@@ -19127,7 +19140,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="457" spans="1:9">
+    <row r="457" ht="30" customHeight="1" spans="1:9">
       <c r="A457" s="2">
         <v>1764</v>
       </c>
@@ -19147,7 +19160,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="458" spans="1:9">
+    <row r="458" ht="30" customHeight="1" spans="1:9">
       <c r="A458" s="2">
         <v>1774</v>
       </c>
@@ -19167,7 +19180,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="459" spans="1:9">
+    <row r="459" ht="30" customHeight="1" spans="1:9">
       <c r="A459" s="2">
         <v>1775</v>
       </c>
@@ -19187,7 +19200,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="460" spans="1:9">
+    <row r="460" ht="30" customHeight="1" spans="1:9">
       <c r="A460" s="2">
         <v>1788</v>
       </c>
@@ -19207,7 +19220,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="461" spans="1:9">
+    <row r="461" ht="30" customHeight="1" spans="1:9">
       <c r="A461" s="2">
         <v>1742</v>
       </c>
@@ -19227,8 +19240,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="462" spans="1:9">
-      <c r="A462" s="6">
+    <row r="462" ht="30" customHeight="1" spans="1:9">
+      <c r="A462" s="9">
         <v>1731</v>
       </c>
       <c r="B462" s="3" t="s">
@@ -19250,7 +19263,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="463" spans="1:9">
+    <row r="463" ht="30" customHeight="1" spans="1:9">
       <c r="A463" s="2">
         <v>1743</v>
       </c>
@@ -19270,7 +19283,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="464" spans="1:9">
+    <row r="464" ht="30" customHeight="1" spans="1:9">
       <c r="A464" s="2">
         <v>1744</v>
       </c>
@@ -19290,7 +19303,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="465" spans="1:9">
+    <row r="465" ht="30" customHeight="1" spans="1:9">
       <c r="A465" s="2">
         <v>1753</v>
       </c>
@@ -19310,7 +19323,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="466" spans="1:9">
+    <row r="466" ht="30" customHeight="1" spans="1:9">
       <c r="A466" s="2">
         <v>1758</v>
       </c>
@@ -19330,7 +19343,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="467" spans="1:9">
+    <row r="467" ht="30" customHeight="1" spans="1:9">
       <c r="A467" s="2">
         <v>1763</v>
       </c>
@@ -19350,7 +19363,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="468" spans="1:9">
+    <row r="468" ht="30" customHeight="1" spans="1:9">
       <c r="A468" s="2">
         <v>1763</v>
       </c>
@@ -19373,7 +19386,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="469" spans="1:9">
+    <row r="469" ht="30" customHeight="1" spans="1:9">
       <c r="A469" s="2">
         <v>1764</v>
       </c>
@@ -19393,7 +19406,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="470" spans="1:9">
+    <row r="470" ht="30" customHeight="1" spans="1:9">
       <c r="A470" s="2">
         <v>1774</v>
       </c>
@@ -19413,8 +19426,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="471" spans="1:9">
-      <c r="A471" s="6">
+    <row r="471" ht="30" customHeight="1" spans="1:9">
+      <c r="A471" s="9">
         <v>1731</v>
       </c>
       <c r="B471" s="3" t="s">
@@ -19436,8 +19449,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="472" spans="1:9">
-      <c r="A472" s="6">
+    <row r="472" ht="30" customHeight="1" spans="1:9">
+      <c r="A472" s="9">
         <v>1737</v>
       </c>
       <c r="B472" s="3" t="s">
@@ -19459,7 +19472,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="473" spans="1:9">
+    <row r="473" ht="30" customHeight="1" spans="1:9">
       <c r="A473" s="2">
         <v>1738</v>
       </c>
@@ -19479,7 +19492,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="474" spans="1:9">
+    <row r="474" ht="30" customHeight="1" spans="1:9">
       <c r="A474" s="2">
         <v>1740</v>
       </c>
@@ -19499,7 +19512,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="475" spans="1:9">
+    <row r="475" ht="30" customHeight="1" spans="1:9">
       <c r="A475" s="2">
         <v>1742</v>
       </c>
@@ -19519,7 +19532,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="476" spans="1:9">
+    <row r="476" ht="30" customHeight="1" spans="1:9">
       <c r="A476" s="2">
         <v>1747</v>
       </c>
@@ -19542,7 +19555,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="477" spans="1:9">
+    <row r="477" ht="30" customHeight="1" spans="1:9">
       <c r="A477" s="2">
         <v>1748</v>
       </c>
@@ -19562,7 +19575,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="478" spans="1:9">
+    <row r="478" ht="30" customHeight="1" spans="1:9">
       <c r="A478" s="2">
         <v>1754</v>
       </c>
@@ -19582,7 +19595,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="479" spans="1:9">
+    <row r="479" ht="30" customHeight="1" spans="1:9">
       <c r="A479" s="2">
         <v>1755</v>
       </c>
@@ -19602,7 +19615,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="480" spans="1:9">
+    <row r="480" ht="30" customHeight="1" spans="1:9">
       <c r="A480" s="2">
         <v>1757</v>
       </c>
@@ -19622,7 +19635,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="481" spans="1:9">
+    <row r="481" ht="30" customHeight="1" spans="1:9">
       <c r="A481" s="2">
         <v>1758</v>
       </c>
@@ -19642,7 +19655,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="482" spans="1:9">
+    <row r="482" ht="30" customHeight="1" spans="1:9">
       <c r="A482" s="2">
         <v>1758</v>
       </c>
@@ -19662,7 +19675,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="483" spans="1:9">
+    <row r="483" ht="30" customHeight="1" spans="1:9">
       <c r="A483" s="2">
         <v>1760</v>
       </c>
@@ -19682,7 +19695,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="484" spans="1:9">
+    <row r="484" ht="30" customHeight="1" spans="1:9">
       <c r="A484" s="2">
         <v>1760</v>
       </c>
@@ -19702,7 +19715,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="485" spans="1:9">
+    <row r="485" ht="30" customHeight="1" spans="1:9">
       <c r="A485" s="2">
         <v>1763</v>
       </c>
@@ -19722,7 +19735,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="486" spans="1:9">
+    <row r="486" ht="30" customHeight="1" spans="1:9">
       <c r="A486" s="2">
         <v>1763</v>
       </c>
@@ -19742,7 +19755,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="487" spans="1:9">
+    <row r="487" ht="30" customHeight="1" spans="1:9">
       <c r="A487" s="2">
         <v>1764</v>
       </c>
@@ -19762,7 +19775,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="488" spans="1:9">
+    <row r="488" ht="30" customHeight="1" spans="1:9">
       <c r="A488" s="2">
         <v>1766</v>
       </c>
@@ -19782,7 +19795,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="489" spans="1:9">
+    <row r="489" ht="30" customHeight="1" spans="1:9">
       <c r="A489" s="2">
         <v>1766</v>
       </c>
@@ -19802,7 +19815,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="490" spans="1:9">
+    <row r="490" ht="30" customHeight="1" spans="1:9">
       <c r="A490" s="2">
         <v>1767</v>
       </c>
@@ -19822,7 +19835,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="491" spans="1:9">
+    <row r="491" ht="30" customHeight="1" spans="1:9">
       <c r="A491" s="2">
         <v>1767</v>
       </c>
@@ -19842,7 +19855,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="492" spans="1:9">
+    <row r="492" ht="30" customHeight="1" spans="1:9">
       <c r="A492" s="2">
         <v>1775.6</v>
       </c>
@@ -19862,7 +19875,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="493" spans="1:9">
+    <row r="493" ht="30" customHeight="1" spans="1:9">
       <c r="A493" s="2">
         <v>1784</v>
       </c>
@@ -19882,7 +19895,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="494" spans="1:9">
+    <row r="494" ht="30" customHeight="1" spans="1:9">
       <c r="A494" s="2">
         <v>1731</v>
       </c>
@@ -19905,8 +19918,8 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="495" spans="1:9">
-      <c r="A495" s="6">
+    <row r="495" ht="30" customHeight="1" spans="1:9">
+      <c r="A495" s="9">
         <v>1731</v>
       </c>
       <c r="B495" s="3" t="s">
@@ -19928,8 +19941,8 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="496" spans="1:9">
-      <c r="A496" s="6">
+    <row r="496" ht="30" customHeight="1" spans="1:9">
+      <c r="A496" s="9">
         <v>1737</v>
       </c>
       <c r="B496" s="3" t="s">
@@ -19951,7 +19964,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="497" spans="1:8">
+    <row r="497" ht="30" customHeight="1" spans="1:8">
       <c r="A497" s="2">
         <v>1741</v>
       </c>
@@ -19971,7 +19984,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="498" spans="1:8">
+    <row r="498" ht="30" customHeight="1" spans="1:8">
       <c r="A498" s="2">
         <v>1744</v>
       </c>
@@ -19991,7 +20004,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="499" spans="1:8">
+    <row r="499" ht="30" customHeight="1" spans="1:8">
       <c r="A499" s="2">
         <v>1745</v>
       </c>
@@ -20011,7 +20024,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="500" spans="1:8">
+    <row r="500" ht="30" customHeight="1" spans="1:8">
       <c r="A500" s="2">
         <v>1745</v>
       </c>
@@ -20031,7 +20044,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="501" spans="1:8">
+    <row r="501" ht="30" customHeight="1" spans="1:8">
       <c r="A501" s="2">
         <v>1746</v>
       </c>
@@ -20051,7 +20064,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="502" spans="1:8">
+    <row r="502" ht="30" customHeight="1" spans="1:8">
       <c r="A502" s="2">
         <v>1749</v>
       </c>
@@ -20071,7 +20084,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="503" spans="1:8">
+    <row r="503" ht="30" customHeight="1" spans="1:8">
       <c r="A503" s="2">
         <v>1749</v>
       </c>
@@ -20091,7 +20104,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="504" spans="1:8">
+    <row r="504" ht="30" customHeight="1" spans="1:8">
       <c r="A504" s="2">
         <v>1753</v>
       </c>
@@ -20111,7 +20124,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="505" spans="1:8">
+    <row r="505" ht="30" customHeight="1" spans="1:8">
       <c r="A505" s="2">
         <v>1757</v>
       </c>
@@ -20131,7 +20144,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="506" spans="1:8">
+    <row r="506" ht="30" customHeight="1" spans="1:8">
       <c r="A506" s="2">
         <v>1760</v>
       </c>
@@ -20151,7 +20164,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="507" spans="1:8">
+    <row r="507" ht="30" customHeight="1" spans="1:8">
       <c r="A507" s="2">
         <v>1760</v>
       </c>
@@ -20171,7 +20184,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="508" spans="1:8">
+    <row r="508" ht="30" customHeight="1" spans="1:8">
       <c r="A508" s="2">
         <v>1760</v>
       </c>
@@ -20191,7 +20204,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="509" spans="1:8">
+    <row r="509" ht="30" customHeight="1" spans="1:8">
       <c r="A509" s="2">
         <v>1762</v>
       </c>
@@ -20211,7 +20224,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="510" spans="1:8">
+    <row r="510" ht="30" customHeight="1" spans="1:8">
       <c r="A510" s="2">
         <v>1762</v>
       </c>
@@ -20231,7 +20244,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="511" spans="1:8">
+    <row r="511" ht="30" customHeight="1" spans="1:8">
       <c r="A511" s="2">
         <v>1763</v>
       </c>
@@ -20251,7 +20264,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="512" ht="51" customHeight="1" spans="1:8">
+    <row r="512" ht="30" customHeight="1" spans="1:8">
       <c r="A512" s="2">
         <v>1766</v>
       </c>
@@ -20271,7 +20284,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="513" spans="1:9">
+    <row r="513" ht="30" customHeight="1" spans="1:9">
       <c r="A513" s="2">
         <v>1766</v>
       </c>
@@ -20291,7 +20304,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="514" spans="1:9">
+    <row r="514" ht="30" customHeight="1" spans="1:9">
       <c r="A514" s="2">
         <v>1773</v>
       </c>
@@ -20311,7 +20324,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="515" spans="1:9">
+    <row r="515" ht="30" customHeight="1" spans="1:9">
       <c r="A515" s="2">
         <v>1775</v>
       </c>
@@ -20331,7 +20344,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="516" spans="1:9">
+    <row r="516" ht="30" customHeight="1" spans="1:9">
       <c r="A516" s="2">
         <v>1775</v>
       </c>
@@ -20351,7 +20364,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="517" spans="1:9">
+    <row r="517" ht="30" customHeight="1" spans="1:9">
       <c r="A517" s="2">
         <v>1775</v>
       </c>
@@ -20371,7 +20384,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="518" spans="1:9">
+    <row r="518" ht="30" customHeight="1" spans="1:9">
       <c r="A518" s="2">
         <v>1775.6</v>
       </c>
@@ -20391,7 +20404,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="519" spans="1:9">
+    <row r="519" ht="30" customHeight="1" spans="1:9">
       <c r="A519" s="2">
         <v>1777</v>
       </c>
@@ -20411,7 +20424,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="520" spans="1:9">
+    <row r="520" ht="30" customHeight="1" spans="1:9">
       <c r="A520" s="2">
         <v>1741</v>
       </c>
@@ -20431,7 +20444,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="521" spans="1:9">
+    <row r="521" ht="30" customHeight="1" spans="1:9">
       <c r="A521" s="2">
         <v>1749</v>
       </c>
@@ -20451,7 +20464,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="522" spans="1:9">
+    <row r="522" ht="30" customHeight="1" spans="1:9">
       <c r="A522" s="2">
         <v>1757</v>
       </c>
@@ -20471,7 +20484,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="523" spans="1:9">
+    <row r="523" ht="30" customHeight="1" spans="1:9">
       <c r="A523" s="2">
         <v>1758</v>
       </c>
@@ -20491,7 +20504,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="524" spans="1:9">
+    <row r="524" ht="30" customHeight="1" spans="1:9">
       <c r="A524" s="2">
         <v>1759</v>
       </c>
@@ -20511,7 +20524,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="525" spans="1:9">
+    <row r="525" ht="30" customHeight="1" spans="1:9">
       <c r="A525" s="2">
         <v>1763</v>
       </c>
@@ -20531,7 +20544,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="526" spans="1:9">
+    <row r="526" ht="30" customHeight="1" spans="1:9">
       <c r="A526" s="2">
         <v>1766</v>
       </c>
@@ -20551,8 +20564,8 @@
         <v>650</v>
       </c>
     </row>
-    <row r="527" spans="1:9">
-      <c r="A527" s="6">
+    <row r="527" ht="30" customHeight="1" spans="1:9">
+      <c r="A527" s="9">
         <v>1731</v>
       </c>
       <c r="B527" s="3" t="s">
@@ -20574,7 +20587,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="528" spans="1:9">
+    <row r="528" ht="30" customHeight="1" spans="1:9">
       <c r="A528" s="2">
         <v>1738</v>
       </c>
@@ -20594,7 +20607,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="529" spans="1:9">
+    <row r="529" ht="30" customHeight="1" spans="1:9">
       <c r="A529" s="2">
         <v>1740</v>
       </c>
@@ -20614,7 +20627,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="530" spans="1:9">
+    <row r="530" ht="30" customHeight="1" spans="1:9">
       <c r="A530" s="2">
         <v>1740</v>
       </c>
@@ -20634,7 +20647,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="531" spans="1:9">
+    <row r="531" ht="30" customHeight="1" spans="1:9">
       <c r="A531" s="2">
         <v>1744</v>
       </c>
@@ -20654,7 +20667,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="532" spans="1:9">
+    <row r="532" ht="30" customHeight="1" spans="1:9">
       <c r="A532" s="2">
         <v>1747</v>
       </c>
@@ -20674,7 +20687,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="533" ht="66" customHeight="1" spans="1:9">
+    <row r="533" ht="30" customHeight="1" spans="1:9">
       <c r="A533" s="2">
         <v>1747</v>
       </c>
@@ -20694,7 +20707,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="534" spans="1:9">
+    <row r="534" ht="30" customHeight="1" spans="1:9">
       <c r="A534" s="2">
         <v>1752</v>
       </c>
@@ -20714,7 +20727,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="535" spans="1:9">
+    <row r="535" ht="30" customHeight="1" spans="1:9">
       <c r="A535" s="2">
         <v>1754</v>
       </c>
@@ -20737,7 +20750,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="536" spans="1:9">
+    <row r="536" ht="30" customHeight="1" spans="1:9">
       <c r="A536" s="2">
         <v>1755</v>
       </c>
@@ -20757,7 +20770,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="537" spans="1:9">
+    <row r="537" ht="30" customHeight="1" spans="1:9">
       <c r="A537" s="2">
         <v>1763</v>
       </c>
@@ -20777,7 +20790,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="538" spans="1:9">
+    <row r="538" ht="30" customHeight="1" spans="1:9">
       <c r="A538" s="2">
         <v>1765</v>
       </c>
@@ -20797,7 +20810,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="539" spans="1:9">
+    <row r="539" ht="30" customHeight="1" spans="1:9">
       <c r="A539" s="2">
         <v>1775</v>
       </c>
@@ -20817,7 +20830,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="540" spans="1:9">
+    <row r="540" ht="30" customHeight="1" spans="1:9">
       <c r="A540" s="2">
         <v>1775.6</v>
       </c>
@@ -20837,7 +20850,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="541" spans="1:9">
+    <row r="541" ht="30" customHeight="1" spans="1:9">
       <c r="A541" s="2">
         <v>1777</v>
       </c>
@@ -20857,7 +20870,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="542" spans="1:9">
+    <row r="542" ht="30" customHeight="1" spans="1:9">
       <c r="A542" s="2">
         <v>1785</v>
       </c>
@@ -20877,7 +20890,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="543" spans="1:9">
+    <row r="543" ht="30" customHeight="1" spans="1:9">
       <c r="A543" s="2">
         <v>1788</v>
       </c>
@@ -20897,8 +20910,8 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="544" spans="1:9">
-      <c r="A544" s="6">
+    <row r="544" ht="30" customHeight="1" spans="1:9">
+      <c r="A544" s="9">
         <v>1731</v>
       </c>
       <c r="B544" s="3" t="s">
@@ -20920,8 +20933,8 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="545" spans="1:9">
-      <c r="A545" s="6">
+    <row r="545" ht="30" customHeight="1" spans="1:9">
+      <c r="A545" s="9">
         <v>1731</v>
       </c>
       <c r="B545" s="3" t="s">
@@ -20946,8 +20959,8 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="546" spans="1:9">
-      <c r="A546" s="6">
+    <row r="546" ht="30" customHeight="1" spans="1:9">
+      <c r="A546" s="9">
         <v>1732</v>
       </c>
       <c r="B546" s="3" t="s">
@@ -20969,7 +20982,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="547" spans="1:9">
+    <row r="547" ht="30" customHeight="1" spans="1:9">
       <c r="A547" s="2">
         <v>1744</v>
       </c>
@@ -20989,7 +21002,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="548" spans="1:9">
+    <row r="548" ht="30" customHeight="1" spans="1:9">
       <c r="A548" s="2">
         <v>1747</v>
       </c>
@@ -21009,7 +21022,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="549" spans="1:9">
+    <row r="549" ht="30" customHeight="1" spans="1:9">
       <c r="A549" s="2">
         <v>1748</v>
       </c>
@@ -21029,7 +21042,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="550" spans="1:9">
+    <row r="550" ht="30" customHeight="1" spans="1:9">
       <c r="A550" s="2">
         <v>1749</v>
       </c>
@@ -21049,7 +21062,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="551" spans="1:9">
+    <row r="551" ht="30" customHeight="1" spans="1:9">
       <c r="A551" s="2">
         <v>1753</v>
       </c>
@@ -21069,7 +21082,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="552" spans="1:9">
+    <row r="552" ht="30" customHeight="1" spans="1:9">
       <c r="A552" s="2">
         <v>1756</v>
       </c>
@@ -21089,7 +21102,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="553" spans="1:9">
+    <row r="553" ht="30" customHeight="1" spans="1:9">
       <c r="A553" s="2">
         <v>1758</v>
       </c>
@@ -21109,7 +21122,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="554" spans="1:9">
+    <row r="554" ht="30" customHeight="1" spans="1:9">
       <c r="A554" s="2">
         <v>1759</v>
       </c>
@@ -21129,7 +21142,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="555" spans="1:9">
+    <row r="555" ht="30" customHeight="1" spans="1:9">
       <c r="A555" s="2">
         <v>1759</v>
       </c>
@@ -21149,7 +21162,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="556" spans="1:9">
+    <row r="556" ht="30" customHeight="1" spans="1:9">
       <c r="A556" s="2">
         <v>1763</v>
       </c>
@@ -21169,7 +21182,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="557" spans="1:9">
+    <row r="557" ht="30" customHeight="1" spans="1:9">
       <c r="A557" s="2">
         <v>1765</v>
       </c>
@@ -21189,7 +21202,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="558" spans="1:9">
+    <row r="558" ht="30" customHeight="1" spans="1:9">
       <c r="A558" s="2">
         <v>1766</v>
       </c>
@@ -21209,7 +21222,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="559" spans="1:9">
+    <row r="559" ht="30" customHeight="1" spans="1:9">
       <c r="A559" s="2">
         <v>1741</v>
       </c>
@@ -21229,7 +21242,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="560" spans="1:9">
+    <row r="560" ht="30" customHeight="1" spans="1:9">
       <c r="A560" s="2">
         <v>1744</v>
       </c>
@@ -21249,7 +21262,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="561" spans="1:9">
+    <row r="561" ht="30" customHeight="1" spans="1:9">
       <c r="A561" s="2">
         <v>1749</v>
       </c>
@@ -21269,7 +21282,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="562" spans="1:9">
+    <row r="562" ht="30" customHeight="1" spans="1:9">
       <c r="A562" s="2">
         <v>1749</v>
       </c>
@@ -21289,7 +21302,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="563" spans="1:9">
+    <row r="563" ht="30" customHeight="1" spans="1:9">
       <c r="A563" s="2">
         <v>1755</v>
       </c>
@@ -21309,7 +21322,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="564" spans="1:9">
+    <row r="564" ht="30" customHeight="1" spans="1:9">
       <c r="A564" s="2">
         <v>1757</v>
       </c>
@@ -21329,7 +21342,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="565" spans="1:9">
+    <row r="565" ht="30" customHeight="1" spans="1:9">
       <c r="A565" s="2">
         <v>1762</v>
       </c>
@@ -21349,7 +21362,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="566" spans="1:9">
+    <row r="566" ht="30" customHeight="1" spans="1:9">
       <c r="A566" s="2">
         <v>1766</v>
       </c>
@@ -21369,8 +21382,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="567" spans="1:9">
-      <c r="A567" s="6">
+    <row r="567" ht="30" customHeight="1" spans="1:9">
+      <c r="A567" s="9">
         <v>1731</v>
       </c>
       <c r="B567" s="3" t="s">
@@ -21392,8 +21405,8 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="568" spans="1:9">
-      <c r="A568" s="6">
+    <row r="568" ht="30" customHeight="1" spans="1:9">
+      <c r="A568" s="9">
         <v>1733</v>
       </c>
       <c r="B568" s="3" t="s">
@@ -21415,8 +21428,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="569" spans="1:9">
-      <c r="A569" s="6">
+    <row r="569" ht="30" customHeight="1" spans="1:9">
+      <c r="A569" s="9">
         <v>1735</v>
       </c>
       <c r="B569" s="3" t="s">
@@ -21438,7 +21451,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="570" spans="1:9">
+    <row r="570" ht="30" customHeight="1" spans="1:9">
       <c r="A570" s="2">
         <v>1737</v>
       </c>
@@ -21458,7 +21471,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="571" spans="1:9">
+    <row r="571" ht="30" customHeight="1" spans="1:9">
       <c r="A571" s="2">
         <v>1743</v>
       </c>
@@ -21478,7 +21491,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="572" spans="1:9">
+    <row r="572" ht="30" customHeight="1" spans="1:9">
       <c r="A572" s="2">
         <v>1747</v>
       </c>
@@ -21498,7 +21511,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="573" spans="1:9">
+    <row r="573" ht="30" customHeight="1" spans="1:9">
       <c r="A573" s="2">
         <v>1751</v>
       </c>
@@ -21518,7 +21531,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="574" spans="1:9">
+    <row r="574" ht="30" customHeight="1" spans="1:9">
       <c r="A574" s="2">
         <v>1756</v>
       </c>
@@ -21538,7 +21551,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="575" spans="1:9">
+    <row r="575" ht="30" customHeight="1" spans="1:9">
       <c r="A575" s="2">
         <v>1758</v>
       </c>
@@ -21558,7 +21571,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="576" spans="1:9">
+    <row r="576" ht="30" customHeight="1" spans="1:9">
       <c r="A576" s="2">
         <v>1763</v>
       </c>
@@ -21578,7 +21591,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="577" spans="1:9">
+    <row r="577" ht="30" customHeight="1" spans="1:9">
       <c r="A577" s="2">
         <v>1765</v>
       </c>
@@ -21598,7 +21611,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="578" spans="1:9">
+    <row r="578" ht="30" customHeight="1" spans="1:9">
       <c r="A578" s="2">
         <v>1775.6</v>
       </c>
@@ -21618,7 +21631,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="579" spans="1:9">
+    <row r="579" ht="30" customHeight="1" spans="1:9">
       <c r="A579" s="2">
         <v>1777</v>
       </c>
@@ -21638,7 +21651,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="580" spans="1:9">
+    <row r="580" ht="30" customHeight="1" spans="1:9">
       <c r="A580" s="2">
         <v>1784</v>
       </c>
@@ -21658,8 +21671,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="581" spans="1:9">
-      <c r="A581" s="6">
+    <row r="581" ht="30" customHeight="1" spans="1:9">
+      <c r="A581" s="9">
         <v>1736</v>
       </c>
       <c r="B581" s="3" t="s">
@@ -21681,7 +21694,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="582" spans="1:9">
+    <row r="582" ht="30" customHeight="1" spans="1:9">
       <c r="A582" s="2">
         <v>1743</v>
       </c>
@@ -21701,7 +21714,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="583" spans="1:9">
+    <row r="583" ht="30" customHeight="1" spans="1:9">
       <c r="A583" s="2">
         <v>1747</v>
       </c>
@@ -21721,7 +21734,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="584" spans="1:9">
+    <row r="584" ht="30" customHeight="1" spans="1:9">
       <c r="A584" s="2">
         <v>1753</v>
       </c>
@@ -21741,7 +21754,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="585" spans="1:9">
+    <row r="585" ht="30" customHeight="1" spans="1:9">
       <c r="A585" s="2">
         <v>1754</v>
       </c>
@@ -21761,7 +21774,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="586" spans="1:9">
+    <row r="586" ht="30" customHeight="1" spans="1:9">
       <c r="A586" s="2">
         <v>1765</v>
       </c>
@@ -21781,7 +21794,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="587" spans="1:9">
+    <row r="587" ht="30" customHeight="1" spans="1:9">
       <c r="A587" s="2">
         <v>1767</v>
       </c>
@@ -21801,7 +21814,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="588" spans="1:9">
+    <row r="588" ht="30" customHeight="1" spans="1:9">
       <c r="A588" s="2">
         <v>1767</v>
       </c>
@@ -21821,7 +21834,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="589" spans="1:9">
+    <row r="589" ht="30" customHeight="1" spans="1:9">
       <c r="A589" s="2">
         <v>1767</v>
       </c>
@@ -21841,7 +21854,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="590" spans="1:9">
+    <row r="590" ht="30" customHeight="1" spans="1:9">
       <c r="A590" s="2">
         <v>1767</v>
       </c>
@@ -21861,7 +21874,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="591" spans="1:9">
+    <row r="591" ht="30" customHeight="1" spans="1:9">
       <c r="A591" s="2">
         <v>1775</v>
       </c>
@@ -21881,7 +21894,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="592" spans="1:9">
+    <row r="592" ht="30" customHeight="1" spans="1:9">
       <c r="A592" s="2">
         <v>1775.6</v>
       </c>
@@ -21901,7 +21914,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="593" spans="1:9">
+    <row r="593" ht="30" customHeight="1" spans="1:9">
       <c r="A593" s="2">
         <v>1786</v>
       </c>
@@ -21921,8 +21934,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="594" spans="1:9">
-      <c r="A594" s="6">
+    <row r="594" ht="30" customHeight="1" spans="1:9">
+      <c r="A594" s="9">
         <v>1731</v>
       </c>
       <c r="B594" s="3" t="s">
@@ -21944,7 +21957,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="595" spans="1:9">
+    <row r="595" ht="30" customHeight="1" spans="1:9">
       <c r="A595" s="2">
         <v>1740</v>
       </c>
@@ -21964,7 +21977,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="596" spans="1:9">
+    <row r="596" ht="30" customHeight="1" spans="1:9">
       <c r="A596" s="2">
         <v>1746</v>
       </c>
@@ -21984,7 +21997,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="597" spans="1:9">
+    <row r="597" ht="30" customHeight="1" spans="1:9">
       <c r="A597" s="2">
         <v>1746</v>
       </c>
@@ -22004,7 +22017,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="598" spans="1:9">
+    <row r="598" ht="30" customHeight="1" spans="1:9">
       <c r="A598" s="2">
         <v>1747</v>
       </c>
@@ -22024,7 +22037,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="599" spans="1:9">
+    <row r="599" ht="30" customHeight="1" spans="1:9">
       <c r="A599" s="2">
         <v>1747</v>
       </c>
@@ -22044,7 +22057,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="600" spans="1:9">
+    <row r="600" ht="30" customHeight="1" spans="1:9">
       <c r="A600" s="2">
         <v>1748</v>
       </c>
@@ -22064,7 +22077,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="601" spans="1:9">
+    <row r="601" ht="30" customHeight="1" spans="1:9">
       <c r="A601" s="2">
         <v>1749</v>
       </c>
@@ -22084,7 +22097,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="602" spans="1:9">
+    <row r="602" ht="30" customHeight="1" spans="1:9">
       <c r="A602" s="2">
         <v>1755</v>
       </c>
@@ -22104,7 +22117,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="603" spans="1:9">
+    <row r="603" ht="30" customHeight="1" spans="1:9">
       <c r="A603" s="2">
         <v>1755</v>
       </c>
@@ -22124,7 +22137,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="604" spans="1:9">
+    <row r="604" ht="30" customHeight="1" spans="1:9">
       <c r="A604" s="2">
         <v>1756</v>
       </c>
@@ -22144,7 +22157,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="605" spans="1:9">
+    <row r="605" ht="30" customHeight="1" spans="1:9">
       <c r="A605" s="2">
         <v>1758</v>
       </c>
@@ -22164,7 +22177,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="606" spans="1:9">
+    <row r="606" ht="30" customHeight="1" spans="1:9">
       <c r="A606" s="2">
         <v>1759</v>
       </c>
@@ -22184,7 +22197,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="607" spans="1:9">
+    <row r="607" ht="30" customHeight="1" spans="1:9">
       <c r="A607" s="2">
         <v>1759</v>
       </c>
@@ -22204,7 +22217,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="608" spans="1:9">
+    <row r="608" ht="30" customHeight="1" spans="1:9">
       <c r="A608" s="2">
         <v>1763</v>
       </c>
@@ -22224,7 +22237,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="609" spans="1:9">
+    <row r="609" ht="30" customHeight="1" spans="1:9">
       <c r="A609" s="2">
         <v>1764</v>
       </c>
@@ -22244,7 +22257,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="610" spans="1:9">
+    <row r="610" ht="30" customHeight="1" spans="1:9">
       <c r="A610" s="2">
         <v>1766</v>
       </c>
@@ -22264,7 +22277,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="611" spans="1:9">
+    <row r="611" ht="30" customHeight="1" spans="1:9">
       <c r="A611" s="2">
         <v>1769</v>
       </c>
@@ -22284,7 +22297,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="612" spans="1:9">
+    <row r="612" ht="30" customHeight="1" spans="1:9">
       <c r="A612" s="2">
         <v>1772</v>
       </c>
@@ -22304,7 +22317,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="613" spans="1:9">
+    <row r="613" ht="30" customHeight="1" spans="1:9">
       <c r="A613" s="2">
         <v>1775</v>
       </c>
@@ -22324,7 +22337,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="614" spans="1:9">
+    <row r="614" ht="30" customHeight="1" spans="1:9">
       <c r="A614" s="2">
         <v>1777</v>
       </c>
@@ -22344,7 +22357,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="615" spans="1:9">
+    <row r="615" ht="30" customHeight="1" spans="1:9">
       <c r="A615" s="2">
         <v>1780</v>
       </c>
@@ -22364,7 +22377,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="616" spans="1:9">
+    <row r="616" ht="30" customHeight="1" spans="1:9">
       <c r="A616" s="2">
         <v>1744</v>
       </c>
@@ -22384,7 +22397,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="617" spans="1:9">
+    <row r="617" ht="30" customHeight="1" spans="1:9">
       <c r="A617" s="2">
         <v>1753</v>
       </c>
@@ -22404,7 +22417,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="618" spans="1:9">
+    <row r="618" ht="30" customHeight="1" spans="1:9">
       <c r="A618" s="2">
         <v>1763</v>
       </c>
@@ -22424,7 +22437,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="619" spans="1:9">
+    <row r="619" ht="30" customHeight="1" spans="1:9">
       <c r="A619" s="2">
         <v>1744</v>
       </c>
@@ -22444,7 +22457,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="620" spans="1:9">
+    <row r="620" ht="30" customHeight="1" spans="1:9">
       <c r="A620" s="2">
         <v>1735</v>
       </c>
@@ -22464,7 +22477,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="621" spans="1:9">
+    <row r="621" ht="30" customHeight="1" spans="1:9">
       <c r="A621" s="2">
         <v>1735</v>
       </c>
@@ -22484,8 +22497,8 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="622" spans="1:9">
-      <c r="A622" s="6">
+    <row r="622" ht="30" customHeight="1" spans="1:9">
+      <c r="A622" s="9">
         <v>1736</v>
       </c>
       <c r="B622" s="3" t="s">
@@ -22507,7 +22520,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="623" spans="1:9">
+    <row r="623" ht="30" customHeight="1" spans="1:9">
       <c r="A623" s="2">
         <v>1739</v>
       </c>
@@ -22527,7 +22540,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="624" spans="1:9">
+    <row r="624" ht="30" customHeight="1" spans="1:9">
       <c r="A624" s="2">
         <v>1739</v>
       </c>
@@ -22547,7 +22560,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="625" spans="1:9">
+    <row r="625" ht="30" customHeight="1" spans="1:9">
       <c r="A625" s="2">
         <v>1740</v>
       </c>
@@ -22567,7 +22580,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="626" spans="1:9">
+    <row r="626" ht="30" customHeight="1" spans="1:9">
       <c r="A626" s="2">
         <v>1745</v>
       </c>
@@ -22587,7 +22600,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="627" spans="1:9">
+    <row r="627" ht="30" customHeight="1" spans="1:9">
       <c r="A627" s="2">
         <v>1747</v>
       </c>
@@ -22607,7 +22620,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="628" spans="1:9">
+    <row r="628" ht="30" customHeight="1" spans="1:9">
       <c r="A628" s="2">
         <v>1748</v>
       </c>
@@ -22627,7 +22640,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="629" spans="1:9">
+    <row r="629" ht="30" customHeight="1" spans="1:9">
       <c r="A629" s="2">
         <v>1750</v>
       </c>
@@ -22647,7 +22660,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="630" spans="1:9">
+    <row r="630" ht="30" customHeight="1" spans="1:9">
       <c r="A630" s="2">
         <v>1750</v>
       </c>
@@ -22667,7 +22680,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="631" spans="1:9">
+    <row r="631" ht="30" customHeight="1" spans="1:9">
       <c r="A631" s="2">
         <v>1754</v>
       </c>
@@ -22687,7 +22700,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="632" spans="1:9">
+    <row r="632" ht="30" customHeight="1" spans="1:9">
       <c r="A632" s="2">
         <v>1754</v>
       </c>
@@ -22710,7 +22723,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="633" spans="1:9">
+    <row r="633" ht="30" customHeight="1" spans="1:9">
       <c r="A633" s="2">
         <v>1754</v>
       </c>
@@ -22730,7 +22743,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="634" spans="1:9">
+    <row r="634" ht="30" customHeight="1" spans="1:9">
       <c r="A634" s="2">
         <v>1754</v>
       </c>
@@ -22750,7 +22763,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="635" spans="1:9">
+    <row r="635" ht="30" customHeight="1" spans="1:9">
       <c r="A635" s="2">
         <v>1755</v>
       </c>
@@ -22770,7 +22783,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="636" spans="1:9">
+    <row r="636" ht="30" customHeight="1" spans="1:9">
       <c r="A636" s="2">
         <v>1755</v>
       </c>
@@ -22790,7 +22803,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="637" spans="1:9">
+    <row r="637" ht="30" customHeight="1" spans="1:9">
       <c r="A637" s="2">
         <v>1757</v>
       </c>
@@ -22810,7 +22823,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="638" spans="1:9">
+    <row r="638" ht="30" customHeight="1" spans="1:9">
       <c r="A638" s="2">
         <v>1759</v>
       </c>
@@ -22830,7 +22843,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="639" spans="1:9">
+    <row r="639" ht="30" customHeight="1" spans="1:9">
       <c r="A639" s="2">
         <v>1763</v>
       </c>
@@ -22853,7 +22866,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="640" spans="1:9">
+    <row r="640" ht="30" customHeight="1" spans="1:9">
       <c r="A640" s="2">
         <v>1765</v>
       </c>
@@ -22873,7 +22886,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="641" spans="1:8">
+    <row r="641" ht="30" customHeight="1" spans="1:8">
       <c r="A641" s="2">
         <v>1774</v>
       </c>
@@ -22893,7 +22906,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="642" spans="1:8">
+    <row r="642" ht="30" customHeight="1" spans="1:8">
       <c r="A642" s="2">
         <v>1775</v>
       </c>
@@ -22913,7 +22926,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="643" spans="1:8">
+    <row r="643" ht="30" customHeight="1" spans="1:8">
       <c r="A643" s="2">
         <v>1775</v>
       </c>
@@ -22933,7 +22946,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="644" spans="1:8">
+    <row r="644" ht="30" customHeight="1" spans="1:8">
       <c r="A644" s="2">
         <v>1781</v>
       </c>
@@ -22953,7 +22966,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="645" spans="1:8">
+    <row r="645" ht="30" customHeight="1" spans="1:8">
       <c r="A645" s="2">
         <v>1783</v>
       </c>
@@ -22973,7 +22986,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="646" spans="1:8">
+    <row r="646" ht="30" customHeight="1" spans="1:8">
       <c r="A646" s="2">
         <v>1785</v>
       </c>
@@ -22993,7 +23006,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="647" spans="1:8">
+    <row r="647" ht="30" customHeight="1" spans="1:8">
       <c r="A647" s="2">
         <v>1786</v>
       </c>
@@ -23013,7 +23026,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="648" spans="1:8">
+    <row r="648" ht="30" customHeight="1" spans="1:8">
       <c r="A648" s="2">
         <v>1786</v>
       </c>
@@ -23033,7 +23046,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="649" spans="1:8">
+    <row r="649" ht="30" customHeight="1" spans="1:8">
       <c r="A649" s="2">
         <v>1788</v>
       </c>
@@ -23053,7 +23066,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="650" spans="1:8">
+    <row r="650" ht="30" customHeight="1" spans="1:8">
       <c r="A650" s="2">
         <v>1739</v>
       </c>
@@ -23073,7 +23086,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="651" spans="1:8">
+    <row r="651" ht="30" customHeight="1" spans="1:8">
       <c r="A651" s="2">
         <v>1746</v>
       </c>
@@ -23093,7 +23106,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="652" spans="1:8">
+    <row r="652" ht="30" customHeight="1" spans="1:8">
       <c r="A652" s="2">
         <v>1750</v>
       </c>
@@ -23113,7 +23126,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="653" spans="1:8">
+    <row r="653" ht="30" customHeight="1" spans="1:8">
       <c r="A653" s="2">
         <v>1752</v>
       </c>
@@ -23133,7 +23146,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="654" spans="1:8">
+    <row r="654" ht="30" customHeight="1" spans="1:8">
       <c r="A654" s="2">
         <v>1755</v>
       </c>
@@ -23153,7 +23166,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="655" spans="1:8">
+    <row r="655" ht="30" customHeight="1" spans="1:8">
       <c r="A655" s="2">
         <v>1757</v>
       </c>
@@ -23173,7 +23186,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="656" spans="1:8">
+    <row r="656" ht="30" customHeight="1" spans="1:8">
       <c r="A656" s="2">
         <v>1759</v>
       </c>
@@ -23193,7 +23206,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="657" spans="1:8">
+    <row r="657" ht="30" customHeight="1" spans="1:8">
       <c r="A657" s="2">
         <v>1761</v>
       </c>
@@ -23213,7 +23226,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="658" spans="1:8">
+    <row r="658" ht="30" customHeight="1" spans="1:8">
       <c r="A658" s="2">
         <v>1766</v>
       </c>
@@ -23233,7 +23246,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="659" spans="1:8">
+    <row r="659" ht="30" customHeight="1" spans="1:8">
       <c r="A659" s="2">
         <v>1766</v>
       </c>
@@ -23253,7 +23266,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="660" spans="1:8">
+    <row r="660" ht="30" customHeight="1" spans="1:8">
       <c r="A660" s="2">
         <v>1740.2</v>
       </c>
@@ -23270,7 +23283,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="661" spans="1:8">
+    <row r="661" ht="30" customHeight="1" spans="1:8">
       <c r="A661" s="2">
         <v>1742.4</v>
       </c>
@@ -23287,7 +23300,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="662" spans="1:8">
+    <row r="662" ht="30" customHeight="1" spans="1:8">
       <c r="A662" s="2">
         <v>1758.9</v>
       </c>
@@ -23304,7 +23317,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="663" spans="1:8">
+    <row r="663" ht="30" customHeight="1" spans="1:8">
       <c r="A663" s="2">
         <v>1762</v>
       </c>
@@ -23318,7 +23331,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="664" spans="1:8">
+    <row r="664" ht="30" customHeight="1" spans="1:8">
       <c r="A664" s="2">
         <v>1762.4</v>
       </c>
@@ -23335,7 +23348,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="665" spans="1:8">
+    <row r="665" ht="30" customHeight="1" spans="1:8">
       <c r="A665" s="2">
         <v>1765.6</v>
       </c>
@@ -23352,7 +23365,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="666" spans="1:8">
+    <row r="666" ht="30" customHeight="1" spans="1:8">
       <c r="A666" s="2">
         <v>1767</v>
       </c>
@@ -23369,7 +23382,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="667" spans="1:8">
+    <row r="667" ht="30" customHeight="1" spans="1:8">
       <c r="A667" s="2">
         <v>1775</v>
       </c>
@@ -23386,7 +23399,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="668" spans="1:8">
+    <row r="668" ht="30" customHeight="1" spans="1:8">
       <c r="A668" s="2">
         <v>1775</v>
       </c>
@@ -23403,7 +23416,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="669" spans="1:8">
+    <row r="669" ht="30" customHeight="1" spans="1:8">
       <c r="A669" s="2">
         <v>1777</v>
       </c>
@@ -23420,7 +23433,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="670" spans="1:8">
+    <row r="670" ht="30" customHeight="1" spans="1:8">
       <c r="A670" s="2">
         <v>1784</v>
       </c>
@@ -23437,7 +23450,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="671" spans="1:8">
+    <row r="671" ht="30" customHeight="1" spans="1:8">
       <c r="A671" s="2">
         <v>1785</v>
       </c>
@@ -23454,7 +23467,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="672" spans="1:8">
+    <row r="672" ht="30" customHeight="1" spans="1:8">
       <c r="A672" s="2" t="s">
         <v>1697</v>
       </c>
@@ -23471,7 +23484,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="673" spans="1:9">
+    <row r="673" ht="30" customHeight="1" spans="1:9">
       <c r="A673" s="2" t="s">
         <v>1700</v>
       </c>
@@ -23488,7 +23501,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="674" spans="1:9">
+    <row r="674" ht="30" customHeight="1" spans="1:9">
       <c r="A674" s="2" t="s">
         <v>1703</v>
       </c>
@@ -23505,7 +23518,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="675" spans="1:9">
+    <row r="675" ht="30" customHeight="1" spans="1:9">
       <c r="A675" s="2" t="s">
         <v>1705</v>
       </c>
@@ -23522,7 +23535,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="676" spans="1:9">
+    <row r="676" ht="30" customHeight="1" spans="1:9">
       <c r="A676" s="2" t="s">
         <v>1707</v>
       </c>
@@ -23539,7 +23552,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="677" spans="1:9">
+    <row r="677" ht="30" customHeight="1" spans="1:9">
       <c r="A677" s="2" t="s">
         <v>1710</v>
       </c>
@@ -23556,7 +23569,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="678" spans="1:9">
+    <row r="678" ht="30" customHeight="1" spans="1:9">
       <c r="A678" s="2" t="s">
         <v>1713</v>
       </c>
@@ -23573,7 +23586,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="679" spans="1:9">
+    <row r="679" ht="30" customHeight="1" spans="1:9">
       <c r="A679" s="2" t="s">
         <v>1715</v>
       </c>
@@ -23590,7 +23603,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="680" spans="1:9">
+    <row r="680" ht="30" customHeight="1" spans="1:9">
       <c r="A680" s="2" t="s">
         <v>1718</v>
       </c>
@@ -23607,7 +23620,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="681" spans="1:9">
+    <row r="681" ht="30" customHeight="1" spans="1:9">
       <c r="A681" s="2" t="s">
         <v>1720</v>
       </c>
@@ -23624,7 +23637,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="682" spans="1:9">
+    <row r="682" ht="30" customHeight="1" spans="1:9">
       <c r="B682" s="3" t="s">
         <v>1722</v>
       </c>
@@ -23638,7 +23651,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="683" spans="1:9">
+    <row r="683" ht="30" customHeight="1" spans="1:9">
       <c r="B683" s="3" t="s">
         <v>1723</v>
       </c>
@@ -23652,8 +23665,8 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="684" spans="1:9">
-      <c r="A684" s="6">
+    <row r="684" ht="30" customHeight="1" spans="1:9">
+      <c r="A684" s="9">
         <v>1734</v>
       </c>
       <c r="B684" s="3" t="s">
@@ -23675,7 +23688,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="685" spans="1:9">
+    <row r="685" ht="30" customHeight="1" spans="1:9">
       <c r="A685" s="2">
         <v>1763</v>
       </c>
@@ -23695,7 +23708,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="686" spans="1:9">
+    <row r="686" ht="30" customHeight="1" spans="1:9">
       <c r="A686" s="2">
         <v>1786</v>
       </c>
@@ -23715,7 +23728,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="687" spans="1:9">
+    <row r="687" ht="30" customHeight="1" spans="1:9">
       <c r="A687" s="2">
         <v>1763</v>
       </c>
@@ -23735,7 +23748,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="688" spans="1:9">
+    <row r="688" ht="30" customHeight="1" spans="1:9">
       <c r="A688" s="2">
         <v>1763</v>
       </c>
@@ -23755,7 +23768,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="689" spans="1:9">
+    <row r="689" ht="30" customHeight="1" spans="1:9">
       <c r="A689" s="2">
         <v>1763</v>
       </c>
@@ -23775,8 +23788,8 @@
         <v>182</v>
       </c>
     </row>
-    <row r="690" spans="1:9">
-      <c r="A690" s="6">
+    <row r="690" ht="30" customHeight="1" spans="1:9">
+      <c r="A690" s="9">
         <v>1734</v>
       </c>
       <c r="B690" s="3" t="s">
@@ -23798,7 +23811,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="691" spans="1:9">
+    <row r="691" ht="30" customHeight="1" spans="1:9">
       <c r="A691" s="2">
         <v>1762</v>
       </c>
@@ -23818,7 +23831,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="692" spans="1:9">
+    <row r="692" ht="30" customHeight="1" spans="1:9">
       <c r="A692" s="2">
         <v>1762</v>
       </c>
@@ -23838,7 +23851,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="693" spans="1:9">
+    <row r="693" ht="30" customHeight="1" spans="1:9">
       <c r="A693" s="2">
         <v>1763</v>
       </c>
@@ -23858,7 +23871,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="694" spans="1:9">
+    <row r="694" ht="30" customHeight="1" spans="1:9">
       <c r="A694" s="2">
         <v>1786</v>
       </c>
@@ -23878,7 +23891,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="695" spans="1:9">
+    <row r="695" ht="30" customHeight="1" spans="1:9">
       <c r="A695" s="2">
         <v>1764</v>
       </c>
@@ -23898,7 +23911,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="696" spans="1:9">
+    <row r="696" ht="30" customHeight="1" spans="1:9">
       <c r="A696" s="2">
         <v>1786</v>
       </c>
@@ -23918,7 +23931,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="697" spans="1:9">
+    <row r="697" ht="30" customHeight="1" spans="1:9">
       <c r="A697" s="2">
         <v>1763</v>
       </c>
@@ -23938,7 +23951,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="698" spans="1:9">
+    <row r="698" ht="30" customHeight="1" spans="1:9">
       <c r="A698" s="2">
         <v>1786</v>
       </c>
@@ -23958,7 +23971,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="699" spans="1:9">
+    <row r="699" ht="30" customHeight="1" spans="1:9">
       <c r="A699" s="2">
         <v>1734</v>
       </c>
@@ -23981,8 +23994,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="700" spans="1:9">
-      <c r="A700" s="6">
+    <row r="700" ht="30" customHeight="1" spans="1:9">
+      <c r="A700" s="9">
         <v>1734</v>
       </c>
       <c r="B700" s="3" t="s">
@@ -24004,7 +24017,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="701" spans="1:9">
+    <row r="701" ht="30" customHeight="1" spans="1:9">
       <c r="A701" s="2">
         <v>1764</v>
       </c>
@@ -24024,7 +24037,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="702" spans="1:9">
+    <row r="702" ht="30" customHeight="1" spans="1:9">
       <c r="A702" s="2">
         <v>1764.5</v>
       </c>
@@ -24044,8 +24057,8 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="703" spans="1:9">
-      <c r="A703" s="6">
+    <row r="703" ht="30" customHeight="1" spans="1:9">
+      <c r="A703" s="9">
         <v>1734</v>
       </c>
       <c r="B703" s="3" t="s">
@@ -24067,7 +24080,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="704" spans="1:9">
+    <row r="704" ht="30" customHeight="1" spans="1:9">
       <c r="A704" s="2">
         <v>1762</v>
       </c>
@@ -24087,7 +24100,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="705" spans="1:9">
+    <row r="705" ht="30" customHeight="1" spans="1:9">
       <c r="A705" s="2">
         <v>1764</v>
       </c>
@@ -24107,7 +24120,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="706" spans="1:9">
+    <row r="706" ht="30" customHeight="1" spans="1:9">
       <c r="A706" s="2">
         <v>1786</v>
       </c>
@@ -24127,8 +24140,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="707" spans="1:9">
-      <c r="A707" s="6">
+    <row r="707" ht="30" customHeight="1" spans="1:9">
+      <c r="A707" s="9">
         <v>1734</v>
       </c>
       <c r="B707" s="3" t="s">
@@ -24150,7 +24163,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="708" spans="1:9">
+    <row r="708" ht="30" customHeight="1" spans="1:9">
       <c r="A708" s="2">
         <v>1762</v>
       </c>
@@ -24170,7 +24183,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="709" spans="1:9">
+    <row r="709" ht="30" customHeight="1" spans="1:9">
       <c r="A709" s="2">
         <v>1762</v>
       </c>
@@ -24190,7 +24203,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="710" spans="1:9">
+    <row r="710" ht="30" customHeight="1" spans="1:9">
       <c r="A710" s="2">
         <v>1786</v>
       </c>
@@ -24210,7 +24223,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="711" spans="1:9">
+    <row r="711" ht="30" customHeight="1" spans="1:9">
       <c r="A711" s="2">
         <v>1734</v>
       </c>
@@ -24227,7 +24240,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="712" spans="1:9">
+    <row r="712" ht="30" customHeight="1" spans="1:9">
       <c r="A712" s="2">
         <v>1755</v>
       </c>
@@ -24247,7 +24260,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="713" spans="1:9">
+    <row r="713" ht="30" customHeight="1" spans="1:9">
       <c r="A713" s="2">
         <v>1755</v>
       </c>
@@ -24267,7 +24280,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="714" spans="1:9">
+    <row r="714" ht="30" customHeight="1" spans="1:9">
       <c r="A714" s="2">
         <v>1756</v>
       </c>
@@ -24287,7 +24300,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="715" spans="1:9">
+    <row r="715" ht="30" customHeight="1" spans="1:9">
       <c r="A715" s="2">
         <v>1756</v>
       </c>
@@ -24307,7 +24320,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="716" spans="1:9">
+    <row r="716" ht="30" customHeight="1" spans="1:9">
       <c r="A716" s="2">
         <v>1756</v>
       </c>
@@ -24327,7 +24340,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="717" spans="1:9">
+    <row r="717" ht="30" customHeight="1" spans="1:9">
       <c r="A717" s="2">
         <v>1757</v>
       </c>
@@ -24347,7 +24360,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="718" spans="1:9">
+    <row r="718" ht="30" customHeight="1" spans="1:9">
       <c r="A718" s="2">
         <v>1755</v>
       </c>
@@ -24367,7 +24380,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="719" spans="1:9">
+    <row r="719" ht="30" customHeight="1" spans="1:9">
       <c r="A719" s="2">
         <v>1755</v>
       </c>
@@ -24387,7 +24400,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="720" spans="1:9">
+    <row r="720" ht="30" customHeight="1" spans="1:9">
       <c r="A720" s="2">
         <v>1762</v>
       </c>
@@ -24407,7 +24420,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="721" spans="1:8">
+    <row r="721" ht="30" customHeight="1" spans="1:8">
       <c r="A721" s="2">
         <v>1766</v>
       </c>
@@ -24427,7 +24440,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="722" spans="1:8">
+    <row r="722" ht="30" customHeight="1" spans="1:8">
       <c r="A722" s="2">
         <v>1741</v>
       </c>
@@ -24447,7 +24460,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="723" spans="1:8">
+    <row r="723" ht="30" customHeight="1" spans="1:8">
       <c r="A723" s="2">
         <v>1745</v>
       </c>
@@ -24467,7 +24480,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="724" spans="1:8">
+    <row r="724" ht="30" customHeight="1" spans="1:8">
       <c r="A724" s="2">
         <v>1758</v>
       </c>
@@ -24487,7 +24500,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="725" spans="1:8">
+    <row r="725" ht="30" customHeight="1" spans="1:8">
       <c r="B725" s="3" t="s">
         <v>1814</v>
       </c>
@@ -24504,7 +24517,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="726" spans="1:8">
+    <row r="726" ht="30" customHeight="1" spans="1:8">
       <c r="B726" s="3" t="s">
         <v>1815</v>
       </c>
@@ -24518,7 +24531,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="727" spans="1:8">
+    <row r="727" ht="30" customHeight="1" spans="1:8">
       <c r="A727" s="2">
         <v>1769</v>
       </c>
@@ -24538,7 +24551,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="728" spans="1:8">
+    <row r="728" ht="30" customHeight="1" spans="1:8">
       <c r="A728" s="2">
         <v>1775</v>
       </c>
@@ -24558,7 +24571,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="729" spans="1:8">
+    <row r="729" ht="30" customHeight="1" spans="1:8">
       <c r="A729" s="2">
         <v>1781</v>
       </c>
@@ -24578,7 +24591,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="730" spans="1:8">
+    <row r="730" ht="30" customHeight="1" spans="1:8">
       <c r="A730" s="2">
         <v>1754</v>
       </c>
@@ -24598,7 +24611,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="731" spans="1:8">
+    <row r="731" ht="30" customHeight="1" spans="1:8">
       <c r="A731" s="2">
         <v>1765</v>
       </c>
@@ -24618,7 +24631,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="732" spans="1:8">
+    <row r="732" ht="30" customHeight="1" spans="1:8">
       <c r="A732" s="2">
         <v>1769</v>
       </c>
@@ -24638,7 +24651,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="733" spans="1:8">
+    <row r="733" ht="30" customHeight="1" spans="1:8">
       <c r="A733" s="2">
         <v>1775</v>
       </c>
@@ -24658,7 +24671,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="734" spans="1:8">
+    <row r="734" ht="30" customHeight="1" spans="1:8">
       <c r="B734" s="3" t="s">
         <v>1838</v>
       </c>
@@ -24675,7 +24688,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="735" spans="1:8">
+    <row r="735" ht="30" customHeight="1" spans="1:8">
       <c r="A735" s="2">
         <v>1769</v>
       </c>
@@ -24695,7 +24708,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="736" spans="1:8">
+    <row r="736" ht="30" customHeight="1" spans="1:8">
       <c r="A736" s="2">
         <v>1775</v>
       </c>
@@ -24715,7 +24728,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="737" spans="1:8">
+    <row r="737" ht="30" customHeight="1" spans="1:8">
       <c r="A737" s="2">
         <v>1775</v>
       </c>
@@ -24735,7 +24748,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="738" spans="1:8">
+    <row r="738" ht="30" customHeight="1" spans="1:8">
       <c r="B738" s="3" t="s">
         <v>1851</v>
       </c>
@@ -24752,7 +24765,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="739" spans="1:8">
+    <row r="739" ht="30" customHeight="1" spans="1:8">
       <c r="A739" s="2">
         <v>1760</v>
       </c>
@@ -24772,7 +24785,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="740" spans="1:8">
+    <row r="740" ht="30" customHeight="1" spans="1:8">
       <c r="A740" s="2">
         <v>1769</v>
       </c>
@@ -24792,7 +24805,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="741" spans="1:8">
+    <row r="741" ht="30" customHeight="1" spans="1:8">
       <c r="A741" s="2">
         <v>1775</v>
       </c>
@@ -24809,7 +24822,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="742" spans="1:8">
+    <row r="742" ht="30" customHeight="1" spans="1:8">
       <c r="A742" s="2">
         <v>1775</v>
       </c>
@@ -24829,7 +24842,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="743" spans="1:8">
+    <row r="743" ht="30" customHeight="1" spans="1:8">
       <c r="A743" s="2">
         <v>1775</v>
       </c>
@@ -24849,7 +24862,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="744" spans="1:8">
+    <row r="744" ht="30" customHeight="1" spans="1:8">
       <c r="A744" s="2">
         <v>1775</v>
       </c>
@@ -24869,7 +24882,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="745" spans="1:8">
+    <row r="745" ht="30" customHeight="1" spans="1:8">
       <c r="B745" s="3" t="s">
         <v>1869</v>
       </c>
@@ -24886,7 +24899,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="746" spans="1:8">
+    <row r="746" ht="30" customHeight="1" spans="1:8">
       <c r="B746" s="3" t="s">
         <v>1872</v>
       </c>
@@ -24903,7 +24916,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="747" spans="1:8">
+    <row r="747" ht="30" customHeight="1" spans="1:8">
       <c r="A747" s="2">
         <v>1769</v>
       </c>
@@ -24923,7 +24936,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="748" spans="1:8">
+    <row r="748" ht="30" customHeight="1" spans="1:8">
       <c r="A748" s="2">
         <v>1756</v>
       </c>
@@ -24943,7 +24956,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="749" spans="1:8">
+    <row r="749" ht="30" customHeight="1" spans="1:8">
       <c r="A749" s="2">
         <v>1775</v>
       </c>
@@ -24960,7 +24973,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="750" spans="1:8">
+    <row r="750" ht="30" customHeight="1" spans="1:8">
       <c r="A750" s="2">
         <v>1775</v>
       </c>
@@ -24980,7 +24993,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="751" spans="1:8">
+    <row r="751" ht="30" customHeight="1" spans="1:8">
       <c r="A751" s="2">
         <v>1775</v>
       </c>
@@ -25000,7 +25013,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="752" spans="1:8">
+    <row r="752" ht="30" customHeight="1" spans="1:8">
       <c r="A752" s="2">
         <v>1775</v>
       </c>
@@ -25017,7 +25030,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="753" spans="1:8">
+    <row r="753" ht="30" customHeight="1" spans="1:8">
       <c r="B753" s="3" t="s">
         <v>1891</v>
       </c>
@@ -25034,7 +25047,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="754" spans="1:8">
+    <row r="754" ht="30" customHeight="1" spans="1:8">
       <c r="B754" s="3" t="s">
         <v>1893</v>
       </c>
@@ -25051,7 +25064,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="755" spans="1:8">
+    <row r="755" ht="30" customHeight="1" spans="1:8">
       <c r="B755" s="3" t="s">
         <v>1895</v>
       </c>
@@ -25068,7 +25081,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="756" spans="1:8">
+    <row r="756" ht="30" customHeight="1" spans="1:8">
       <c r="B756" s="3" t="s">
         <v>1897</v>
       </c>
@@ -25085,7 +25098,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="757" spans="1:8">
+    <row r="757" ht="30" customHeight="1" spans="1:8">
       <c r="A757" s="2">
         <v>1775</v>
       </c>
@@ -25105,7 +25118,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="758" spans="1:8">
+    <row r="758" ht="30" customHeight="1" spans="1:8">
       <c r="A758" s="2">
         <v>1769</v>
       </c>
@@ -25125,7 +25138,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="759" spans="1:8">
+    <row r="759" ht="30" customHeight="1" spans="1:8">
       <c r="A759" s="2">
         <v>1769</v>
       </c>
@@ -25145,7 +25158,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="760" spans="1:8">
+    <row r="760" ht="30" customHeight="1" spans="1:8">
       <c r="A760" s="2">
         <v>1757</v>
       </c>
@@ -25165,7 +25178,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="761" spans="1:8">
+    <row r="761" ht="30" customHeight="1" spans="1:8">
       <c r="B761" s="3" t="s">
         <v>1908</v>
       </c>
@@ -25182,7 +25195,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="762" spans="1:8">
+    <row r="762" ht="30" customHeight="1" spans="1:8">
       <c r="B762" s="3" t="s">
         <v>1911</v>
       </c>
@@ -25199,7 +25212,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="763" spans="1:8">
+    <row r="763" ht="30" customHeight="1" spans="1:8">
       <c r="A763" s="2">
         <v>1769</v>
       </c>
@@ -25219,7 +25232,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="764" spans="1:8">
+    <row r="764" ht="30" customHeight="1" spans="1:8">
       <c r="A764" s="2">
         <v>1769</v>
       </c>
@@ -25239,7 +25252,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="765" spans="1:8">
+    <row r="765" ht="30" customHeight="1" spans="1:8">
       <c r="A765" s="2">
         <v>1769</v>
       </c>
@@ -25259,7 +25272,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="766" spans="1:8">
+    <row r="766" ht="30" customHeight="1" spans="1:8">
       <c r="A766" s="2">
         <v>1775</v>
       </c>
@@ -25279,7 +25292,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="767" spans="1:8">
+    <row r="767" ht="30" customHeight="1" spans="1:8">
       <c r="A767" s="2">
         <v>1738</v>
       </c>
@@ -25296,7 +25309,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="768" spans="1:8">
+    <row r="768" ht="30" customHeight="1" spans="1:8">
       <c r="A768" s="2">
         <v>1738</v>
       </c>
@@ -25310,7 +25323,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="769" spans="1:8">
+    <row r="769" ht="30" customHeight="1" spans="1:8">
       <c r="A769" s="2">
         <v>1738</v>
       </c>
@@ -25324,7 +25337,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="770" spans="1:8">
+    <row r="770" ht="30" customHeight="1" spans="1:8">
       <c r="A770" s="2">
         <v>1738</v>
       </c>
@@ -25338,7 +25351,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="771" spans="1:8">
+    <row r="771" ht="30" customHeight="1" spans="1:8">
       <c r="A771" s="2">
         <v>1743</v>
       </c>
@@ -25352,7 +25365,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="772" spans="1:8">
+    <row r="772" ht="30" customHeight="1" spans="1:8">
       <c r="A772" s="2">
         <v>1743</v>
       </c>
@@ -25366,7 +25379,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="773" spans="1:8">
+    <row r="773" ht="30" customHeight="1" spans="1:8">
       <c r="A773" s="2">
         <v>1748.9</v>
       </c>
@@ -25380,7 +25393,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="774" spans="1:8">
+    <row r="774" ht="30" customHeight="1" spans="1:8">
       <c r="A774" s="2">
         <v>1754</v>
       </c>
@@ -25394,7 +25407,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="775" spans="1:8">
+    <row r="775" ht="30" customHeight="1" spans="1:8">
       <c r="A775" s="2">
         <v>1754</v>
       </c>
@@ -25408,7 +25421,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="776" spans="1:8">
+    <row r="776" ht="30" customHeight="1" spans="1:8">
       <c r="A776" s="2">
         <v>1756</v>
       </c>
@@ -25422,7 +25435,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="777" spans="1:8">
+    <row r="777" ht="30" customHeight="1" spans="1:8">
       <c r="A777" s="2">
         <v>1756</v>
       </c>
@@ -25436,7 +25449,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="778" spans="1:8">
+    <row r="778" ht="30" customHeight="1" spans="1:8">
       <c r="A778" s="2">
         <v>1756</v>
       </c>
@@ -25450,7 +25463,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="779" spans="1:8">
+    <row r="779" ht="30" customHeight="1" spans="1:8">
       <c r="A779" s="2">
         <v>1756</v>
       </c>
@@ -25464,7 +25477,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="780" spans="1:8">
+    <row r="780" ht="30" customHeight="1" spans="1:8">
       <c r="A780" s="2">
         <v>1757</v>
       </c>
@@ -25478,7 +25491,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="781" spans="1:8">
+    <row r="781" ht="30" customHeight="1" spans="1:8">
       <c r="A781" s="2">
         <v>1757</v>
       </c>
@@ -25492,7 +25505,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="782" spans="1:8">
+    <row r="782" ht="30" customHeight="1" spans="1:8">
       <c r="A782" s="2">
         <v>1758</v>
       </c>
@@ -25506,7 +25519,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="783" spans="1:8">
+    <row r="783" ht="30" customHeight="1" spans="1:8">
       <c r="A783" s="2">
         <v>1760</v>
       </c>
@@ -25520,7 +25533,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="784" spans="1:8">
+    <row r="784" ht="30" customHeight="1" spans="1:8">
       <c r="A784" s="2">
         <v>1760</v>
       </c>
@@ -25534,7 +25547,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="785" spans="1:8">
+    <row r="785" ht="30" customHeight="1" spans="1:8">
       <c r="A785" s="2">
         <v>1762</v>
       </c>
@@ -25548,7 +25561,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="786" spans="1:8">
+    <row r="786" ht="30" customHeight="1" spans="1:8">
       <c r="A786" s="2">
         <v>1764</v>
       </c>
@@ -25562,7 +25575,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="787" spans="1:8">
+    <row r="787" ht="30" customHeight="1" spans="1:8">
       <c r="A787" s="2">
         <v>1764</v>
       </c>
@@ -25576,7 +25589,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="788" spans="1:8">
+    <row r="788" ht="30" customHeight="1" spans="1:8">
       <c r="A788" s="2">
         <v>1764</v>
       </c>
@@ -25590,7 +25603,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="789" spans="1:8">
+    <row r="789" ht="30" customHeight="1" spans="1:8">
       <c r="A789" s="2">
         <v>1764</v>
       </c>
@@ -25604,7 +25617,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="790" spans="1:8">
+    <row r="790" ht="30" customHeight="1" spans="1:8">
       <c r="A790" s="2">
         <v>1764</v>
       </c>
@@ -25618,7 +25631,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="791" spans="1:8">
+    <row r="791" ht="30" customHeight="1" spans="1:8">
       <c r="A791" s="2">
         <v>1764</v>
       </c>
@@ -25632,7 +25645,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="792" spans="1:8">
+    <row r="792" ht="30" customHeight="1" spans="1:8">
       <c r="A792" s="2">
         <v>1764</v>
       </c>
@@ -25646,7 +25659,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="793" spans="1:8">
+    <row r="793" ht="30" customHeight="1" spans="1:8">
       <c r="A793" s="2">
         <v>1764</v>
       </c>
@@ -25660,7 +25673,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="794" spans="1:8">
+    <row r="794" ht="30" customHeight="1" spans="1:8">
       <c r="A794" s="2">
         <v>1765</v>
       </c>
@@ -25674,7 +25687,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="795" spans="1:8">
+    <row r="795" ht="30" customHeight="1" spans="1:8">
       <c r="A795" s="2">
         <v>1766</v>
       </c>
@@ -25688,7 +25701,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="796" spans="1:8">
+    <row r="796" ht="30" customHeight="1" spans="1:8">
       <c r="A796" s="2">
         <v>1766</v>
       </c>
@@ -25702,7 +25715,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="797" spans="1:8">
+    <row r="797" ht="30" customHeight="1" spans="1:8">
       <c r="A797" s="2">
         <v>1767</v>
       </c>
@@ -25719,7 +25732,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="798" spans="1:8">
+    <row r="798" ht="30" customHeight="1" spans="1:8">
       <c r="A798" s="2">
         <v>1767</v>
       </c>
@@ -25733,7 +25746,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="799" spans="1:8">
+    <row r="799" ht="30" customHeight="1" spans="1:8">
       <c r="A799" s="2">
         <v>1767</v>
       </c>
@@ -25747,7 +25760,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="800" spans="1:8">
+    <row r="800" ht="30" customHeight="1" spans="1:8">
       <c r="A800" s="2">
         <v>1767</v>
       </c>
@@ -25761,7 +25774,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="801" spans="1:8">
+    <row r="801" ht="30" customHeight="1" spans="1:8">
       <c r="A801" s="2">
         <v>1767</v>
       </c>
@@ -25775,7 +25788,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="802" spans="1:8">
+    <row r="802" ht="30" customHeight="1" spans="1:8">
       <c r="A802" s="2">
         <v>1767</v>
       </c>
@@ -25789,7 +25802,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="803" spans="1:8">
+    <row r="803" ht="30" customHeight="1" spans="1:8">
       <c r="A803" s="2">
         <v>1767</v>
       </c>
@@ -25803,7 +25816,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="804" spans="1:8">
+    <row r="804" ht="30" customHeight="1" spans="1:8">
       <c r="A804" s="2">
         <v>1767</v>
       </c>
@@ -25817,7 +25830,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="805" spans="1:8">
+    <row r="805" ht="30" customHeight="1" spans="1:8">
       <c r="A805" s="2">
         <v>1767</v>
       </c>
@@ -25831,7 +25844,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="806" spans="1:8">
+    <row r="806" ht="30" customHeight="1" spans="1:8">
       <c r="A806" s="2">
         <v>1767</v>
       </c>
@@ -25845,7 +25858,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="807" spans="1:8">
+    <row r="807" ht="30" customHeight="1" spans="1:8">
       <c r="A807" s="2">
         <v>1767</v>
       </c>
@@ -25859,7 +25872,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="808" spans="1:8">
+    <row r="808" ht="30" customHeight="1" spans="1:8">
       <c r="A808" s="2">
         <v>1767</v>
       </c>
@@ -25873,7 +25886,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="809" spans="1:8">
+    <row r="809" ht="30" customHeight="1" spans="1:8">
       <c r="A809" s="2">
         <v>1767</v>
       </c>
@@ -25887,7 +25900,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="810" spans="1:8">
+    <row r="810" ht="30" customHeight="1" spans="1:8">
       <c r="A810" s="2">
         <v>1767</v>
       </c>
@@ -25901,7 +25914,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="811" spans="1:8">
+    <row r="811" ht="30" customHeight="1" spans="1:8">
       <c r="A811" s="2">
         <v>1767</v>
       </c>
@@ -25915,7 +25928,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="812" spans="1:8">
+    <row r="812" ht="30" customHeight="1" spans="1:8">
       <c r="A812" s="2">
         <v>1768</v>
       </c>
@@ -25929,7 +25942,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="813" spans="1:8">
+    <row r="813" ht="30" customHeight="1" spans="1:8">
       <c r="A813" s="2">
         <v>1768</v>
       </c>
@@ -25943,7 +25956,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="814" spans="1:8">
+    <row r="814" ht="30" customHeight="1" spans="1:8">
       <c r="A814" s="2">
         <v>1768</v>
       </c>
@@ -25957,7 +25970,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="815" spans="1:8">
+    <row r="815" ht="30" customHeight="1" spans="1:8">
       <c r="A815" s="2">
         <v>1769</v>
       </c>
@@ -25974,7 +25987,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="816" spans="1:8">
+    <row r="816" ht="30" customHeight="1" spans="1:8">
       <c r="A816" s="2">
         <v>1769</v>
       </c>
@@ -25988,7 +26001,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="817" spans="1:9">
+    <row r="817" ht="30" customHeight="1" spans="1:9">
       <c r="A817" s="2">
         <v>1769</v>
       </c>
@@ -26002,7 +26015,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="818" spans="1:9">
+    <row r="818" ht="30" customHeight="1" spans="1:9">
       <c r="A818" s="2">
         <v>1769</v>
       </c>
@@ -26016,7 +26029,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="819" spans="1:9">
+    <row r="819" ht="30" customHeight="1" spans="1:9">
       <c r="A819" s="2">
         <v>1769</v>
       </c>
@@ -26030,7 +26043,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="820" spans="1:9">
+    <row r="820" ht="30" customHeight="1" spans="1:9">
       <c r="A820" s="2">
         <v>1769</v>
       </c>
@@ -26044,7 +26057,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="821" spans="1:9">
+    <row r="821" ht="30" customHeight="1" spans="1:9">
       <c r="A821" s="2">
         <v>1769</v>
       </c>
@@ -26058,7 +26071,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="822" spans="1:9">
+    <row r="822" ht="30" customHeight="1" spans="1:9">
       <c r="A822" s="2">
         <v>1769</v>
       </c>
@@ -26072,7 +26085,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="823" spans="1:9">
+    <row r="823" ht="30" customHeight="1" spans="1:9">
       <c r="A823" s="2">
         <v>1769</v>
       </c>
@@ -26095,7 +26108,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="824" spans="1:9">
+    <row r="824" ht="30" customHeight="1" spans="1:9">
       <c r="A824" s="2">
         <v>1769</v>
       </c>
@@ -26109,7 +26122,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="825" spans="1:9">
+    <row r="825" ht="30" customHeight="1" spans="1:9">
       <c r="A825" s="2">
         <v>1770</v>
       </c>
@@ -26123,7 +26136,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="826" spans="1:9">
+    <row r="826" ht="30" customHeight="1" spans="1:9">
       <c r="A826" s="2">
         <v>1770</v>
       </c>
@@ -26137,7 +26150,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="827" spans="1:9">
+    <row r="827" ht="30" customHeight="1" spans="1:9">
       <c r="A827" s="2">
         <v>1771</v>
       </c>
@@ -26151,7 +26164,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="828" spans="1:9">
+    <row r="828" ht="30" customHeight="1" spans="1:9">
       <c r="A828" s="2">
         <v>1772</v>
       </c>
@@ -26165,7 +26178,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="829" spans="1:9">
+    <row r="829" ht="30" customHeight="1" spans="1:9">
       <c r="A829" s="2">
         <v>1772</v>
       </c>
@@ -26179,7 +26192,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="830" spans="1:9">
+    <row r="830" ht="30" customHeight="1" spans="1:9">
       <c r="A830" s="2">
         <v>1773</v>
       </c>
@@ -26193,7 +26206,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="831" spans="1:9">
+    <row r="831" ht="30" customHeight="1" spans="1:9">
       <c r="A831" s="2">
         <v>1773</v>
       </c>
@@ -26207,7 +26220,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="832" spans="1:9">
+    <row r="832" ht="30" customHeight="1" spans="1:9">
       <c r="A832" s="2">
         <v>1774</v>
       </c>
@@ -26221,7 +26234,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="833" spans="1:8">
+    <row r="833" ht="30" customHeight="1" spans="1:8">
       <c r="A833" s="2">
         <v>1774</v>
       </c>
@@ -26235,7 +26248,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="834" spans="1:8">
+    <row r="834" ht="30" customHeight="1" spans="1:8">
       <c r="A834" s="2">
         <v>1774</v>
       </c>
@@ -26249,7 +26262,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="835" spans="1:8">
+    <row r="835" ht="30" customHeight="1" spans="1:8">
       <c r="A835" s="2">
         <v>1774</v>
       </c>
@@ -26263,7 +26276,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="836" spans="1:8">
+    <row r="836" ht="30" customHeight="1" spans="1:8">
       <c r="A836" s="2">
         <v>1775</v>
       </c>
@@ -26283,7 +26296,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="837" spans="1:8">
+    <row r="837" ht="30" customHeight="1" spans="1:8">
       <c r="A837" s="2">
         <v>1775</v>
       </c>
@@ -26297,7 +26310,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="838" spans="1:8">
+    <row r="838" ht="30" customHeight="1" spans="1:8">
       <c r="A838" s="2">
         <v>1775</v>
       </c>
@@ -26311,7 +26324,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="839" spans="1:8">
+    <row r="839" ht="30" customHeight="1" spans="1:8">
       <c r="A839" s="2">
         <v>1775</v>
       </c>
@@ -26325,7 +26338,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="840" spans="1:8">
+    <row r="840" ht="30" customHeight="1" spans="1:8">
       <c r="A840" s="2">
         <v>1775</v>
       </c>
@@ -26339,7 +26352,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="841" spans="1:8">
+    <row r="841" ht="30" customHeight="1" spans="1:8">
       <c r="A841" s="2">
         <v>1775</v>
       </c>
@@ -26353,7 +26366,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="842" spans="1:8">
+    <row r="842" ht="30" customHeight="1" spans="1:8">
       <c r="A842" s="2">
         <v>1775</v>
       </c>
@@ -26367,7 +26380,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="843" spans="1:8">
+    <row r="843" ht="30" customHeight="1" spans="1:8">
       <c r="A843" s="2">
         <v>1776</v>
       </c>
@@ -26381,7 +26394,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="844" spans="1:8">
+    <row r="844" ht="30" customHeight="1" spans="1:8">
       <c r="A844" s="2">
         <v>1776</v>
       </c>
@@ -26395,7 +26408,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="845" spans="1:8">
+    <row r="845" ht="30" customHeight="1" spans="1:8">
       <c r="A845" s="2">
         <v>1777</v>
       </c>
@@ -26409,7 +26422,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="846" spans="1:8">
+    <row r="846" ht="30" customHeight="1" spans="1:8">
       <c r="A846" s="2">
         <v>1777</v>
       </c>
@@ -26423,7 +26436,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="847" spans="1:8">
+    <row r="847" ht="30" customHeight="1" spans="1:8">
       <c r="A847" s="2">
         <v>1778</v>
       </c>
@@ -26437,7 +26450,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="848" spans="1:8">
+    <row r="848" ht="30" customHeight="1" spans="1:8">
       <c r="A848" s="2">
         <v>1780</v>
       </c>
@@ -26451,7 +26464,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="849" spans="1:4">
+    <row r="849" ht="30" customHeight="1" spans="1:4">
       <c r="A849" s="2">
         <v>1780</v>
       </c>
@@ -26465,7 +26478,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="850" spans="1:4">
+    <row r="850" ht="30" customHeight="1" spans="1:4">
       <c r="A850" s="2">
         <v>1780</v>
       </c>
@@ -26479,7 +26492,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="851" spans="1:4">
+    <row r="851" ht="30" customHeight="1" spans="1:4">
       <c r="A851" s="2">
         <v>1780</v>
       </c>
@@ -26493,7 +26506,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="852" spans="1:4">
+    <row r="852" ht="30" customHeight="1" spans="1:4">
       <c r="A852" s="2">
         <v>1780</v>
       </c>
@@ -26507,7 +26520,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="853" spans="1:4">
+    <row r="853" ht="30" customHeight="1" spans="1:4">
       <c r="A853" s="2">
         <v>1780</v>
       </c>
@@ -26521,7 +26534,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="854" spans="1:4">
+    <row r="854" ht="30" customHeight="1" spans="1:4">
       <c r="A854" s="2">
         <v>1780</v>
       </c>
@@ -26535,7 +26548,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="855" spans="1:4">
+    <row r="855" ht="30" customHeight="1" spans="1:4">
       <c r="A855" s="2">
         <v>1780</v>
       </c>
@@ -26549,7 +26562,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="856" spans="1:4">
+    <row r="856" ht="30" customHeight="1" spans="1:4">
       <c r="A856" s="2">
         <v>1780</v>
       </c>
@@ -26563,7 +26576,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="857" spans="1:4">
+    <row r="857" ht="30" customHeight="1" spans="1:4">
       <c r="A857" s="2">
         <v>1780</v>
       </c>
@@ -26577,7 +26590,7 @@
         <v>2198</v>
       </c>
     </row>
-    <row r="858" spans="1:4">
+    <row r="858" ht="30" customHeight="1" spans="1:4">
       <c r="A858" s="2">
         <v>1780</v>
       </c>
@@ -26591,7 +26604,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="859" spans="1:4">
+    <row r="859" ht="30" customHeight="1" spans="1:4">
       <c r="A859" s="2">
         <v>1780</v>
       </c>
@@ -26605,7 +26618,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="860" spans="1:4">
+    <row r="860" ht="30" customHeight="1" spans="1:4">
       <c r="A860" s="2">
         <v>1780</v>
       </c>
@@ -26619,7 +26632,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="861" spans="1:4">
+    <row r="861" ht="30" customHeight="1" spans="1:4">
       <c r="A861" s="2">
         <v>1780</v>
       </c>
@@ -26633,7 +26646,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="862" spans="1:4">
+    <row r="862" ht="30" customHeight="1" spans="1:4">
       <c r="A862" s="2">
         <v>1780</v>
       </c>
@@ -26647,7 +26660,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="863" spans="1:4">
+    <row r="863" ht="30" customHeight="1" spans="1:4">
       <c r="A863" s="2">
         <v>1780</v>
       </c>
@@ -26661,7 +26674,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="864" spans="1:4">
+    <row r="864" ht="30" customHeight="1" spans="1:4">
       <c r="A864" s="2">
         <v>1780</v>
       </c>
@@ -26675,7 +26688,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="865" spans="1:4">
+    <row r="865" ht="30" customHeight="1" spans="1:4">
       <c r="A865" s="2">
         <v>1780</v>
       </c>
@@ -26689,7 +26702,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="866" spans="1:4">
+    <row r="866" ht="30" customHeight="1" spans="1:4">
       <c r="A866" s="2">
         <v>1780</v>
       </c>
@@ -26703,7 +26716,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="867" spans="1:4">
+    <row r="867" ht="30" customHeight="1" spans="1:4">
       <c r="A867" s="2">
         <v>1780</v>
       </c>
@@ -26717,7 +26730,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="868" spans="1:4">
+    <row r="868" ht="30" customHeight="1" spans="1:4">
       <c r="A868" s="2">
         <v>1780</v>
       </c>
@@ -26731,7 +26744,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="869" spans="1:4">
+    <row r="869" ht="30" customHeight="1" spans="1:4">
       <c r="A869" s="2">
         <v>1780</v>
       </c>
@@ -26745,7 +26758,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="870" spans="1:4">
+    <row r="870" ht="30" customHeight="1" spans="1:4">
       <c r="A870" s="2">
         <v>1781</v>
       </c>
@@ -26759,7 +26772,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="871" spans="1:4">
+    <row r="871" ht="30" customHeight="1" spans="1:4">
       <c r="A871" s="2">
         <v>1781</v>
       </c>
@@ -26773,7 +26786,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="872" spans="1:4">
+    <row r="872" ht="30" customHeight="1" spans="1:4">
       <c r="A872" s="2">
         <v>1781</v>
       </c>
@@ -26787,7 +26800,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="873" spans="1:4">
+    <row r="873" ht="30" customHeight="1" spans="1:4">
       <c r="A873" s="2">
         <v>1781</v>
       </c>
@@ -26801,7 +26814,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="874" spans="1:4">
+    <row r="874" ht="30" customHeight="1" spans="1:4">
       <c r="A874" s="2">
         <v>1781</v>
       </c>
@@ -26815,7 +26828,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="875" spans="1:4">
+    <row r="875" ht="30" customHeight="1" spans="1:4">
       <c r="A875" s="2">
         <v>1781</v>
       </c>
@@ -26829,7 +26842,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="876" spans="1:4">
+    <row r="876" ht="30" customHeight="1" spans="1:4">
       <c r="A876" s="2">
         <v>1781</v>
       </c>
@@ -26843,7 +26856,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="877" spans="1:4">
+    <row r="877" ht="30" customHeight="1" spans="1:4">
       <c r="A877" s="2">
         <v>1781</v>
       </c>
@@ -26857,7 +26870,7 @@
         <v>2257</v>
       </c>
     </row>
-    <row r="878" spans="1:4">
+    <row r="878" ht="30" customHeight="1" spans="1:4">
       <c r="A878" s="2">
         <v>1781</v>
       </c>
@@ -26871,7 +26884,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="879" spans="1:4">
+    <row r="879" ht="30" customHeight="1" spans="1:4">
       <c r="A879" s="2">
         <v>1781</v>
       </c>
@@ -26885,7 +26898,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="880" spans="1:4">
+    <row r="880" ht="30" customHeight="1" spans="1:4">
       <c r="A880" s="2">
         <v>1781</v>
       </c>
@@ -26899,7 +26912,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="881" spans="1:4">
+    <row r="881" ht="30" customHeight="1" spans="1:4">
       <c r="A881" s="2">
         <v>1781</v>
       </c>
@@ -26913,7 +26926,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="882" spans="1:4">
+    <row r="882" ht="30" customHeight="1" spans="1:4">
       <c r="A882" s="2">
         <v>1781</v>
       </c>
@@ -26927,7 +26940,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="883" spans="1:4">
+    <row r="883" ht="30" customHeight="1" spans="1:4">
       <c r="A883" s="2">
         <v>1781</v>
       </c>
@@ -26941,7 +26954,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="884" spans="1:4">
+    <row r="884" ht="30" customHeight="1" spans="1:4">
       <c r="A884" s="2">
         <v>1781</v>
       </c>
@@ -26955,7 +26968,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="885" spans="1:4">
+    <row r="885" ht="30" customHeight="1" spans="1:4">
       <c r="A885" s="2">
         <v>1781</v>
       </c>
@@ -26969,7 +26982,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="886" spans="1:4">
+    <row r="886" ht="30" customHeight="1" spans="1:4">
       <c r="A886" s="2">
         <v>1781</v>
       </c>
@@ -26983,7 +26996,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="887" spans="1:4">
+    <row r="887" ht="30" customHeight="1" spans="1:4">
       <c r="A887" s="2">
         <v>1781</v>
       </c>
@@ -26997,7 +27010,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="888" spans="1:4">
+    <row r="888" ht="30" customHeight="1" spans="1:4">
       <c r="A888" s="2">
         <v>1781</v>
       </c>
@@ -27011,7 +27024,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="889" spans="1:4">
+    <row r="889" ht="30" customHeight="1" spans="1:4">
       <c r="A889" s="2">
         <v>1781</v>
       </c>
@@ -27025,7 +27038,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="890" spans="1:4">
+    <row r="890" ht="30" customHeight="1" spans="1:4">
       <c r="A890" s="2">
         <v>1781</v>
       </c>
@@ -27039,7 +27052,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="891" spans="1:4">
+    <row r="891" ht="30" customHeight="1" spans="1:4">
       <c r="A891" s="2">
         <v>1781</v>
       </c>
@@ -27053,7 +27066,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="892" spans="1:4">
+    <row r="892" ht="30" customHeight="1" spans="1:4">
       <c r="A892" s="2">
         <v>1781</v>
       </c>
@@ -27067,7 +27080,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="893" spans="1:4">
+    <row r="893" ht="30" customHeight="1" spans="1:4">
       <c r="A893" s="2">
         <v>1781</v>
       </c>
@@ -27081,7 +27094,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="894" spans="1:4">
+    <row r="894" ht="30" customHeight="1" spans="1:4">
       <c r="A894" s="2">
         <v>1781</v>
       </c>
@@ -27095,7 +27108,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="895" spans="1:4">
+    <row r="895" ht="30" customHeight="1" spans="1:4">
       <c r="A895" s="2">
         <v>1781</v>
       </c>
@@ -27109,7 +27122,7 @@
         <v>2311</v>
       </c>
     </row>
-    <row r="896" spans="1:4">
+    <row r="896" ht="30" customHeight="1" spans="1:4">
       <c r="A896" s="2">
         <v>1781</v>
       </c>
@@ -27123,7 +27136,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="897" spans="1:4">
+    <row r="897" ht="30" customHeight="1" spans="1:4">
       <c r="A897" s="2">
         <v>1781</v>
       </c>
@@ -27137,7 +27150,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="898" spans="1:4">
+    <row r="898" ht="30" customHeight="1" spans="1:4">
       <c r="A898" s="2">
         <v>1781.2</v>
       </c>
@@ -27151,7 +27164,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="899" spans="1:4">
+    <row r="899" ht="30" customHeight="1" spans="1:4">
       <c r="A899" s="2">
         <v>1782</v>
       </c>
@@ -27165,7 +27178,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="900" spans="1:4">
+    <row r="900" ht="30" customHeight="1" spans="1:4">
       <c r="A900" s="2">
         <v>1782</v>
       </c>
@@ -27179,7 +27192,7 @@
         <v>2325</v>
       </c>
     </row>
-    <row r="901" spans="1:4">
+    <row r="901" ht="30" customHeight="1" spans="1:4">
       <c r="A901" s="2">
         <v>1782</v>
       </c>
@@ -27193,7 +27206,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="902" spans="1:4">
+    <row r="902" ht="30" customHeight="1" spans="1:4">
       <c r="A902" s="2">
         <v>1783</v>
       </c>
@@ -27207,7 +27220,7 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="903" spans="1:4">
+    <row r="903" ht="30" customHeight="1" spans="1:4">
       <c r="A903" s="2">
         <v>1783</v>
       </c>
@@ -27221,7 +27234,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="904" spans="1:4">
+    <row r="904" ht="30" customHeight="1" spans="1:4">
       <c r="A904" s="2">
         <v>1783</v>
       </c>
@@ -27235,7 +27248,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="905" spans="1:4">
+    <row r="905" ht="30" customHeight="1" spans="1:4">
       <c r="A905" s="2">
         <v>1784</v>
       </c>
@@ -27249,7 +27262,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="906" spans="1:4">
+    <row r="906" ht="30" customHeight="1" spans="1:4">
       <c r="A906" s="2">
         <v>1785</v>
       </c>
@@ -27263,7 +27276,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="907" spans="1:4">
+    <row r="907" ht="30" customHeight="1" spans="1:4">
       <c r="A907" s="2">
         <v>1785</v>
       </c>
@@ -27277,7 +27290,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="908" spans="1:4">
+    <row r="908" ht="30" customHeight="1" spans="1:4">
       <c r="A908" s="2">
         <v>1785</v>
       </c>
@@ -27291,7 +27304,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="909" spans="1:4">
+    <row r="909" ht="30" customHeight="1" spans="1:4">
       <c r="A909" s="2">
         <v>1785</v>
       </c>
@@ -27305,7 +27318,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="910" spans="1:4">
+    <row r="910" ht="30" customHeight="1" spans="1:4">
       <c r="A910" s="2">
         <v>1785</v>
       </c>
@@ -27319,7 +27332,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="911" spans="1:4">
+    <row r="911" ht="30" customHeight="1" spans="1:4">
       <c r="A911" s="2">
         <v>1785</v>
       </c>
@@ -27333,7 +27346,7 @@
         <v>2357</v>
       </c>
     </row>
-    <row r="912" spans="1:4">
+    <row r="912" ht="30" customHeight="1" spans="1:4">
       <c r="A912" s="2">
         <v>1785</v>
       </c>
@@ -27347,7 +27360,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="913" spans="1:4">
+    <row r="913" ht="30" customHeight="1" spans="1:4">
       <c r="A913" s="2">
         <v>1787</v>
       </c>
@@ -27361,7 +27374,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="914" spans="1:4">
+    <row r="914" ht="30" customHeight="1" spans="1:4">
       <c r="A914" s="2">
         <v>1787</v>
       </c>
@@ -27375,7 +27388,7 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="915" spans="1:4">
+    <row r="915" ht="30" customHeight="1" spans="1:4">
       <c r="A915" s="2">
         <v>1787</v>
       </c>
@@ -27389,7 +27402,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="916" spans="1:4">
+    <row r="916" ht="30" customHeight="1" spans="1:4">
       <c r="A916" s="2">
         <v>1787</v>
       </c>
@@ -27403,7 +27416,7 @@
         <v>2372</v>
       </c>
     </row>
-    <row r="917" spans="1:4">
+    <row r="917" ht="30" customHeight="1" spans="1:4">
       <c r="A917" s="2">
         <v>1787</v>
       </c>
@@ -27417,7 +27430,7 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="918" spans="1:4">
+    <row r="918" ht="30" customHeight="1" spans="1:4">
       <c r="A918" s="2">
         <v>1787</v>
       </c>
@@ -27431,7 +27444,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="919" spans="1:4">
+    <row r="919" ht="30" customHeight="1" spans="1:4">
       <c r="A919" s="2">
         <v>1787</v>
       </c>
@@ -27445,7 +27458,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="920" spans="1:4">
+    <row r="920" ht="30" customHeight="1" spans="1:4">
       <c r="A920" s="2">
         <v>1787</v>
       </c>
@@ -27459,7 +27472,7 @@
         <v>2384</v>
       </c>
     </row>
-    <row r="921" spans="1:4">
+    <row r="921" ht="30" customHeight="1" spans="1:4">
       <c r="A921" s="2">
         <v>1787</v>
       </c>
@@ -27473,7 +27486,7 @@
         <v>2387</v>
       </c>
     </row>
-    <row r="922" spans="1:4">
+    <row r="922" ht="30" customHeight="1" spans="1:4">
       <c r="A922" s="2">
         <v>1787</v>
       </c>
@@ -27487,7 +27500,7 @@
         <v>2390</v>
       </c>
     </row>
-    <row r="923" spans="1:4">
+    <row r="923" ht="30" customHeight="1" spans="1:4">
       <c r="A923" s="2">
         <v>1787</v>
       </c>
@@ -27501,7 +27514,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="924" spans="1:4">
+    <row r="924" ht="30" customHeight="1" spans="1:4">
       <c r="A924" s="2">
         <v>1787</v>
       </c>
@@ -27515,7 +27528,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="925" spans="1:4">
+    <row r="925" ht="30" customHeight="1" spans="1:4">
       <c r="A925" s="2">
         <v>1787</v>
       </c>
@@ -27529,7 +27542,7 @@
         <v>2399</v>
       </c>
     </row>
-    <row r="926" spans="1:4">
+    <row r="926" ht="30" customHeight="1" spans="1:4">
       <c r="A926" s="2">
         <v>1787</v>
       </c>
@@ -27543,7 +27556,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="927" spans="1:4">
+    <row r="927" ht="30" customHeight="1" spans="1:4">
       <c r="A927" s="2">
         <v>1787</v>
       </c>
@@ -27557,7 +27570,7 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="928" spans="1:4">
+    <row r="928" ht="30" customHeight="1" spans="1:4">
       <c r="A928" s="2">
         <v>1788</v>
       </c>
@@ -27571,7 +27584,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="929" spans="1:4">
+    <row r="929" ht="30" customHeight="1" spans="1:4">
       <c r="A929" s="2">
         <v>1788</v>
       </c>
@@ -27585,7 +27598,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="930" spans="1:4">
+    <row r="930" ht="30" customHeight="1" spans="1:4">
       <c r="A930" s="2">
         <v>1788</v>
       </c>
@@ -27599,7 +27612,7 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="931" spans="1:4">
+    <row r="931" ht="30" customHeight="1" spans="1:4">
       <c r="A931" s="2">
         <v>1788</v>
       </c>
@@ -27613,7 +27626,7 @@
         <v>2417</v>
       </c>
     </row>
-    <row r="932" spans="1:4">
+    <row r="932" ht="30" customHeight="1" spans="1:4">
       <c r="A932" s="2">
         <v>1788</v>
       </c>
@@ -27627,7 +27640,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="933" spans="1:4">
+    <row r="933" ht="30" customHeight="1" spans="1:4">
       <c r="A933" s="2">
         <v>1788</v>
       </c>
@@ -27641,7 +27654,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="934" spans="1:4">
+    <row r="934" ht="30" customHeight="1" spans="1:4">
       <c r="A934" s="2">
         <v>1788</v>
       </c>
@@ -27655,7 +27668,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="935" spans="1:4">
+    <row r="935" ht="30" customHeight="1" spans="1:4">
       <c r="A935" s="2">
         <v>1788</v>
       </c>
@@ -27669,7 +27682,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="936" spans="1:4">
+    <row r="936" ht="30" customHeight="1" spans="1:4">
       <c r="A936" s="2">
         <v>1788</v>
       </c>
@@ -27683,7 +27696,7 @@
         <v>2432</v>
       </c>
     </row>
-    <row r="937" spans="1:4">
+    <row r="937" ht="30" customHeight="1" spans="1:4">
       <c r="A937" s="2" t="s">
         <v>784</v>
       </c>
@@ -27697,7 +27710,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="938" spans="1:4">
+    <row r="938" ht="30" customHeight="1" spans="1:4">
       <c r="A938" s="2" t="s">
         <v>784</v>
       </c>
@@ -27711,7 +27724,7 @@
         <v>2438</v>
       </c>
     </row>
-    <row r="939" spans="1:4">
+    <row r="939" ht="30" customHeight="1" spans="1:4">
       <c r="A939" s="2" t="s">
         <v>2439</v>
       </c>
@@ -27725,7 +27738,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="940" spans="1:4">
+    <row r="940" ht="30" customHeight="1" spans="1:4">
       <c r="A940" s="2" t="s">
         <v>788</v>
       </c>
@@ -27739,7 +27752,7 @@
         <v>2445</v>
       </c>
     </row>
-    <row r="941" spans="1:4">
+    <row r="941" ht="30" customHeight="1" spans="1:4">
       <c r="A941" s="2" t="s">
         <v>788</v>
       </c>
@@ -27753,7 +27766,7 @@
         <v>2448</v>
       </c>
     </row>
-    <row r="942" spans="1:4">
+    <row r="942" ht="30" customHeight="1" spans="1:4">
       <c r="A942" s="2" t="s">
         <v>788</v>
       </c>
@@ -27767,7 +27780,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="943" spans="1:4">
+    <row r="943" ht="30" customHeight="1" spans="1:4">
       <c r="A943" s="2" t="s">
         <v>788</v>
       </c>
@@ -27781,7 +27794,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="944" spans="1:4">
+    <row r="944" ht="30" customHeight="1" spans="1:4">
       <c r="A944" s="2" t="s">
         <v>788</v>
       </c>
@@ -27795,7 +27808,7 @@
         <v>2457</v>
       </c>
     </row>
-    <row r="945" spans="1:4">
+    <row r="945" ht="30" customHeight="1" spans="1:4">
       <c r="A945" s="2" t="s">
         <v>788</v>
       </c>
@@ -27809,7 +27822,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="946" spans="1:4">
+    <row r="946" ht="30" customHeight="1" spans="1:4">
       <c r="A946" s="2" t="s">
         <v>788</v>
       </c>
@@ -27823,7 +27836,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="947" spans="1:4">
+    <row r="947" ht="30" customHeight="1" spans="1:4">
       <c r="A947" s="2" t="s">
         <v>788</v>
       </c>
@@ -27837,7 +27850,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="948" spans="1:4">
+    <row r="948" ht="30" customHeight="1" spans="1:4">
       <c r="A948" s="2" t="s">
         <v>788</v>
       </c>
@@ -27851,7 +27864,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="949" spans="1:4">
+    <row r="949" ht="30" customHeight="1" spans="1:4">
       <c r="A949" s="2" t="s">
         <v>788</v>
       </c>
@@ -27865,7 +27878,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="950" spans="1:4">
+    <row r="950" ht="30" customHeight="1" spans="1:4">
       <c r="A950" s="2" t="s">
         <v>788</v>
       </c>
@@ -27879,7 +27892,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="951" spans="1:4">
+    <row r="951" ht="30" customHeight="1" spans="1:4">
       <c r="A951" s="2" t="s">
         <v>788</v>
       </c>
@@ -27893,7 +27906,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="952" spans="1:4">
+    <row r="952" ht="30" customHeight="1" spans="1:4">
       <c r="A952" s="2" t="s">
         <v>788</v>
       </c>
@@ -27907,7 +27920,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="953" spans="1:4">
+    <row r="953" ht="30" customHeight="1" spans="1:4">
       <c r="A953" s="2" t="s">
         <v>788</v>
       </c>
@@ -27921,7 +27934,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="954" spans="1:4">
+    <row r="954" ht="30" customHeight="1" spans="1:4">
       <c r="A954" s="2" t="s">
         <v>788</v>
       </c>
@@ -27935,7 +27948,7 @@
         <v>2487</v>
       </c>
     </row>
-    <row r="955" spans="1:4">
+    <row r="955" ht="30" customHeight="1" spans="1:4">
       <c r="A955" s="2" t="s">
         <v>788</v>
       </c>
@@ -27949,7 +27962,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="956" spans="1:4">
+    <row r="956" ht="30" customHeight="1" spans="1:4">
       <c r="A956" s="2" t="s">
         <v>788</v>
       </c>
@@ -27963,7 +27976,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="957" spans="1:4">
+    <row r="957" ht="30" customHeight="1" spans="1:4">
       <c r="A957" s="2" t="s">
         <v>788</v>
       </c>
@@ -27977,7 +27990,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="958" spans="1:4">
+    <row r="958" ht="30" customHeight="1" spans="1:4">
       <c r="A958" s="2" t="s">
         <v>788</v>
       </c>
@@ -27991,7 +28004,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="959" spans="1:4">
+    <row r="959" ht="30" customHeight="1" spans="1:4">
       <c r="A959" s="2" t="s">
         <v>788</v>
       </c>
@@ -28005,7 +28018,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="960" spans="1:4">
+    <row r="960" ht="30" customHeight="1" spans="1:4">
       <c r="A960" s="2" t="s">
         <v>788</v>
       </c>
@@ -28019,7 +28032,7 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="961" spans="1:9">
+    <row r="961" ht="30" customHeight="1" spans="1:9">
       <c r="A961" s="2" t="s">
         <v>788</v>
       </c>
@@ -28033,7 +28046,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="962" spans="1:9">
+    <row r="962" ht="30" customHeight="1" spans="1:9">
       <c r="A962" s="2" t="s">
         <v>788</v>
       </c>
@@ -28047,7 +28060,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="963" spans="1:9">
+    <row r="963" ht="30" customHeight="1" spans="1:9">
       <c r="A963" s="2" t="s">
         <v>788</v>
       </c>
@@ -28061,7 +28074,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="964" spans="1:9">
+    <row r="964" ht="30" customHeight="1" spans="1:9">
       <c r="A964" s="2" t="s">
         <v>788</v>
       </c>
@@ -28075,7 +28088,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="965" spans="1:9">
+    <row r="965" ht="30" customHeight="1" spans="1:9">
       <c r="A965" s="2" t="s">
         <v>788</v>
       </c>
@@ -28089,7 +28102,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="966" spans="1:9">
+    <row r="966" ht="30" customHeight="1" spans="1:9">
       <c r="A966" s="2" t="s">
         <v>788</v>
       </c>
@@ -28103,7 +28116,7 @@
         <v>2523</v>
       </c>
     </row>
-    <row r="967" spans="1:9">
+    <row r="967" ht="30" customHeight="1" spans="1:9">
       <c r="A967" s="2" t="s">
         <v>788</v>
       </c>
@@ -28117,7 +28130,7 @@
         <v>2526</v>
       </c>
     </row>
-    <row r="968" spans="1:9">
+    <row r="968" ht="30" customHeight="1" spans="1:9">
       <c r="A968" s="2" t="s">
         <v>788</v>
       </c>
@@ -28131,7 +28144,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="969" spans="1:9">
+    <row r="969" ht="30" customHeight="1" spans="1:9">
       <c r="A969" s="2" t="s">
         <v>788</v>
       </c>
@@ -28145,7 +28158,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="970" spans="1:9">
+    <row r="970" ht="30" customHeight="1" spans="1:9">
       <c r="A970" s="2" t="s">
         <v>788</v>
       </c>
@@ -28159,7 +28172,7 @@
         <v>2535</v>
       </c>
     </row>
-    <row r="971" s="1" customFormat="1" spans="1:9">
+    <row r="971" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A971" s="2" t="s">
         <v>788</v>
       </c>
@@ -28178,7 +28191,7 @@
       <c r="H971" s="5"/>
       <c r="I971" s="5"/>
     </row>
-    <row r="972" s="1" customFormat="1" spans="1:9">
+    <row r="972" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A972" s="2" t="s">
         <v>788</v>
       </c>
@@ -28197,7 +28210,7 @@
       <c r="H972" s="5"/>
       <c r="I972" s="5"/>
     </row>
-    <row r="973" s="1" customFormat="1" spans="1:9">
+    <row r="973" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A973" s="2" t="s">
         <v>788</v>
       </c>
@@ -28216,7 +28229,7 @@
       <c r="H973" s="5"/>
       <c r="I973" s="5"/>
     </row>
-    <row r="974" s="1" customFormat="1" spans="1:9">
+    <row r="974" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A974" s="2" t="s">
         <v>788</v>
       </c>
@@ -28235,7 +28248,7 @@
       <c r="H974" s="5"/>
       <c r="I974" s="5"/>
     </row>
-    <row r="975" s="1" customFormat="1" spans="1:9">
+    <row r="975" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A975" s="2" t="s">
         <v>788</v>
       </c>
@@ -28254,7 +28267,7 @@
       <c r="H975" s="5"/>
       <c r="I975" s="5"/>
     </row>
-    <row r="976" s="1" customFormat="1" spans="1:9">
+    <row r="976" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A976" s="2" t="s">
         <v>788</v>
       </c>
@@ -28273,7 +28286,7 @@
       <c r="H976" s="5"/>
       <c r="I976" s="5"/>
     </row>
-    <row r="977" s="1" customFormat="1" spans="1:9">
+    <row r="977" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A977" s="2" t="s">
         <v>788</v>
       </c>
@@ -28292,7 +28305,7 @@
       <c r="H977" s="5"/>
       <c r="I977" s="5"/>
     </row>
-    <row r="978" s="1" customFormat="1" spans="1:9">
+    <row r="978" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A978" s="2" t="s">
         <v>788</v>
       </c>
@@ -28311,7 +28324,7 @@
       <c r="H978" s="5"/>
       <c r="I978" s="5"/>
     </row>
-    <row r="979" s="1" customFormat="1" spans="1:9">
+    <row r="979" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A979" s="2" t="s">
         <v>788</v>
       </c>
@@ -28330,7 +28343,7 @@
       <c r="H979" s="5"/>
       <c r="I979" s="5"/>
     </row>
-    <row r="980" s="1" customFormat="1" spans="1:9">
+    <row r="980" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A980" s="2" t="s">
         <v>788</v>
       </c>
@@ -28349,7 +28362,7 @@
       <c r="H980" s="5"/>
       <c r="I980" s="5"/>
     </row>
-    <row r="981" s="1" customFormat="1" spans="1:9">
+    <row r="981" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A981" s="2" t="s">
         <v>788</v>
       </c>
@@ -28368,7 +28381,7 @@
       <c r="H981" s="5"/>
       <c r="I981" s="5"/>
     </row>
-    <row r="982" s="1" customFormat="1" spans="1:9">
+    <row r="982" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A982" s="2" t="s">
         <v>788</v>
       </c>
@@ -28387,7 +28400,7 @@
       <c r="H982" s="5"/>
       <c r="I982" s="5"/>
     </row>
-    <row r="983" s="1" customFormat="1" spans="1:9">
+    <row r="983" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A983" s="2" t="s">
         <v>788</v>
       </c>
@@ -28406,7 +28419,7 @@
       <c r="H983" s="5"/>
       <c r="I983" s="5"/>
     </row>
-    <row r="984" s="1" customFormat="1" spans="1:9">
+    <row r="984" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A984" s="2" t="s">
         <v>788</v>
       </c>
@@ -28425,7 +28438,7 @@
       <c r="H984" s="5"/>
       <c r="I984" s="5"/>
     </row>
-    <row r="985" s="1" customFormat="1" spans="1:9">
+    <row r="985" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A985" s="2" t="s">
         <v>788</v>
       </c>
@@ -28444,7 +28457,7 @@
       <c r="H985" s="5"/>
       <c r="I985" s="5"/>
     </row>
-    <row r="986" s="1" customFormat="1" spans="1:9">
+    <row r="986" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A986" s="2" t="s">
         <v>788</v>
       </c>
@@ -28463,7 +28476,7 @@
       <c r="H986" s="5"/>
       <c r="I986" s="5"/>
     </row>
-    <row r="987" s="1" customFormat="1" spans="1:9">
+    <row r="987" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A987" s="2" t="s">
         <v>2583</v>
       </c>
@@ -28482,7 +28495,7 @@
       <c r="H987" s="5"/>
       <c r="I987" s="5"/>
     </row>
-    <row r="988" s="1" customFormat="1" spans="1:9">
+    <row r="988" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A988" s="2" t="s">
         <v>2583</v>
       </c>
@@ -28501,7 +28514,7 @@
       <c r="H988" s="5"/>
       <c r="I988" s="5"/>
     </row>
-    <row r="989" s="1" customFormat="1" spans="1:9">
+    <row r="989" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A989" s="2" t="s">
         <v>2590</v>
       </c>
@@ -28520,7 +28533,7 @@
       <c r="H989" s="5"/>
       <c r="I989" s="5"/>
     </row>
-    <row r="990" s="1" customFormat="1" spans="1:9">
+    <row r="990" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A990" s="2" t="s">
         <v>2590</v>
       </c>
@@ -28539,7 +28552,7 @@
       <c r="H990" s="5"/>
       <c r="I990" s="5"/>
     </row>
-    <row r="991" s="1" customFormat="1" spans="1:9">
+    <row r="991" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A991" s="2" t="s">
         <v>2590</v>
       </c>
@@ -28558,7 +28571,7 @@
       <c r="H991" s="5"/>
       <c r="I991" s="5"/>
     </row>
-    <row r="992" s="1" customFormat="1" spans="1:9">
+    <row r="992" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A992" s="2" t="s">
         <v>2600</v>
       </c>
@@ -28577,7 +28590,7 @@
       <c r="H992" s="5"/>
       <c r="I992" s="5"/>
     </row>
-    <row r="993" s="1" customFormat="1" spans="1:9">
+    <row r="993" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A993" s="2" t="s">
         <v>2604</v>
       </c>
@@ -28596,7 +28609,7 @@
       <c r="H993" s="5"/>
       <c r="I993" s="5"/>
     </row>
-    <row r="994" s="1" customFormat="1" spans="1:9">
+    <row r="994" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A994" s="2" t="s">
         <v>816</v>
       </c>
@@ -28615,7 +28628,7 @@
       <c r="H994" s="5"/>
       <c r="I994" s="5"/>
     </row>
-    <row r="995" s="1" customFormat="1" spans="1:9">
+    <row r="995" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A995" s="2" t="s">
         <v>816</v>
       </c>
@@ -28634,7 +28647,7 @@
       <c r="H995" s="5"/>
       <c r="I995" s="5"/>
     </row>
-    <row r="996" s="1" customFormat="1" spans="1:9">
+    <row r="996" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A996" s="2" t="s">
         <v>816</v>
       </c>
@@ -28653,7 +28666,7 @@
       <c r="H996" s="5"/>
       <c r="I996" s="5"/>
     </row>
-    <row r="997" s="1" customFormat="1" spans="1:9">
+    <row r="997" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A997" s="2" t="s">
         <v>816</v>
       </c>
@@ -28672,7 +28685,7 @@
       <c r="H997" s="5"/>
       <c r="I997" s="5"/>
     </row>
-    <row r="998" s="1" customFormat="1" spans="1:9">
+    <row r="998" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A998" s="2" t="s">
         <v>2620</v>
       </c>
@@ -28691,7 +28704,7 @@
       <c r="H998" s="5"/>
       <c r="I998" s="5"/>
     </row>
-    <row r="999" s="1" customFormat="1" spans="1:9">
+    <row r="999" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A999" s="2" t="s">
         <v>2624</v>
       </c>
@@ -28710,7 +28723,7 @@
       <c r="H999" s="5"/>
       <c r="I999" s="5"/>
     </row>
-    <row r="1000" s="1" customFormat="1" spans="1:9">
+    <row r="1000" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A1000" s="2" t="s">
         <v>2624</v>
       </c>
@@ -28729,7 +28742,7 @@
       <c r="H1000" s="5"/>
       <c r="I1000" s="5"/>
     </row>
-    <row r="1001" s="1" customFormat="1" spans="1:9">
+    <row r="1001" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A1001" s="2" t="s">
         <v>2624</v>
       </c>
@@ -28748,7 +28761,7 @@
       <c r="H1001" s="5"/>
       <c r="I1001" s="5"/>
     </row>
-    <row r="1002" s="1" customFormat="1" spans="1:9">
+    <row r="1002" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A1002" s="2" t="s">
         <v>2634</v>
       </c>
@@ -28767,7 +28780,7 @@
       <c r="H1002" s="5"/>
       <c r="I1002" s="5"/>
     </row>
-    <row r="1003" s="1" customFormat="1" spans="1:9">
+    <row r="1003" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A1003" s="2" t="s">
         <v>2638</v>
       </c>
@@ -28786,8 +28799,7 @@
       <c r="H1003" s="5"/>
       <c r="I1003" s="5"/>
     </row>
-    <row r="1004" s="1" customFormat="1" spans="1:9">
-      <c r="A1004" s="2"/>
+    <row r="1004" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="B1004" s="3" t="s">
         <v>2642</v>
       </c>
@@ -28805,8 +28817,7 @@
       </c>
       <c r="I1004" s="5"/>
     </row>
-    <row r="1005" s="1" customFormat="1" spans="1:9">
-      <c r="A1005" s="2"/>
+    <row r="1005" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="B1005" s="3" t="s">
         <v>2644</v>
       </c>
@@ -28822,8 +28833,7 @@
       <c r="H1005" s="5"/>
       <c r="I1005" s="5"/>
     </row>
-    <row r="1006" s="1" customFormat="1" spans="1:9">
-      <c r="A1006" s="2"/>
+    <row r="1006" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="B1006" s="3" t="s">
         <v>2647</v>
       </c>
@@ -28839,8 +28849,7 @@
       <c r="H1006" s="5"/>
       <c r="I1006" s="5"/>
     </row>
-    <row r="1007" s="1" customFormat="1" spans="1:9">
-      <c r="A1007" s="2"/>
+    <row r="1007" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="B1007" s="3" t="s">
         <v>2649</v>
       </c>
@@ -28856,8 +28865,7 @@
       <c r="H1007" s="5"/>
       <c r="I1007" s="5"/>
     </row>
-    <row r="1008" s="1" customFormat="1" spans="1:9">
-      <c r="A1008" s="2"/>
+    <row r="1008" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="B1008" s="3" t="s">
         <v>2651</v>
       </c>
@@ -28873,8 +28881,7 @@
       <c r="H1008" s="5"/>
       <c r="I1008" s="5"/>
     </row>
-    <row r="1009" s="1" customFormat="1" spans="1:9">
-      <c r="A1009" s="2"/>
+    <row r="1009" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1009" s="3" t="s">
         <v>2653</v>
       </c>
@@ -28890,8 +28897,7 @@
       <c r="H1009" s="5"/>
       <c r="I1009" s="5"/>
     </row>
-    <row r="1010" s="1" customFormat="1" spans="1:9">
-      <c r="A1010" s="2"/>
+    <row r="1010" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1010" s="3" t="s">
         <v>2655</v>
       </c>
@@ -28907,8 +28913,7 @@
       <c r="H1010" s="5"/>
       <c r="I1010" s="5"/>
     </row>
-    <row r="1011" s="1" customFormat="1" spans="1:9">
-      <c r="A1011" s="2"/>
+    <row r="1011" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1011" s="3" t="s">
         <v>2658</v>
       </c>
@@ -28924,8 +28929,7 @@
       <c r="H1011" s="5"/>
       <c r="I1011" s="5"/>
     </row>
-    <row r="1012" s="1" customFormat="1" spans="1:9">
-      <c r="A1012" s="2"/>
+    <row r="1012" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1012" s="3" t="s">
         <v>2661</v>
       </c>
@@ -28941,8 +28945,7 @@
       <c r="H1012" s="5"/>
       <c r="I1012" s="5"/>
     </row>
-    <row r="1013" s="1" customFormat="1" spans="1:9">
-      <c r="A1013" s="2"/>
+    <row r="1013" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1013" s="3" t="s">
         <v>2664</v>
       </c>
@@ -28958,8 +28961,7 @@
       <c r="H1013" s="5"/>
       <c r="I1013" s="5"/>
     </row>
-    <row r="1014" s="1" customFormat="1" spans="1:9">
-      <c r="A1014" s="2"/>
+    <row r="1014" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1014" s="3" t="s">
         <v>2666</v>
       </c>
@@ -28975,8 +28977,7 @@
       <c r="H1014" s="5"/>
       <c r="I1014" s="5"/>
     </row>
-    <row r="1015" s="1" customFormat="1" spans="1:9">
-      <c r="A1015" s="2"/>
+    <row r="1015" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1015" s="3" t="s">
         <v>2669</v>
       </c>
@@ -28992,8 +28993,7 @@
       <c r="H1015" s="5"/>
       <c r="I1015" s="5"/>
     </row>
-    <row r="1016" s="1" customFormat="1" spans="1:9">
-      <c r="A1016" s="2"/>
+    <row r="1016" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1016" s="3" t="s">
         <v>2672</v>
       </c>
@@ -29009,8 +29009,7 @@
       <c r="H1016" s="5"/>
       <c r="I1016" s="5"/>
     </row>
-    <row r="1017" s="1" customFormat="1" spans="1:9">
-      <c r="A1017" s="2"/>
+    <row r="1017" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1017" s="3" t="s">
         <v>2675</v>
       </c>
@@ -29026,8 +29025,7 @@
       <c r="H1017" s="5"/>
       <c r="I1017" s="5"/>
     </row>
-    <row r="1018" s="1" customFormat="1" spans="1:9">
-      <c r="A1018" s="2"/>
+    <row r="1018" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1018" s="3" t="s">
         <v>2678</v>
       </c>
@@ -29043,8 +29041,7 @@
       <c r="H1018" s="5"/>
       <c r="I1018" s="5"/>
     </row>
-    <row r="1019" s="1" customFormat="1" spans="1:9">
-      <c r="A1019" s="2"/>
+    <row r="1019" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1019" s="3" t="s">
         <v>2681</v>
       </c>
@@ -29060,8 +29057,7 @@
       <c r="H1019" s="5"/>
       <c r="I1019" s="5"/>
     </row>
-    <row r="1020" s="1" customFormat="1" spans="1:9">
-      <c r="A1020" s="2"/>
+    <row r="1020" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1020" s="3" t="s">
         <v>2684</v>
       </c>
@@ -29077,8 +29073,7 @@
       <c r="H1020" s="5"/>
       <c r="I1020" s="5"/>
     </row>
-    <row r="1021" s="1" customFormat="1" spans="1:9">
-      <c r="A1021" s="2"/>
+    <row r="1021" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1021" s="3" t="s">
         <v>2687</v>
       </c>
@@ -29094,8 +29089,7 @@
       <c r="H1021" s="5"/>
       <c r="I1021" s="5"/>
     </row>
-    <row r="1022" s="1" customFormat="1" spans="1:9">
-      <c r="A1022" s="2"/>
+    <row r="1022" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1022" s="3" t="s">
         <v>2690</v>
       </c>
@@ -29109,8 +29103,7 @@
       <c r="H1022" s="5"/>
       <c r="I1022" s="5"/>
     </row>
-    <row r="1023" s="1" customFormat="1" spans="1:9">
-      <c r="A1023" s="2"/>
+    <row r="1023" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1023" s="3" t="s">
         <v>2692</v>
       </c>
@@ -29124,8 +29117,7 @@
       <c r="H1023" s="5"/>
       <c r="I1023" s="5"/>
     </row>
-    <row r="1024" s="1" customFormat="1" spans="1:9">
-      <c r="A1024" s="2"/>
+    <row r="1024" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1024" s="3" t="s">
         <v>2694</v>
       </c>
@@ -29139,8 +29131,7 @@
       <c r="H1024" s="5"/>
       <c r="I1024" s="5"/>
     </row>
-    <row r="1025" s="1" customFormat="1" spans="1:9">
-      <c r="A1025" s="2"/>
+    <row r="1025" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1025" s="3" t="s">
         <v>2696</v>
       </c>
@@ -29154,8 +29145,7 @@
       <c r="H1025" s="5"/>
       <c r="I1025" s="5"/>
     </row>
-    <row r="1026" s="1" customFormat="1" spans="1:9">
-      <c r="A1026" s="2"/>
+    <row r="1026" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1026" s="3" t="s">
         <v>2698</v>
       </c>
@@ -29169,8 +29159,7 @@
       <c r="H1026" s="5"/>
       <c r="I1026" s="5"/>
     </row>
-    <row r="1027" s="1" customFormat="1" spans="1:9">
-      <c r="A1027" s="2"/>
+    <row r="1027" s="2" customFormat="1" ht="30" customHeight="1" spans="2:9">
       <c r="B1027" s="3" t="s">
         <v>2700</v>
       </c>
@@ -29186,7 +29175,7 @@
       </c>
       <c r="I1027" s="5"/>
     </row>
-    <row r="1028" spans="1:9">
+    <row r="1028" ht="30" customHeight="1" spans="2:9">
       <c r="B1028" s="3" t="s">
         <v>2702</v>
       </c>
@@ -29194,7 +29183,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="1029" spans="1:9">
+    <row r="1029" ht="30" customHeight="1" spans="2:9">
       <c r="B1029" s="3" t="s">
         <v>2704</v>
       </c>
@@ -29202,7 +29191,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="1030" spans="1:9">
+    <row r="1030" ht="30" customHeight="1" spans="2:9">
       <c r="B1030" s="3" t="s">
         <v>2706</v>
       </c>
@@ -29214,61 +29203,58 @@
       </c>
     </row>
     <row r="1109" spans="9:9">
-      <c r="I1109" s="13"/>
+      <c r="I1109" s="16"/>
     </row>
     <row r="1110" spans="9:9">
-      <c r="I1110" s="13"/>
+      <c r="I1110" s="16"/>
     </row>
     <row r="1111" spans="9:9">
-      <c r="I1111" s="13"/>
+      <c r="I1111" s="16"/>
     </row>
     <row r="1112" spans="9:9">
-      <c r="I1112" s="13"/>
+      <c r="I1112" s="16"/>
     </row>
     <row r="1113" spans="9:9">
-      <c r="I1113" s="13"/>
+      <c r="I1113" s="16"/>
     </row>
     <row r="1114" spans="9:9">
-      <c r="I1114" s="13"/>
+      <c r="I1114" s="16"/>
     </row>
     <row r="1115" spans="9:9">
-      <c r="I1115" s="13"/>
+      <c r="I1115" s="16"/>
     </row>
     <row r="1116" spans="9:9">
-      <c r="I1116" s="13"/>
+      <c r="I1116" s="16"/>
     </row>
     <row r="1117" spans="9:9">
-      <c r="I1117" s="13"/>
+      <c r="I1117" s="16"/>
     </row>
     <row r="1118" spans="9:9">
-      <c r="I1118" s="13"/>
+      <c r="I1118" s="16"/>
     </row>
     <row r="1119" spans="9:9">
-      <c r="I1119" s="13"/>
+      <c r="I1119" s="16"/>
     </row>
     <row r="1120" spans="9:9">
-      <c r="I1120" s="13"/>
+      <c r="I1120" s="16"/>
     </row>
     <row r="1121" spans="9:9">
-      <c r="I1121" s="13"/>
+      <c r="I1121" s="16"/>
     </row>
     <row r="1122" spans="9:9">
-      <c r="I1122" s="13"/>
+      <c r="I1122" s="16"/>
     </row>
     <row r="1123" spans="9:9">
-      <c r="I1123" s="13"/>
+      <c r="I1123" s="16"/>
     </row>
     <row r="1124" spans="9:9">
-      <c r="I1124" s="13"/>
+      <c r="I1124" s="16"/>
     </row>
     <row r="1125" spans="9:9">
-      <c r="I1125" s="13"/>
+      <c r="I1125" s="16"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I1030" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:I1030">
-      <sortCondition ref="E1"/>
-    </sortState>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I1125" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -29277,7 +29263,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B1:I1 B1031:I1125" numberStoredAsText="1"/>
+    <ignoredError sqref="B1031:I1125 B1:I1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/xlsx/CPE.xlsx
+++ b/xlsx/CPE.xlsx
@@ -123,8 +123,7 @@
 3. Allegro (A major)</t>
   </si>
   <si>
-    <t>Aussi version pour flûte traversière et cordes (Wq 168/H 438);
-violoncelle et cordes (Wq 172/H 439)</t>
+    <t>Aussi version pour flûte traversière et cordes (Wq 168/H 438); violoncelle et cordes (Wq 172/H 439)</t>
   </si>
   <si>
     <t>Wq. 168</t>
@@ -144,8 +143,7 @@
     <t>Transverse Flute, 2 Violins, Viola, Basso</t>
   </si>
   <si>
-    <t>Aussi version pour clavecin et cordes (Wq 29/H 437);
-violoncelle et cordes (Wq 172/H 439)</t>
+    <t>Aussi version pour clavecin et cordes (Wq 29/H 437); violoncelle et cordes (Wq 172/H 439)</t>
   </si>
   <si>
     <t>Wq. 172</t>
@@ -12502,6 +12500,10 @@
       <c r="C106" s="3" t="s">
         <v>381</v>
       </c>
+      <c r="D106" s="4" t="str">
+        <f t="shared" ref="D106:D112" si="0">E106&amp;" in "&amp;F106</f>
+        <v>Duet in A minor</v>
+      </c>
       <c r="E106" s="5" t="s">
         <v>382</v>
       </c>
@@ -12522,6 +12524,10 @@
       <c r="C107" s="3" t="s">
         <v>385</v>
       </c>
+      <c r="D107" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Duet in B-flat major</v>
+      </c>
       <c r="E107" s="5" t="s">
         <v>382</v>
       </c>
@@ -12539,6 +12545,10 @@
       <c r="C108" s="3" t="s">
         <v>387</v>
       </c>
+      <c r="D108" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Duet in C major</v>
+      </c>
       <c r="E108" s="5" t="s">
         <v>382</v>
       </c>
@@ -12559,6 +12569,10 @@
       <c r="C109" s="3" t="s">
         <v>390</v>
       </c>
+      <c r="D109" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Duet in D minor</v>
+      </c>
       <c r="E109" s="5" t="s">
         <v>382</v>
       </c>
@@ -12579,6 +12593,10 @@
       <c r="C110" s="3" t="s">
         <v>393</v>
       </c>
+      <c r="D110" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Duet in E minor</v>
+      </c>
       <c r="E110" s="5" t="s">
         <v>382</v>
       </c>
@@ -12599,6 +12617,10 @@
       <c r="C111" s="3" t="s">
         <v>396</v>
       </c>
+      <c r="D111" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Duet in E-flat major</v>
+      </c>
       <c r="E111" s="5" t="s">
         <v>382</v>
       </c>
@@ -12619,6 +12641,10 @@
       <c r="C112" s="3" t="s">
         <v>398</v>
       </c>
+      <c r="D112" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Duet in F major</v>
+      </c>
       <c r="E112" s="5" t="s">
         <v>382</v>
       </c>
@@ -12653,6 +12679,10 @@
       <c r="C114" s="3" t="s">
         <v>401</v>
       </c>
+      <c r="D114" s="4" t="str">
+        <f t="shared" ref="D114:D119" si="1">E114&amp;" in "&amp;F114</f>
+        <v>Fantasia in A major</v>
+      </c>
       <c r="E114" s="5" t="s">
         <v>402</v>
       </c>
@@ -12673,6 +12703,10 @@
       <c r="C115" s="3" t="s">
         <v>404</v>
       </c>
+      <c r="D115" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Fantasia in B-flat major</v>
+      </c>
       <c r="E115" s="5" t="s">
         <v>402</v>
       </c>
@@ -12693,6 +12727,10 @@
       <c r="C116" s="3" t="s">
         <v>404</v>
       </c>
+      <c r="D116" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Fantasia in B-flat major</v>
+      </c>
       <c r="E116" s="5" t="s">
         <v>402</v>
       </c>
@@ -12713,6 +12751,10 @@
       <c r="C117" s="3" t="s">
         <v>407</v>
       </c>
+      <c r="D117" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Fantasia in B-flat major</v>
+      </c>
       <c r="E117" s="5" t="s">
         <v>402</v>
       </c>
@@ -12733,6 +12775,10 @@
       <c r="C118" s="3" t="s">
         <v>409</v>
       </c>
+      <c r="D118" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Fantasia in C major</v>
+      </c>
       <c r="E118" s="5" t="s">
         <v>402</v>
       </c>
@@ -12753,6 +12799,10 @@
       <c r="C119" s="3" t="s">
         <v>411</v>
       </c>
+      <c r="D119" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Fantasia in C major</v>
+      </c>
       <c r="E119" s="5" t="s">
         <v>402</v>
       </c>
@@ -12796,6 +12846,10 @@
       <c r="C121" s="3" t="s">
         <v>416</v>
       </c>
+      <c r="D121" s="4" t="str">
+        <f t="shared" ref="D121:D133" si="2">E121&amp;" in "&amp;F121</f>
+        <v>Fantasia in D major</v>
+      </c>
       <c r="E121" s="5" t="s">
         <v>402</v>
       </c>
@@ -12816,6 +12870,10 @@
       <c r="C122" s="3" t="s">
         <v>416</v>
       </c>
+      <c r="D122" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in D major</v>
+      </c>
       <c r="E122" s="5" t="s">
         <v>402</v>
       </c>
@@ -12836,6 +12894,10 @@
       <c r="C123" s="3" t="s">
         <v>419</v>
       </c>
+      <c r="D123" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in D major</v>
+      </c>
       <c r="E123" s="5" t="s">
         <v>402</v>
       </c>
@@ -12856,6 +12918,10 @@
       <c r="C124" s="3" t="s">
         <v>421</v>
       </c>
+      <c r="D124" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in D minor</v>
+      </c>
       <c r="E124" s="5" t="s">
         <v>402</v>
       </c>
@@ -12876,6 +12942,10 @@
       <c r="C125" s="3" t="s">
         <v>421</v>
       </c>
+      <c r="D125" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in D minor</v>
+      </c>
       <c r="E125" s="5" t="s">
         <v>402</v>
       </c>
@@ -12896,6 +12966,10 @@
       <c r="C126" s="3" t="s">
         <v>424</v>
       </c>
+      <c r="D126" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in D minor</v>
+      </c>
       <c r="E126" s="5" t="s">
         <v>402</v>
       </c>
@@ -12916,6 +12990,10 @@
       <c r="C127" s="3" t="s">
         <v>426</v>
       </c>
+      <c r="D127" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in D minor</v>
+      </c>
       <c r="E127" s="5" t="s">
         <v>402</v>
       </c>
@@ -12936,6 +13014,10 @@
       <c r="C128" s="3" t="s">
         <v>426</v>
       </c>
+      <c r="D128" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in D minor</v>
+      </c>
       <c r="E128" s="5" t="s">
         <v>402</v>
       </c>
@@ -12956,6 +13038,10 @@
       <c r="C129" s="3" t="s">
         <v>429</v>
       </c>
+      <c r="D129" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in E-flat major</v>
+      </c>
       <c r="E129" s="5" t="s">
         <v>402</v>
       </c>
@@ -12976,6 +13062,10 @@
       <c r="C130" s="3" t="s">
         <v>431</v>
       </c>
+      <c r="D130" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in F major</v>
+      </c>
       <c r="E130" s="5" t="s">
         <v>402</v>
       </c>
@@ -12996,6 +13086,10 @@
       <c r="C131" s="3" t="s">
         <v>431</v>
       </c>
+      <c r="D131" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in F major</v>
+      </c>
       <c r="E131" s="5" t="s">
         <v>402</v>
       </c>
@@ -13016,6 +13110,10 @@
       <c r="C132" s="3" t="s">
         <v>434</v>
       </c>
+      <c r="D132" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in F major</v>
+      </c>
       <c r="E132" s="5" t="s">
         <v>402</v>
       </c>
@@ -13036,6 +13134,10 @@
       <c r="C133" s="3" t="s">
         <v>436</v>
       </c>
+      <c r="D133" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Fantasia in F-sharp minor</v>
+      </c>
       <c r="E133" s="5" t="s">
         <v>402</v>
       </c>
@@ -13079,6 +13181,10 @@
       <c r="C135" s="3" t="s">
         <v>443</v>
       </c>
+      <c r="D135" s="4" t="str">
+        <f>E135&amp;" in "&amp;F135</f>
+        <v>Fantasia in G major</v>
+      </c>
       <c r="E135" s="5" t="s">
         <v>402</v>
       </c>
@@ -13099,6 +13205,10 @@
       <c r="C136" s="3" t="s">
         <v>445</v>
       </c>
+      <c r="D136" s="4" t="str">
+        <f>E136&amp;" in "&amp;F136</f>
+        <v>Fantasia in G minor</v>
+      </c>
       <c r="E136" s="5" t="s">
         <v>402</v>
       </c>
@@ -16422,6 +16532,10 @@
       <c r="C299" s="3" t="s">
         <v>871</v>
       </c>
+      <c r="D299" s="4" t="str">
+        <f t="shared" ref="D299:D311" si="3">E299&amp;" in "&amp;F299</f>
+        <v>March in C major</v>
+      </c>
       <c r="E299" s="5" t="s">
         <v>872</v>
       </c>
@@ -16465,6 +16579,10 @@
       <c r="C301" s="3" t="s">
         <v>879</v>
       </c>
+      <c r="D301" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in D major</v>
+      </c>
       <c r="E301" s="5" t="s">
         <v>872</v>
       </c>
@@ -16485,6 +16603,10 @@
       <c r="C302" s="3" t="s">
         <v>881</v>
       </c>
+      <c r="D302" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in D major</v>
+      </c>
       <c r="E302" s="5" t="s">
         <v>872</v>
       </c>
@@ -16505,6 +16627,10 @@
       <c r="C303" s="3" t="s">
         <v>883</v>
       </c>
+      <c r="D303" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in D major</v>
+      </c>
       <c r="E303" s="5" t="s">
         <v>872</v>
       </c>
@@ -16522,6 +16648,10 @@
       <c r="C304" s="3" t="s">
         <v>885</v>
       </c>
+      <c r="D304" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in D major</v>
+      </c>
       <c r="E304" s="5" t="s">
         <v>872</v>
       </c>
@@ -16539,6 +16669,10 @@
       <c r="C305" s="3" t="s">
         <v>887</v>
       </c>
+      <c r="D305" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in D major</v>
+      </c>
       <c r="E305" s="5" t="s">
         <v>872</v>
       </c>
@@ -16559,6 +16693,10 @@
       <c r="C306" s="3" t="s">
         <v>890</v>
       </c>
+      <c r="D306" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in E-flat major</v>
+      </c>
       <c r="E306" s="5" t="s">
         <v>872</v>
       </c>
@@ -16579,6 +16717,10 @@
       <c r="C307" s="3" t="s">
         <v>892</v>
       </c>
+      <c r="D307" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in F major</v>
+      </c>
       <c r="E307" s="5" t="s">
         <v>872</v>
       </c>
@@ -16599,6 +16741,10 @@
       <c r="C308" s="3" t="s">
         <v>894</v>
       </c>
+      <c r="D308" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in F major</v>
+      </c>
       <c r="E308" s="5" t="s">
         <v>872</v>
       </c>
@@ -16616,6 +16762,10 @@
       <c r="C309" s="3" t="s">
         <v>896</v>
       </c>
+      <c r="D309" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in F major</v>
+      </c>
       <c r="E309" s="5" t="s">
         <v>872</v>
       </c>
@@ -16636,6 +16786,10 @@
       <c r="C310" s="3" t="s">
         <v>898</v>
       </c>
+      <c r="D310" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in G major</v>
+      </c>
       <c r="E310" s="5" t="s">
         <v>872</v>
       </c>
@@ -16656,6 +16810,10 @@
       <c r="C311" s="3" t="s">
         <v>900</v>
       </c>
+      <c r="D311" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>March in G major</v>
+      </c>
       <c r="E311" s="5" t="s">
         <v>872</v>
       </c>
@@ -16701,6 +16859,10 @@
       <c r="C314" s="3" t="s">
         <v>905</v>
       </c>
+      <c r="D314" s="4" t="str">
+        <f t="shared" ref="D314:D316" si="4">E314&amp;" in "&amp;F314</f>
+        <v>Menuet in A major</v>
+      </c>
       <c r="E314" s="5" t="s">
         <v>906</v>
       </c>
@@ -16721,6 +16883,10 @@
       <c r="C315" s="3" t="s">
         <v>905</v>
       </c>
+      <c r="D315" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>Menuet in A major</v>
+      </c>
       <c r="E315" s="5" t="s">
         <v>906</v>
       </c>
@@ -16741,6 +16907,10 @@
       <c r="C316" s="3" t="s">
         <v>909</v>
       </c>
+      <c r="D316" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>Menuet in C major</v>
+      </c>
       <c r="E316" s="5" t="s">
         <v>906</v>
       </c>
@@ -16784,6 +16954,10 @@
       <c r="C318" s="3" t="s">
         <v>914</v>
       </c>
+      <c r="D318" s="4" t="str">
+        <f t="shared" ref="D318:D332" si="5">E318&amp;" in "&amp;F318</f>
+        <v>Menuet in C major</v>
+      </c>
       <c r="E318" s="5" t="s">
         <v>906</v>
       </c>
@@ -16804,6 +16978,10 @@
       <c r="C319" s="3" t="s">
         <v>916</v>
       </c>
+      <c r="D319" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in C major</v>
+      </c>
       <c r="E319" s="5" t="s">
         <v>906</v>
       </c>
@@ -16870,6 +17048,10 @@
       <c r="C322" s="3" t="s">
         <v>924</v>
       </c>
+      <c r="D322" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in C major</v>
+      </c>
       <c r="E322" s="5" t="s">
         <v>906</v>
       </c>
@@ -16887,6 +17069,10 @@
       <c r="C323" s="3" t="s">
         <v>926</v>
       </c>
+      <c r="D323" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in C major</v>
+      </c>
       <c r="E323" s="5" t="s">
         <v>906</v>
       </c>
@@ -16913,6 +17099,10 @@
       <c r="C324" s="3" t="s">
         <v>931</v>
       </c>
+      <c r="D324" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E324" s="5" t="s">
         <v>906</v>
       </c>
@@ -16933,6 +17123,10 @@
       <c r="C325" s="3" t="s">
         <v>931</v>
       </c>
+      <c r="D325" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E325" s="5" t="s">
         <v>906</v>
       </c>
@@ -16953,6 +17147,10 @@
       <c r="C326" s="3" t="s">
         <v>934</v>
       </c>
+      <c r="D326" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E326" s="5" t="s">
         <v>906</v>
       </c>
@@ -16973,6 +17171,10 @@
       <c r="C327" s="3" t="s">
         <v>934</v>
       </c>
+      <c r="D327" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E327" s="5" t="s">
         <v>906</v>
       </c>
@@ -16993,6 +17195,10 @@
       <c r="C328" s="3" t="s">
         <v>937</v>
       </c>
+      <c r="D328" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E328" s="5" t="s">
         <v>906</v>
       </c>
@@ -17013,6 +17219,10 @@
       <c r="C329" s="3" t="s">
         <v>940</v>
       </c>
+      <c r="D329" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E329" s="5" t="s">
         <v>906</v>
       </c>
@@ -17033,6 +17243,10 @@
       <c r="C330" s="3" t="s">
         <v>942</v>
       </c>
+      <c r="D330" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E330" s="5" t="s">
         <v>906</v>
       </c>
@@ -17053,6 +17267,10 @@
       <c r="C331" s="3" t="s">
         <v>944</v>
       </c>
+      <c r="D331" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E331" s="5" t="s">
         <v>906</v>
       </c>
@@ -17073,6 +17291,10 @@
       <c r="C332" s="3" t="s">
         <v>947</v>
       </c>
+      <c r="D332" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E332" s="5" t="s">
         <v>906</v>
       </c>
@@ -17113,6 +17335,10 @@
       <c r="C334" s="3" t="s">
         <v>953</v>
       </c>
+      <c r="D334" s="4" t="str">
+        <f t="shared" ref="D334:D341" si="6">E334&amp;" in "&amp;F334</f>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E334" s="5" t="s">
         <v>906</v>
       </c>
@@ -17133,6 +17359,10 @@
       <c r="C335" s="3" t="s">
         <v>955</v>
       </c>
+      <c r="D335" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E335" s="5" t="s">
         <v>906</v>
       </c>
@@ -17153,6 +17383,10 @@
       <c r="C336" s="3" t="s">
         <v>957</v>
       </c>
+      <c r="D336" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E336" s="5" t="s">
         <v>906</v>
       </c>
@@ -17170,6 +17404,10 @@
       <c r="C337" s="3" t="s">
         <v>959</v>
       </c>
+      <c r="D337" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>Menuet in D major</v>
+      </c>
       <c r="E337" s="5" t="s">
         <v>906</v>
       </c>
@@ -17196,6 +17434,10 @@
       <c r="C338" s="3" t="s">
         <v>964</v>
       </c>
+      <c r="D338" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>Menuet in E-flat major</v>
+      </c>
       <c r="E338" s="5" t="s">
         <v>906</v>
       </c>
@@ -17216,6 +17458,10 @@
       <c r="C339" s="3" t="s">
         <v>966</v>
       </c>
+      <c r="D339" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>Menuet in F major</v>
+      </c>
       <c r="E339" s="5" t="s">
         <v>906</v>
       </c>
@@ -17236,6 +17482,10 @@
       <c r="C340" s="3" t="s">
         <v>968</v>
       </c>
+      <c r="D340" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>Menuet in F major</v>
+      </c>
       <c r="E340" s="5" t="s">
         <v>906</v>
       </c>
@@ -17256,6 +17506,10 @@
       <c r="C341" s="3" t="s">
         <v>970</v>
       </c>
+      <c r="D341" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v>Menuet in F major</v>
+      </c>
       <c r="E341" s="5" t="s">
         <v>906</v>
       </c>
@@ -17296,6 +17550,10 @@
       <c r="C343" s="3" t="s">
         <v>975</v>
       </c>
+      <c r="D343" s="4" t="str">
+        <f t="shared" ref="D343:D347" si="7">E343&amp;" in "&amp;F343</f>
+        <v>Menuet in F major</v>
+      </c>
       <c r="E343" s="5" t="s">
         <v>906</v>
       </c>
@@ -17316,6 +17574,10 @@
       <c r="C344" s="3" t="s">
         <v>977</v>
       </c>
+      <c r="D344" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Menuet in G major</v>
+      </c>
       <c r="E344" s="5" t="s">
         <v>906</v>
       </c>
@@ -17336,6 +17598,10 @@
       <c r="C345" s="3" t="s">
         <v>979</v>
       </c>
+      <c r="D345" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Menuet in G major</v>
+      </c>
       <c r="E345" s="5" t="s">
         <v>906</v>
       </c>
@@ -17362,6 +17628,10 @@
       <c r="C346" s="3" t="s">
         <v>984</v>
       </c>
+      <c r="D346" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Menuet in G major</v>
+      </c>
       <c r="E346" s="5" t="s">
         <v>906</v>
       </c>
@@ -17382,6 +17652,10 @@
       <c r="C347" s="3" t="s">
         <v>986</v>
       </c>
+      <c r="D347" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Menuet in G major</v>
+      </c>
       <c r="E347" s="5" t="s">
         <v>906</v>
       </c>
@@ -17448,6 +17722,10 @@
       <c r="C350" s="3" t="s">
         <v>994</v>
       </c>
+      <c r="D350" s="4" t="str">
+        <f t="shared" ref="D350:D352" si="8">E350&amp;" in "&amp;F350</f>
+        <v>Menuet in G major</v>
+      </c>
       <c r="E350" s="5" t="s">
         <v>906</v>
       </c>
@@ -17468,6 +17746,10 @@
       <c r="C351" s="3" t="s">
         <v>996</v>
       </c>
+      <c r="D351" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v>Menuet in G major</v>
+      </c>
       <c r="E351" s="5" t="s">
         <v>906</v>
       </c>
@@ -17488,6 +17770,10 @@
       <c r="C352" s="3" t="s">
         <v>998</v>
       </c>
+      <c r="D352" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v>Menuet in G major</v>
+      </c>
       <c r="E352" s="5" t="s">
         <v>906</v>
       </c>
@@ -17693,7 +17979,6 @@
       <c r="E363" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="F363" s="2"/>
       <c r="G363" s="6" t="s">
         <v>1030</v>
       </c>
@@ -19066,7 +19351,7 @@
         <v>1258</v>
       </c>
       <c r="D436" s="4" t="str">
-        <f t="shared" ref="D436:D475" si="0">E436&amp;" in "&amp;F436</f>
+        <f t="shared" ref="D436:D475" si="9">E436&amp;" in "&amp;F436</f>
         <v>Sonata in A major</v>
       </c>
       <c r="E436" s="5" t="s">
@@ -19093,7 +19378,7 @@
         <v>1260</v>
       </c>
       <c r="D437" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E437" s="5" t="s">
@@ -19117,7 +19402,7 @@
         <v>1262</v>
       </c>
       <c r="D438" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E438" s="5" t="s">
@@ -19141,7 +19426,7 @@
         <v>1264</v>
       </c>
       <c r="D439" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E439" s="5" t="s">
@@ -19165,7 +19450,7 @@
         <v>1266</v>
       </c>
       <c r="D440" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E440" s="5" t="s">
@@ -19189,7 +19474,7 @@
         <v>1268</v>
       </c>
       <c r="D441" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E441" s="5" t="s">
@@ -19213,7 +19498,7 @@
         <v>1270</v>
       </c>
       <c r="D442" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E442" s="5" t="s">
@@ -19237,7 +19522,7 @@
         <v>1272</v>
       </c>
       <c r="D443" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E443" s="5" t="s">
@@ -19261,7 +19546,7 @@
         <v>1274</v>
       </c>
       <c r="D444" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E444" s="5" t="s">
@@ -19285,7 +19570,7 @@
         <v>1276</v>
       </c>
       <c r="D445" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E445" s="5" t="s">
@@ -19309,7 +19594,7 @@
         <v>1279</v>
       </c>
       <c r="D446" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E446" s="5" t="s">
@@ -19333,7 +19618,7 @@
         <v>1282</v>
       </c>
       <c r="D447" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A major</v>
       </c>
       <c r="E447" s="5" t="s">
@@ -19357,7 +19642,7 @@
         <v>1284</v>
       </c>
       <c r="D448" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E448" s="5" t="s">
@@ -19384,7 +19669,7 @@
         <v>1286</v>
       </c>
       <c r="D449" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E449" s="5" t="s">
@@ -19411,7 +19696,7 @@
         <v>1288</v>
       </c>
       <c r="D450" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E450" s="5" t="s">
@@ -19435,7 +19720,7 @@
         <v>1290</v>
       </c>
       <c r="D451" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E451" s="5" t="s">
@@ -19459,7 +19744,7 @@
         <v>1292</v>
       </c>
       <c r="D452" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E452" s="5" t="s">
@@ -19486,7 +19771,7 @@
         <v>1296</v>
       </c>
       <c r="D453" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E453" s="5" t="s">
@@ -19510,7 +19795,7 @@
         <v>1298</v>
       </c>
       <c r="D454" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E454" s="5" t="s">
@@ -19534,7 +19819,7 @@
         <v>1300</v>
       </c>
       <c r="D455" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E455" s="5" t="s">
@@ -19558,7 +19843,7 @@
         <v>1302</v>
       </c>
       <c r="D456" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E456" s="5" t="s">
@@ -19582,7 +19867,7 @@
         <v>1304</v>
       </c>
       <c r="D457" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E457" s="5" t="s">
@@ -19606,7 +19891,7 @@
         <v>1306</v>
       </c>
       <c r="D458" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E458" s="5" t="s">
@@ -19630,7 +19915,7 @@
         <v>1308</v>
       </c>
       <c r="D459" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E459" s="5" t="s">
@@ -19654,7 +19939,7 @@
         <v>1311</v>
       </c>
       <c r="D460" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A minor</v>
       </c>
       <c r="E460" s="5" t="s">
@@ -19678,7 +19963,7 @@
         <v>1314</v>
       </c>
       <c r="D461" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in A-flat major</v>
       </c>
       <c r="E461" s="5" t="s">
@@ -19702,7 +19987,7 @@
         <v>1317</v>
       </c>
       <c r="D462" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B minor</v>
       </c>
       <c r="E462" s="5" t="s">
@@ -19729,7 +20014,7 @@
         <v>1319</v>
       </c>
       <c r="D463" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B minor</v>
       </c>
       <c r="E463" s="5" t="s">
@@ -19753,7 +20038,7 @@
         <v>1321</v>
       </c>
       <c r="D464" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B minor</v>
       </c>
       <c r="E464" s="5" t="s">
@@ -19777,7 +20062,7 @@
         <v>1323</v>
       </c>
       <c r="D465" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B minor</v>
       </c>
       <c r="E465" s="5" t="s">
@@ -19801,7 +20086,7 @@
         <v>1325</v>
       </c>
       <c r="D466" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B minor</v>
       </c>
       <c r="E466" s="5" t="s">
@@ -19825,7 +20110,7 @@
         <v>1327</v>
       </c>
       <c r="D467" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B minor</v>
       </c>
       <c r="E467" s="5" t="s">
@@ -19846,7 +20131,7 @@
         <v>1328</v>
       </c>
       <c r="D468" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B minor</v>
       </c>
       <c r="E468" s="5" t="s">
@@ -19876,7 +20161,7 @@
         <v>1331</v>
       </c>
       <c r="D469" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B minor</v>
       </c>
       <c r="E469" s="5" t="s">
@@ -19900,7 +20185,7 @@
         <v>1333</v>
       </c>
       <c r="D470" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B minor</v>
       </c>
       <c r="E470" s="5" t="s">
@@ -19924,7 +20209,7 @@
         <v>1335</v>
       </c>
       <c r="D471" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E471" s="5" t="s">
@@ -19951,7 +20236,7 @@
         <v>1337</v>
       </c>
       <c r="D472" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E472" s="5" t="s">
@@ -19978,7 +20263,7 @@
         <v>1339</v>
       </c>
       <c r="D473" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E473" s="5" t="s">
@@ -20002,7 +20287,7 @@
         <v>1341</v>
       </c>
       <c r="D474" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E474" s="5" t="s">
@@ -20026,7 +20311,7 @@
         <v>1343</v>
       </c>
       <c r="D475" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E475" s="5" t="s">
@@ -20097,7 +20382,7 @@
         <v>1350</v>
       </c>
       <c r="D478" s="4" t="str">
-        <f t="shared" ref="D478:D509" si="1">E478&amp;" in "&amp;F478</f>
+        <f t="shared" ref="D478:D509" si="10">E478&amp;" in "&amp;F478</f>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E478" s="5" t="s">
@@ -20121,7 +20406,7 @@
         <v>1352</v>
       </c>
       <c r="D479" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E479" s="5" t="s">
@@ -20145,7 +20430,7 @@
         <v>1355</v>
       </c>
       <c r="D480" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E480" s="5" t="s">
@@ -20169,7 +20454,7 @@
         <v>1357</v>
       </c>
       <c r="D481" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E481" s="5" t="s">
@@ -20193,7 +20478,7 @@
         <v>1359</v>
       </c>
       <c r="D482" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E482" s="5" t="s">
@@ -20217,7 +20502,7 @@
         <v>1361</v>
       </c>
       <c r="D483" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E483" s="5" t="s">
@@ -20241,7 +20526,7 @@
         <v>1363</v>
       </c>
       <c r="D484" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E484" s="5" t="s">
@@ -20265,7 +20550,7 @@
         <v>1365</v>
       </c>
       <c r="D485" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E485" s="5" t="s">
@@ -20289,7 +20574,7 @@
         <v>1367</v>
       </c>
       <c r="D486" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E486" s="5" t="s">
@@ -20313,7 +20598,7 @@
         <v>1369</v>
       </c>
       <c r="D487" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E487" s="5" t="s">
@@ -20337,7 +20622,7 @@
         <v>1371</v>
       </c>
       <c r="D488" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E488" s="5" t="s">
@@ -20361,7 +20646,7 @@
         <v>1373</v>
       </c>
       <c r="D489" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E489" s="5" t="s">
@@ -20385,7 +20670,7 @@
         <v>1375</v>
       </c>
       <c r="D490" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E490" s="5" t="s">
@@ -20409,7 +20694,7 @@
         <v>1378</v>
       </c>
       <c r="D491" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E491" s="5" t="s">
@@ -20433,7 +20718,7 @@
         <v>1380</v>
       </c>
       <c r="D492" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E492" s="5" t="s">
@@ -20457,7 +20742,7 @@
         <v>1382</v>
       </c>
       <c r="D493" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in B-flat major</v>
       </c>
       <c r="E493" s="5" t="s">
@@ -20478,7 +20763,7 @@
         <v>1383</v>
       </c>
       <c r="D494" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E494" s="5" t="s">
@@ -20508,7 +20793,7 @@
         <v>1387</v>
       </c>
       <c r="D495" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E495" s="5" t="s">
@@ -20535,7 +20820,7 @@
         <v>1389</v>
       </c>
       <c r="D496" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E496" s="5" t="s">
@@ -20562,7 +20847,7 @@
         <v>1391</v>
       </c>
       <c r="D497" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E497" s="5" t="s">
@@ -20586,7 +20871,7 @@
         <v>1393</v>
       </c>
       <c r="D498" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E498" s="5" t="s">
@@ -20610,7 +20895,7 @@
         <v>1395</v>
       </c>
       <c r="D499" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E499" s="5" t="s">
@@ -20634,7 +20919,7 @@
         <v>1397</v>
       </c>
       <c r="D500" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E500" s="5" t="s">
@@ -20658,7 +20943,7 @@
         <v>1399</v>
       </c>
       <c r="D501" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E501" s="5" t="s">
@@ -20682,7 +20967,7 @@
         <v>1401</v>
       </c>
       <c r="D502" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E502" s="5" t="s">
@@ -20706,7 +20991,7 @@
         <v>1403</v>
       </c>
       <c r="D503" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E503" s="5" t="s">
@@ -20730,7 +21015,7 @@
         <v>1405</v>
       </c>
       <c r="D504" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E504" s="5" t="s">
@@ -20754,7 +21039,7 @@
         <v>1407</v>
       </c>
       <c r="D505" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E505" s="5" t="s">
@@ -20778,7 +21063,7 @@
         <v>1409</v>
       </c>
       <c r="D506" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E506" s="5" t="s">
@@ -20802,7 +21087,7 @@
         <v>1411</v>
       </c>
       <c r="D507" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E507" s="5" t="s">
@@ -20826,7 +21111,7 @@
         <v>1413</v>
       </c>
       <c r="D508" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E508" s="5" t="s">
@@ -20850,7 +21135,7 @@
         <v>1415</v>
       </c>
       <c r="D509" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E509" s="5" t="s">
@@ -20874,7 +21159,7 @@
         <v>1417</v>
       </c>
       <c r="D510" s="4" t="str">
-        <f t="shared" ref="D510:D534" si="2">E510&amp;" in "&amp;F510</f>
+        <f t="shared" ref="D510:D534" si="11">E510&amp;" in "&amp;F510</f>
         <v>Sonata in C major</v>
       </c>
       <c r="E510" s="5" t="s">
@@ -20898,7 +21183,7 @@
         <v>1419</v>
       </c>
       <c r="D511" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E511" s="5" t="s">
@@ -20922,7 +21207,7 @@
         <v>1421</v>
       </c>
       <c r="D512" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E512" s="5" t="s">
@@ -20946,7 +21231,7 @@
         <v>1423</v>
       </c>
       <c r="D513" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E513" s="5" t="s">
@@ -20970,7 +21255,7 @@
         <v>1426</v>
       </c>
       <c r="D514" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E514" s="5" t="s">
@@ -20994,7 +21279,7 @@
         <v>1428</v>
       </c>
       <c r="D515" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E515" s="5" t="s">
@@ -21018,7 +21303,7 @@
         <v>1430</v>
       </c>
       <c r="D516" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E516" s="5" t="s">
@@ -21042,7 +21327,7 @@
         <v>1432</v>
       </c>
       <c r="D517" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E517" s="5" t="s">
@@ -21066,7 +21351,7 @@
         <v>1434</v>
       </c>
       <c r="D518" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E518" s="5" t="s">
@@ -21090,7 +21375,7 @@
         <v>1436</v>
       </c>
       <c r="D519" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C major</v>
       </c>
       <c r="E519" s="5" t="s">
@@ -21114,7 +21399,7 @@
         <v>1438</v>
       </c>
       <c r="D520" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C minor</v>
       </c>
       <c r="E520" s="5" t="s">
@@ -21138,7 +21423,7 @@
         <v>1440</v>
       </c>
       <c r="D521" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C minor</v>
       </c>
       <c r="E521" s="5" t="s">
@@ -21162,7 +21447,7 @@
         <v>1442</v>
       </c>
       <c r="D522" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C minor</v>
       </c>
       <c r="E522" s="5" t="s">
@@ -21186,7 +21471,7 @@
         <v>1444</v>
       </c>
       <c r="D523" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C minor</v>
       </c>
       <c r="E523" s="5" t="s">
@@ -21210,7 +21495,7 @@
         <v>1446</v>
       </c>
       <c r="D524" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C minor</v>
       </c>
       <c r="E524" s="5" t="s">
@@ -21234,7 +21519,7 @@
         <v>1448</v>
       </c>
       <c r="D525" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C minor</v>
       </c>
       <c r="E525" s="5" t="s">
@@ -21258,7 +21543,7 @@
         <v>1450</v>
       </c>
       <c r="D526" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in C minor</v>
       </c>
       <c r="E526" s="5" t="s">
@@ -21282,7 +21567,7 @@
         <v>1452</v>
       </c>
       <c r="D527" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E527" s="5" t="s">
@@ -21309,7 +21594,7 @@
         <v>1455</v>
       </c>
       <c r="D528" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E528" s="5" t="s">
@@ -21333,7 +21618,7 @@
         <v>1457</v>
       </c>
       <c r="D529" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E529" s="5" t="s">
@@ -21357,7 +21642,7 @@
         <v>1459</v>
       </c>
       <c r="D530" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E530" s="5" t="s">
@@ -21381,7 +21666,7 @@
         <v>1461</v>
       </c>
       <c r="D531" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E531" s="5" t="s">
@@ -21405,7 +21690,7 @@
         <v>1463</v>
       </c>
       <c r="D532" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E532" s="5" t="s">
@@ -21429,7 +21714,7 @@
         <v>1465</v>
       </c>
       <c r="D533" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E533" s="5" t="s">
@@ -21453,7 +21738,7 @@
         <v>1467</v>
       </c>
       <c r="D534" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E534" s="5" t="s">
@@ -21524,7 +21809,7 @@
         <v>1474</v>
       </c>
       <c r="D537" s="4" t="str">
-        <f t="shared" ref="D537:D568" si="3">E537&amp;" in "&amp;F537</f>
+        <f t="shared" ref="D537:D568" si="12">E537&amp;" in "&amp;F537</f>
         <v>Sonata in D major</v>
       </c>
       <c r="E537" s="5" t="s">
@@ -21548,7 +21833,7 @@
         <v>1476</v>
       </c>
       <c r="D538" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E538" s="5" t="s">
@@ -21572,7 +21857,7 @@
         <v>1478</v>
       </c>
       <c r="D539" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E539" s="5" t="s">
@@ -21596,7 +21881,7 @@
         <v>1480</v>
       </c>
       <c r="D540" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E540" s="5" t="s">
@@ -21620,7 +21905,7 @@
         <v>1482</v>
       </c>
       <c r="D541" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E541" s="5" t="s">
@@ -21644,7 +21929,7 @@
         <v>1484</v>
       </c>
       <c r="D542" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E542" s="5" t="s">
@@ -21668,7 +21953,7 @@
         <v>1486</v>
       </c>
       <c r="D543" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D major</v>
       </c>
       <c r="E543" s="5" t="s">
@@ -21692,7 +21977,7 @@
         <v>1488</v>
       </c>
       <c r="D544" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E544" s="5" t="s">
@@ -21719,7 +22004,7 @@
         <v>1490</v>
       </c>
       <c r="D545" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E545" s="5" t="s">
@@ -21749,7 +22034,7 @@
         <v>1493</v>
       </c>
       <c r="D546" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E546" s="5" t="s">
@@ -21776,7 +22061,7 @@
         <v>1495</v>
       </c>
       <c r="D547" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E547" s="5" t="s">
@@ -21800,7 +22085,7 @@
         <v>1497</v>
       </c>
       <c r="D548" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E548" s="5" t="s">
@@ -21824,7 +22109,7 @@
         <v>1499</v>
       </c>
       <c r="D549" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E549" s="5" t="s">
@@ -21848,7 +22133,7 @@
         <v>1501</v>
       </c>
       <c r="D550" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E550" s="5" t="s">
@@ -21872,7 +22157,7 @@
         <v>1503</v>
       </c>
       <c r="D551" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E551" s="5" t="s">
@@ -21896,7 +22181,7 @@
         <v>1505</v>
       </c>
       <c r="D552" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E552" s="5" t="s">
@@ -21920,7 +22205,7 @@
         <v>1507</v>
       </c>
       <c r="D553" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E553" s="5" t="s">
@@ -21944,7 +22229,7 @@
         <v>1509</v>
       </c>
       <c r="D554" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E554" s="5" t="s">
@@ -21968,7 +22253,7 @@
         <v>1511</v>
       </c>
       <c r="D555" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E555" s="5" t="s">
@@ -21992,7 +22277,7 @@
         <v>1513</v>
       </c>
       <c r="D556" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E556" s="5" t="s">
@@ -22016,7 +22301,7 @@
         <v>1515</v>
       </c>
       <c r="D557" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E557" s="5" t="s">
@@ -22040,7 +22325,7 @@
         <v>1517</v>
       </c>
       <c r="D558" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in D minor</v>
       </c>
       <c r="E558" s="5" t="s">
@@ -22064,7 +22349,7 @@
         <v>1519</v>
       </c>
       <c r="D559" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in E major</v>
       </c>
       <c r="E559" s="5" t="s">
@@ -22088,7 +22373,7 @@
         <v>1521</v>
       </c>
       <c r="D560" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in E major</v>
       </c>
       <c r="E560" s="5" t="s">
@@ -22112,7 +22397,7 @@
         <v>1523</v>
       </c>
       <c r="D561" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in E major</v>
       </c>
       <c r="E561" s="5" t="s">
@@ -22136,7 +22421,7 @@
         <v>1525</v>
       </c>
       <c r="D562" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in E major</v>
       </c>
       <c r="E562" s="5" t="s">
@@ -22160,7 +22445,7 @@
         <v>1528</v>
       </c>
       <c r="D563" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in E major</v>
       </c>
       <c r="E563" s="5" t="s">
@@ -22184,7 +22469,7 @@
         <v>1530</v>
       </c>
       <c r="D564" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in E major</v>
       </c>
       <c r="E564" s="5" t="s">
@@ -22208,7 +22493,7 @@
         <v>1532</v>
       </c>
       <c r="D565" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in E major</v>
       </c>
       <c r="E565" s="5" t="s">
@@ -22232,7 +22517,7 @@
         <v>1534</v>
       </c>
       <c r="D566" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in E major</v>
       </c>
       <c r="E566" s="5" t="s">
@@ -22256,7 +22541,7 @@
         <v>1536</v>
       </c>
       <c r="D567" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E567" s="5" t="s">
@@ -22283,7 +22568,7 @@
         <v>1538</v>
       </c>
       <c r="D568" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E568" s="5" t="s">
@@ -22310,7 +22595,7 @@
         <v>1540</v>
       </c>
       <c r="D569" s="4" t="str">
-        <f t="shared" ref="D569:D600" si="4">E569&amp;" in "&amp;F569</f>
+        <f t="shared" ref="D569:D600" si="13">E569&amp;" in "&amp;F569</f>
         <v>Sonata in E minor</v>
       </c>
       <c r="E569" s="5" t="s">
@@ -22337,7 +22622,7 @@
         <v>1542</v>
       </c>
       <c r="D570" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E570" s="5" t="s">
@@ -22361,7 +22646,7 @@
         <v>1544</v>
       </c>
       <c r="D571" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E571" s="5" t="s">
@@ -22385,7 +22670,7 @@
         <v>1546</v>
       </c>
       <c r="D572" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E572" s="5" t="s">
@@ -22409,7 +22694,7 @@
         <v>1548</v>
       </c>
       <c r="D573" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E573" s="5" t="s">
@@ -22433,7 +22718,7 @@
         <v>1550</v>
       </c>
       <c r="D574" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E574" s="5" t="s">
@@ -22457,7 +22742,7 @@
         <v>1552</v>
       </c>
       <c r="D575" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E575" s="5" t="s">
@@ -22481,7 +22766,7 @@
         <v>1554</v>
       </c>
       <c r="D576" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E576" s="5" t="s">
@@ -22505,7 +22790,7 @@
         <v>1556</v>
       </c>
       <c r="D577" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E577" s="5" t="s">
@@ -22529,7 +22814,7 @@
         <v>1558</v>
       </c>
       <c r="D578" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E578" s="5" t="s">
@@ -22553,7 +22838,7 @@
         <v>1560</v>
       </c>
       <c r="D579" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E579" s="5" t="s">
@@ -22577,7 +22862,7 @@
         <v>1562</v>
       </c>
       <c r="D580" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E minor</v>
       </c>
       <c r="E580" s="5" t="s">
@@ -22601,7 +22886,7 @@
         <v>1564</v>
       </c>
       <c r="D581" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E581" s="5" t="s">
@@ -22628,7 +22913,7 @@
         <v>1566</v>
       </c>
       <c r="D582" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E582" s="5" t="s">
@@ -22652,7 +22937,7 @@
         <v>1568</v>
       </c>
       <c r="D583" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E583" s="5" t="s">
@@ -22676,7 +22961,7 @@
         <v>1570</v>
       </c>
       <c r="D584" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E584" s="5" t="s">
@@ -22700,7 +22985,7 @@
         <v>1572</v>
       </c>
       <c r="D585" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E585" s="5" t="s">
@@ -22724,7 +23009,7 @@
         <v>1574</v>
       </c>
       <c r="D586" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E586" s="5" t="s">
@@ -22748,7 +23033,7 @@
         <v>1576</v>
       </c>
       <c r="D587" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E587" s="5" t="s">
@@ -22772,7 +23057,7 @@
         <v>1578</v>
       </c>
       <c r="D588" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E588" s="5" t="s">
@@ -22796,7 +23081,7 @@
         <v>1580</v>
       </c>
       <c r="D589" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E589" s="5" t="s">
@@ -22820,7 +23105,7 @@
         <v>1582</v>
       </c>
       <c r="D590" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E590" s="5" t="s">
@@ -22844,7 +23129,7 @@
         <v>1584</v>
       </c>
       <c r="D591" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E591" s="5" t="s">
@@ -22868,7 +23153,7 @@
         <v>1586</v>
       </c>
       <c r="D592" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E592" s="5" t="s">
@@ -22892,7 +23177,7 @@
         <v>1588</v>
       </c>
       <c r="D593" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in E-flat major</v>
       </c>
       <c r="E593" s="5" t="s">
@@ -22916,7 +23201,7 @@
         <v>1590</v>
       </c>
       <c r="D594" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E594" s="5" t="s">
@@ -22943,7 +23228,7 @@
         <v>1592</v>
       </c>
       <c r="D595" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E595" s="5" t="s">
@@ -22967,7 +23252,7 @@
         <v>1594</v>
       </c>
       <c r="D596" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E596" s="5" t="s">
@@ -22991,7 +23276,7 @@
         <v>1596</v>
       </c>
       <c r="D597" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E597" s="5" t="s">
@@ -23015,7 +23300,7 @@
         <v>1598</v>
       </c>
       <c r="D598" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E598" s="5" t="s">
@@ -23039,7 +23324,7 @@
         <v>1600</v>
       </c>
       <c r="D599" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E599" s="5" t="s">
@@ -23063,7 +23348,7 @@
         <v>1602</v>
       </c>
       <c r="D600" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E600" s="5" t="s">
@@ -23087,7 +23372,7 @@
         <v>1604</v>
       </c>
       <c r="D601" s="4" t="str">
-        <f t="shared" ref="D601:D631" si="5">E601&amp;" in "&amp;F601</f>
+        <f t="shared" ref="D601:D631" si="14">E601&amp;" in "&amp;F601</f>
         <v>Sonata in F major</v>
       </c>
       <c r="E601" s="5" t="s">
@@ -23111,7 +23396,7 @@
         <v>1606</v>
       </c>
       <c r="D602" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E602" s="5" t="s">
@@ -23135,7 +23420,7 @@
         <v>1609</v>
       </c>
       <c r="D603" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E603" s="5" t="s">
@@ -23159,7 +23444,7 @@
         <v>1611</v>
       </c>
       <c r="D604" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E604" s="5" t="s">
@@ -23183,7 +23468,7 @@
         <v>1613</v>
       </c>
       <c r="D605" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E605" s="5" t="s">
@@ -23207,7 +23492,7 @@
         <v>1615</v>
       </c>
       <c r="D606" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E606" s="5" t="s">
@@ -23231,7 +23516,7 @@
         <v>1617</v>
       </c>
       <c r="D607" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E607" s="5" t="s">
@@ -23255,7 +23540,7 @@
         <v>1619</v>
       </c>
       <c r="D608" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E608" s="5" t="s">
@@ -23279,7 +23564,7 @@
         <v>1621</v>
       </c>
       <c r="D609" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E609" s="5" t="s">
@@ -23303,7 +23588,7 @@
         <v>1623</v>
       </c>
       <c r="D610" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E610" s="5" t="s">
@@ -23327,7 +23612,7 @@
         <v>1625</v>
       </c>
       <c r="D611" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E611" s="5" t="s">
@@ -23351,7 +23636,7 @@
         <v>1627</v>
       </c>
       <c r="D612" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E612" s="5" t="s">
@@ -23375,7 +23660,7 @@
         <v>1629</v>
       </c>
       <c r="D613" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E613" s="5" t="s">
@@ -23399,7 +23684,7 @@
         <v>1630</v>
       </c>
       <c r="D614" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E614" s="5" t="s">
@@ -23423,7 +23708,7 @@
         <v>1632</v>
       </c>
       <c r="D615" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F major</v>
       </c>
       <c r="E615" s="5" t="s">
@@ -23447,7 +23732,7 @@
         <v>1634</v>
       </c>
       <c r="D616" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F minor</v>
       </c>
       <c r="E616" s="5" t="s">
@@ -23471,7 +23756,7 @@
         <v>1636</v>
       </c>
       <c r="D617" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F minor</v>
       </c>
       <c r="E617" s="5" t="s">
@@ -23495,7 +23780,7 @@
         <v>1638</v>
       </c>
       <c r="D618" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F minor</v>
       </c>
       <c r="E618" s="5" t="s">
@@ -23519,7 +23804,7 @@
         <v>1640</v>
       </c>
       <c r="D619" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in F-sharp minor</v>
       </c>
       <c r="E619" s="5" t="s">
@@ -23543,7 +23828,7 @@
         <v>1642</v>
       </c>
       <c r="D620" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E620" s="5" t="s">
@@ -23567,7 +23852,7 @@
         <v>1644</v>
       </c>
       <c r="D621" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E621" s="5" t="s">
@@ -23591,7 +23876,7 @@
         <v>1646</v>
       </c>
       <c r="D622" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E622" s="5" t="s">
@@ -23618,7 +23903,7 @@
         <v>1648</v>
       </c>
       <c r="D623" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E623" s="5" t="s">
@@ -23642,7 +23927,7 @@
         <v>1650</v>
       </c>
       <c r="D624" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E624" s="5" t="s">
@@ -23666,7 +23951,7 @@
         <v>1652</v>
       </c>
       <c r="D625" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E625" s="5" t="s">
@@ -23690,7 +23975,7 @@
         <v>1654</v>
       </c>
       <c r="D626" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E626" s="5" t="s">
@@ -23714,7 +23999,7 @@
         <v>1656</v>
       </c>
       <c r="D627" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E627" s="5" t="s">
@@ -23738,7 +24023,7 @@
         <v>1658</v>
       </c>
       <c r="D628" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E628" s="5" t="s">
@@ -23762,7 +24047,7 @@
         <v>1660</v>
       </c>
       <c r="D629" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E629" s="5" t="s">
@@ -23786,7 +24071,7 @@
         <v>1662</v>
       </c>
       <c r="D630" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E630" s="5" t="s">
@@ -23810,7 +24095,7 @@
         <v>1664</v>
       </c>
       <c r="D631" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E631" s="5" t="s">
@@ -23881,7 +24166,7 @@
         <v>1671</v>
       </c>
       <c r="D634" s="4" t="str">
-        <f t="shared" ref="D634:D659" si="6">E634&amp;" in "&amp;F634</f>
+        <f t="shared" ref="D634:D659" si="15">E634&amp;" in "&amp;F634</f>
         <v>Sonata in G major</v>
       </c>
       <c r="E634" s="5" t="s">
@@ -23905,7 +24190,7 @@
         <v>1673</v>
       </c>
       <c r="D635" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E635" s="5" t="s">
@@ -23929,7 +24214,7 @@
         <v>1675</v>
       </c>
       <c r="D636" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E636" s="5" t="s">
@@ -23953,7 +24238,7 @@
         <v>1677</v>
       </c>
       <c r="D637" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E637" s="5" t="s">
@@ -23977,7 +24262,7 @@
         <v>1679</v>
       </c>
       <c r="D638" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E638" s="5" t="s">
@@ -23998,7 +24283,7 @@
         <v>1680</v>
       </c>
       <c r="D639" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E639" s="5" t="s">
@@ -24028,7 +24313,7 @@
         <v>1683</v>
       </c>
       <c r="D640" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E640" s="5" t="s">
@@ -24052,7 +24337,7 @@
         <v>1685</v>
       </c>
       <c r="D641" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E641" s="5" t="s">
@@ -24076,7 +24361,7 @@
         <v>1687</v>
       </c>
       <c r="D642" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E642" s="5" t="s">
@@ -24100,7 +24385,7 @@
         <v>1689</v>
       </c>
       <c r="D643" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E643" s="5" t="s">
@@ -24124,7 +24409,7 @@
         <v>1690</v>
       </c>
       <c r="D644" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E644" s="5" t="s">
@@ -24148,7 +24433,7 @@
         <v>1692</v>
       </c>
       <c r="D645" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E645" s="5" t="s">
@@ -24172,7 +24457,7 @@
         <v>1694</v>
       </c>
       <c r="D646" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E646" s="5" t="s">
@@ -24196,7 +24481,7 @@
         <v>1696</v>
       </c>
       <c r="D647" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E647" s="5" t="s">
@@ -24220,7 +24505,7 @@
         <v>1698</v>
       </c>
       <c r="D648" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E648" s="5" t="s">
@@ -24244,7 +24529,7 @@
         <v>1700</v>
       </c>
       <c r="D649" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G major</v>
       </c>
       <c r="E649" s="5" t="s">
@@ -24268,7 +24553,7 @@
         <v>1702</v>
       </c>
       <c r="D650" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G minor</v>
       </c>
       <c r="E650" s="5" t="s">
@@ -24292,7 +24577,7 @@
         <v>1704</v>
       </c>
       <c r="D651" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G minor</v>
       </c>
       <c r="E651" s="5" t="s">
@@ -24316,7 +24601,7 @@
         <v>1706</v>
       </c>
       <c r="D652" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G minor</v>
       </c>
       <c r="E652" s="5" t="s">
@@ -24340,7 +24625,7 @@
         <v>1708</v>
       </c>
       <c r="D653" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G minor</v>
       </c>
       <c r="E653" s="5" t="s">
@@ -24364,7 +24649,7 @@
         <v>1710</v>
       </c>
       <c r="D654" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G minor</v>
       </c>
       <c r="E654" s="5" t="s">
@@ -24388,7 +24673,7 @@
         <v>1712</v>
       </c>
       <c r="D655" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G minor</v>
       </c>
       <c r="E655" s="5" t="s">
@@ -24412,7 +24697,7 @@
         <v>1714</v>
       </c>
       <c r="D656" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G minor</v>
       </c>
       <c r="E656" s="5" t="s">
@@ -24436,7 +24721,7 @@
         <v>1717</v>
       </c>
       <c r="D657" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G minor</v>
       </c>
       <c r="E657" s="5" t="s">
@@ -24460,7 +24745,7 @@
         <v>1719</v>
       </c>
       <c r="D658" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G minor</v>
       </c>
       <c r="E658" s="5" t="s">
@@ -24484,7 +24769,7 @@
         <v>1721</v>
       </c>
       <c r="D659" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>Sonata in G minor</v>
       </c>
       <c r="E659" s="5" t="s">
@@ -24934,7 +25219,7 @@
         <v>1771</v>
       </c>
       <c r="D685" s="4" t="str">
-        <f t="shared" ref="D685:D710" si="7">E685&amp;" in "&amp;F685</f>
+        <f t="shared" ref="D685:D710" si="16">E685&amp;" in "&amp;F685</f>
         <v>Sonatina in B-flat major</v>
       </c>
       <c r="E685" s="5" t="s">
@@ -24958,7 +25243,7 @@
         <v>1774</v>
       </c>
       <c r="D686" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in B-flat major</v>
       </c>
       <c r="E686" s="5" t="s">
@@ -24982,7 +25267,7 @@
         <v>1776</v>
       </c>
       <c r="D687" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in C major</v>
       </c>
       <c r="E687" s="5" t="s">
@@ -25006,7 +25291,7 @@
         <v>1778</v>
       </c>
       <c r="D688" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in C major</v>
       </c>
       <c r="E688" s="5" t="s">
@@ -25030,7 +25315,7 @@
         <v>1781</v>
       </c>
       <c r="D689" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in C major</v>
       </c>
       <c r="E689" s="5" t="s">
@@ -25054,7 +25339,7 @@
         <v>1783</v>
       </c>
       <c r="D690" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in D major</v>
       </c>
       <c r="E690" s="5" t="s">
@@ -25081,7 +25366,7 @@
         <v>1785</v>
       </c>
       <c r="D691" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in D major</v>
       </c>
       <c r="E691" s="5" t="s">
@@ -25105,7 +25390,7 @@
         <v>1787</v>
       </c>
       <c r="D692" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in D major</v>
       </c>
       <c r="E692" s="5" t="s">
@@ -25129,7 +25414,7 @@
         <v>1789</v>
       </c>
       <c r="D693" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in D major</v>
       </c>
       <c r="E693" s="5" t="s">
@@ -25153,7 +25438,7 @@
         <v>1791</v>
       </c>
       <c r="D694" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in D major</v>
       </c>
       <c r="E694" s="5" t="s">
@@ -25177,7 +25462,7 @@
         <v>1793</v>
       </c>
       <c r="D695" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in D minor</v>
       </c>
       <c r="E695" s="5" t="s">
@@ -25201,7 +25486,7 @@
         <v>1796</v>
       </c>
       <c r="D696" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in D minor</v>
       </c>
       <c r="E696" s="5" t="s">
@@ -25225,7 +25510,7 @@
         <v>1798</v>
       </c>
       <c r="D697" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in E major</v>
       </c>
       <c r="E697" s="5" t="s">
@@ -25249,7 +25534,7 @@
         <v>1800</v>
       </c>
       <c r="D698" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in E major</v>
       </c>
       <c r="E698" s="5" t="s">
@@ -25273,7 +25558,7 @@
         <v>1802</v>
       </c>
       <c r="D699" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in E minor</v>
       </c>
       <c r="E699" s="5" t="s">
@@ -25300,7 +25585,7 @@
         <v>1804</v>
       </c>
       <c r="D700" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in E-flat major</v>
       </c>
       <c r="E700" s="5" t="s">
@@ -25327,7 +25612,7 @@
         <v>1806</v>
       </c>
       <c r="D701" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in E-flat major</v>
       </c>
       <c r="E701" s="5" t="s">
@@ -25351,7 +25636,7 @@
         <v>1808</v>
       </c>
       <c r="D702" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in E-flat major</v>
       </c>
       <c r="E702" s="5" t="s">
@@ -25375,7 +25660,7 @@
         <v>1810</v>
       </c>
       <c r="D703" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in F major</v>
       </c>
       <c r="E703" s="5" t="s">
@@ -25402,7 +25687,7 @@
         <v>1812</v>
       </c>
       <c r="D704" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in F major</v>
       </c>
       <c r="E704" s="5" t="s">
@@ -25426,7 +25711,7 @@
         <v>1814</v>
       </c>
       <c r="D705" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in F major</v>
       </c>
       <c r="E705" s="5" t="s">
@@ -25450,7 +25735,7 @@
         <v>1816</v>
       </c>
       <c r="D706" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in F major</v>
       </c>
       <c r="E706" s="5" t="s">
@@ -25474,7 +25759,7 @@
         <v>1818</v>
       </c>
       <c r="D707" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in G major</v>
       </c>
       <c r="E707" s="5" t="s">
@@ -25501,7 +25786,7 @@
         <v>1820</v>
       </c>
       <c r="D708" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in G major</v>
       </c>
       <c r="E708" s="5" t="s">
@@ -25525,7 +25810,7 @@
         <v>1822</v>
       </c>
       <c r="D709" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in G major</v>
       </c>
       <c r="E709" s="5" t="s">
@@ -25549,7 +25834,7 @@
         <v>1824</v>
       </c>
       <c r="D710" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>Sonatina in G major</v>
       </c>
       <c r="E710" s="5" t="s">
@@ -25614,7 +25899,7 @@
         <v>1831</v>
       </c>
       <c r="D713" s="4" t="str">
-        <f t="shared" ref="D713:D725" si="8">E713&amp;" in "&amp;F713</f>
+        <f t="shared" ref="D713:D725" si="17">E713&amp;" in "&amp;F713</f>
         <v>Symphony in D major</v>
       </c>
       <c r="E713" s="5" t="s">
@@ -25638,7 +25923,7 @@
         <v>1833</v>
       </c>
       <c r="D714" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in E minor</v>
       </c>
       <c r="E714" s="5" t="s">
@@ -25662,7 +25947,7 @@
         <v>1835</v>
       </c>
       <c r="D715" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in E minor</v>
       </c>
       <c r="E715" s="5" t="s">
@@ -25686,7 +25971,7 @@
         <v>1837</v>
       </c>
       <c r="D716" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in E minor</v>
       </c>
       <c r="E716" s="5" t="s">
@@ -25710,7 +25995,7 @@
         <v>1840</v>
       </c>
       <c r="D717" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in E-flat major</v>
       </c>
       <c r="E717" s="5" t="s">
@@ -25734,7 +26019,7 @@
         <v>1843</v>
       </c>
       <c r="D718" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in F major</v>
       </c>
       <c r="E718" s="5" t="s">
@@ -25758,7 +26043,7 @@
         <v>1845</v>
       </c>
       <c r="D719" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in F major</v>
       </c>
       <c r="E719" s="5" t="s">
@@ -25782,7 +26067,7 @@
         <v>1848</v>
       </c>
       <c r="D720" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in F major</v>
       </c>
       <c r="E720" s="5" t="s">
@@ -25806,7 +26091,7 @@
         <v>1850</v>
       </c>
       <c r="D721" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in F major</v>
       </c>
       <c r="E721" s="5" t="s">
@@ -25830,7 +26115,7 @@
         <v>1852</v>
       </c>
       <c r="D722" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in G major</v>
       </c>
       <c r="E722" s="5" t="s">
@@ -25854,7 +26139,7 @@
         <v>1854</v>
       </c>
       <c r="D723" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in G major</v>
       </c>
       <c r="E723" s="5" t="s">
@@ -25878,7 +26163,7 @@
         <v>1856</v>
       </c>
       <c r="D724" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in G major</v>
       </c>
       <c r="E724" s="5" t="s">
@@ -25899,7 +26184,7 @@
         <v>1217</v>
       </c>
       <c r="D725" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>Symphony in G major</v>
       </c>
       <c r="E725" s="5" t="s">
@@ -30658,7 +30943,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B1:C1 E1:I1 B1031:C1125 E1031:I1125" numberStoredAsText="1"/>
+    <ignoredError sqref="E1031:I1125 B1031:C1125 E1:I1 B1:C1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/xlsx/CPE.xlsx
+++ b/xlsx/CPE.xlsx
@@ -3234,7 +3234,7 @@
     <t>Oratorio de Pâques</t>
   </si>
   <si>
-    <t>Oratario</t>
+    <t>Oratorio</t>
   </si>
   <si>
     <t>Wq. 241</t>
@@ -30943,7 +30943,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E1031:I1125 B1031:C1125 E1:I1 B1:C1" numberStoredAsText="1"/>
+    <ignoredError sqref="B1:C1 E1:I1 B1031:C1125 E1031:I1125" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>